--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18135"/>
+    <workbookView windowHeight="15560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
   <si>
     <t>##</t>
   </si>
@@ -1116,6 +1116,24 @@
   </si>
   <si>
     <t>사과</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>测试1</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>测试2</t>
+  </si>
+  <si>
+    <t>1test</t>
+  </si>
+  <si>
+    <t>1测试</t>
   </si>
 </sst>
 </file>
@@ -1288,17 +1306,17 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="MS Gothic"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Courier New"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2081,15 +2099,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.83333333333333" style="1"/>
+    <col min="1" max="1" width="8.83035714285714" style="1"/>
     <col min="2" max="2" width="23.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6696428571429" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83333333333333" style="1"/>
+    <col min="6" max="16384" width="8.83035714285714" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2130,7 +2148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="17" spans="1:6">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2166,7 +2184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:6">
+    <row r="5" ht="17" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>18</v>
@@ -2184,7 +2202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" ht="17" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>23</v>
@@ -2338,7 +2356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" ht="15" spans="1:6">
+    <row r="15" ht="17" spans="1:6">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -2410,7 +2428,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="1:6">
+    <row r="19" ht="17" spans="1:6">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>77</v>
@@ -2482,7 +2500,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" ht="17" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>92</v>
@@ -2551,6 +2569,30 @@
       </c>
       <c r="F26" s="1" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1af74662fb4a4f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R096d4034927b490f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3377,35 +3377,147 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141"/>
-      <x:c r="B141"/>
-      <x:c r="C141"/>
-      <x:c r="D141"/>
-      <x:c r="E141"/>
-      <x:c r="F141"/>
+      <x:c r="B141" t="str">
+        <x:v>Buqi.Stage.OperationChoice.Description</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>选择坊市、机缘或静修；当前周天保持可见。</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>Choose the bazaar, an encounter, or cultivation; the current cycle remains visible.</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>選擇坊市、機緣或靜修；目前周天保持可見。</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>상점, 기연 또는 수련을 선택하세요. 현재 주천은 계속 표시됩니다.</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142"/>
-      <x:c r="B142"/>
-      <x:c r="C142"/>
-      <x:c r="D142"/>
-      <x:c r="E142"/>
-      <x:c r="F142"/>
+      <x:c r="B142" t="str">
+        <x:v>Buqi.Stage.OperationChoice.Title</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>经营选择</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>Operation Choice</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>經營選擇</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>운영 선택</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143"/>
-      <x:c r="B143"/>
-      <x:c r="C143"/>
-      <x:c r="D143"/>
-      <x:c r="E143"/>
-      <x:c r="F143"/>
+      <x:c r="B143" t="str">
+        <x:v>Buqi.Stage.PveSelection.Description</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>选择初阶、进阶或险阶后直接进入战斗。</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>Choose Novice, Advanced, or Perilous, then enter battle.</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>選擇初階、進階或險階後直接進入戰鬥。</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>초급, 중급 또는 위험 단계를 선택한 뒤 바로 전투에 진입하세요.</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144"/>
-      <x:c r="B144"/>
-      <x:c r="C144"/>
-      <x:c r="D144"/>
-      <x:c r="E144"/>
-      <x:c r="F144"/>
+      <x:c r="B144" t="str">
+        <x:v>Buqi.Stage.PveSelection.Title</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>PVE 选关</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>PVE Selection</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>PVE 選關</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>PVE 선택</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145"/>
+      <x:c r="B145" t="str">
+        <x:v>Buqi.Stage.TribulationRoute.Description</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>九日夜战后选择一条渡劫路线。</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>After the ninth night's battle, choose a tribulation route.</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>九日夜戰後選擇一條渡劫路線。</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>9일째 야간 전투 후 천겁 경로를 하나 선택하세요.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146"/>
+      <x:c r="B146" t="str">
+        <x:v>Buqi.Stage.TribulationRoute.Title</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>渡劫路线</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>Tribulation Route</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>渡劫路線</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>천겁 경로</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147"/>
+      <x:c r="B147" t="str">
+        <x:v>Buqi.Stage.TribulationStage.Description</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>应劫并推进当前阶段。</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>Face the tribulation and advance the current stage.</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>應劫並推進目前階段。</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>천겁에 맞서 현재 단계를 진행하세요.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148"/>
+      <x:c r="B148" t="str">
+        <x:v>Buqi.Stage.TribulationStage.Title</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>三阶段天劫</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>Three-Stage Tribulation</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>三階段天劫</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>3단계 천겁</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R096d4034927b490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1d4f81e9d79483e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3519,6 +3519,114 @@
         <x:v>3단계 천겁</x:v>
       </x:c>
     </x:row>
+    <x:row r="149">
+      <x:c r="A149"/>
+      <x:c r="B149" t="str">
+        <x:v>Buqi.RunShell.DayRecord</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>日记录</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>Day Record</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>日記錄</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>일일 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150"/>
+      <x:c r="B150" t="str">
+        <x:v>Buqi.RunShell.MorningOperation</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>晨 · 经营</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>Morning · Operation</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>晨 · 經營</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>아침 · 경영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151"/>
+      <x:c r="B151" t="str">
+        <x:v>Buqi.RunShell.NoonOperation</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>昼 · 经营</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>Noon · Operation</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>晝 · 經營</x:v>
+      </x:c>
+      <x:c r="F151" t="str">
+        <x:v>낮 · 경영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152"/>
+      <x:c r="B152" t="str">
+        <x:v>Buqi.RunShell.DuskPve</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>昏 · PVE</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>Dusk · PVE</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>昏 · PVE</x:v>
+      </x:c>
+      <x:c r="F152" t="str">
+        <x:v>해질녘 · PVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153"/>
+      <x:c r="B153" t="str">
+        <x:v>Buqi.RunShell.NightPvp</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>夜 · 异步 PVP</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>Night · Async PVP</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>夜 · 非同步 PVP</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>밤 · 비동기 PVP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154"/>
+      <x:c r="B154" t="str">
+        <x:v>Buqi.Stage.Shared.CurrentBoard</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>当前周天</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>Current Cycle Board</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>當前周天</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>현재 주천</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1d4f81e9d79483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdce68705486742b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3627,6 +3627,5142 @@
         <x:v>현재 주천</x:v>
       </x:c>
     </x:row>
+    <x:row r="155">
+      <x:c r="A155"/>
+      <x:c r="B155" t="str">
+        <x:v>Buqi.Content.Item.W8_003.Name</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>急攻令</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>Rapid Writ</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>急攻令</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>Rapid Writ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156"/>
+      <x:c r="B156" t="str">
+        <x:v>Buqi.Content.Item.W8_003.Upgrade</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157"/>
+      <x:c r="B157" t="str">
+        <x:v>Buqi.Content.Item.W8_005.Name</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>冲锋看板</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>Charge Ledger</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>冲锋看板</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>Charge Ledger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158"/>
+      <x:c r="B158" t="str">
+        <x:v>Buqi.Content.Item.W8_005.Upgrade</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159"/>
+      <x:c r="B159" t="str">
+        <x:v>Buqi.Content.Item.W8_006.Name</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>终局重锤</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>Final Maul</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>终局重锤</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>Final Maul</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160"/>
+      <x:c r="B160" t="str">
+        <x:v>Buqi.Content.Item.W8_006.Upgrade</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161"/>
+      <x:c r="B161" t="str">
+        <x:v>Buqi.Content.Item.W8_007.Name</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>小护盾</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>Ward Tile</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>小护盾</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>Ward Tile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162"/>
+      <x:c r="B162" t="str">
+        <x:v>Buqi.Content.Item.W8_007.Upgrade</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163"/>
+      <x:c r="B163" t="str">
+        <x:v>Buqi.Content.Item.W8_008.Name</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>破盾清单</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>Rupture List</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>破盾清单</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>Rupture List</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164"/>
+      <x:c r="B164" t="str">
+        <x:v>Buqi.Content.Item.W8_008.Upgrade</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165"/>
+      <x:c r="B165" t="str">
+        <x:v>Buqi.Content.Item.W8_012.Name</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>堡垒核心</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>Bastion Core</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>堡垒核心</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>Bastion Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166"/>
+      <x:c r="B166" t="str">
+        <x:v>Buqi.Content.Item.W8_012.Upgrade</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F166" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167"/>
+      <x:c r="B167" t="str">
+        <x:v>Buqi.Content.Item.W8_013.Name</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>传能接线</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>Conduction Lead</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>传能接线</x:v>
+      </x:c>
+      <x:c r="F167" t="str">
+        <x:v>Conduction Lead</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168"/>
+      <x:c r="B168" t="str">
+        <x:v>Buqi.Content.Item.W8_013.Upgrade</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F168" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169"/>
+      <x:c r="B169" t="str">
+        <x:v>Buqi.Content.Item.W8_014.Name</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>连击印</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>Chain Seal</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>连击印</x:v>
+      </x:c>
+      <x:c r="F169" t="str">
+        <x:v>Chain Seal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170"/>
+      <x:c r="B170" t="str">
+        <x:v>Buqi.Content.Item.W8_014.Upgrade</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171"/>
+      <x:c r="B171" t="str">
+        <x:v>Buqi.Content.Item.W8_015.Name</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>节奏节点</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>Cadence Node</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>节奏节点</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>Cadence Node</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172"/>
+      <x:c r="B172" t="str">
+        <x:v>Buqi.Content.Item.W8_015.Upgrade</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173"/>
+      <x:c r="B173" t="str">
+        <x:v>Buqi.Content.Item.W8_016.Name</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>急救包</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>First Aid Satchel</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>急救包</x:v>
+      </x:c>
+      <x:c r="F173" t="str">
+        <x:v>First Aid Satchel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174"/>
+      <x:c r="B174" t="str">
+        <x:v>Buqi.Content.Item.W8_016.Upgrade</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F174" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175"/>
+      <x:c r="B175" t="str">
+        <x:v>Buqi.Content.Item.W8_017.Name</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>回春泉</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>Renewal Spring</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>回春泉</x:v>
+      </x:c>
+      <x:c r="F175" t="str">
+        <x:v>Renewal Spring</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176"/>
+      <x:c r="B176" t="str">
+        <x:v>Buqi.Content.Item.W8_017.Upgrade</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F176" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177"/>
+      <x:c r="B177" t="str">
+        <x:v>Buqi.Content.Item.W8_018.Name</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>救援旗</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>Rescue Banner</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>救援旗</x:v>
+      </x:c>
+      <x:c r="F177" t="str">
+        <x:v>Rescue Banner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178"/>
+      <x:c r="B178" t="str">
+        <x:v>Buqi.Content.Item.W8_018.Upgrade</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F178" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179"/>
+      <x:c r="B179" t="str">
+        <x:v>Buqi.Content.Item.W8_019.Name</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>毒针</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
+        <x:v>Venom Needle</x:v>
+      </x:c>
+      <x:c r="E179" t="str">
+        <x:v>毒针</x:v>
+      </x:c>
+      <x:c r="F179" t="str">
+        <x:v>Venom Needle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180"/>
+      <x:c r="B180" t="str">
+        <x:v>Buqi.Content.Item.W8_019.Upgrade</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E180" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F180" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181"/>
+      <x:c r="B181" t="str">
+        <x:v>Buqi.Content.Item.W8_020.Name</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>腐蚀瓶</x:v>
+      </x:c>
+      <x:c r="D181" t="str">
+        <x:v>Corrosion Flask</x:v>
+      </x:c>
+      <x:c r="E181" t="str">
+        <x:v>腐蚀瓶</x:v>
+      </x:c>
+      <x:c r="F181" t="str">
+        <x:v>Corrosion Flask</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182"/>
+      <x:c r="B182" t="str">
+        <x:v>Buqi.Content.Item.W8_020.Upgrade</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D182" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E182" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F182" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183"/>
+      <x:c r="B183" t="str">
+        <x:v>Buqi.Content.Item.W8_021.Name</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>毒雾炉</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>Miasma Furnace</x:v>
+      </x:c>
+      <x:c r="E183" t="str">
+        <x:v>毒雾炉</x:v>
+      </x:c>
+      <x:c r="F183" t="str">
+        <x:v>Miasma Furnace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184"/>
+      <x:c r="B184" t="str">
+        <x:v>Buqi.Content.Item.W8_021.Upgrade</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D184" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E184" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F184" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185"/>
+      <x:c r="B185" t="str">
+        <x:v>Buqi.Content.Item.W8_022.Name</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>火花符</x:v>
+      </x:c>
+      <x:c r="D185" t="str">
+        <x:v>Spark Talisman</x:v>
+      </x:c>
+      <x:c r="E185" t="str">
+        <x:v>火花符</x:v>
+      </x:c>
+      <x:c r="F185" t="str">
+        <x:v>Spark Talisman</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186"/>
+      <x:c r="B186" t="str">
+        <x:v>Buqi.Content.Item.W8_022.Upgrade</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D186" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E186" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F186" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187"/>
+      <x:c r="B187" t="str">
+        <x:v>Buqi.Content.Item.W8_023.Name</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>炽焰炉</x:v>
+      </x:c>
+      <x:c r="D187" t="str">
+        <x:v>Ember Furnace</x:v>
+      </x:c>
+      <x:c r="E187" t="str">
+        <x:v>炽焰炉</x:v>
+      </x:c>
+      <x:c r="F187" t="str">
+        <x:v>Ember Furnace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188"/>
+      <x:c r="B188" t="str">
+        <x:v>Buqi.Content.Item.W8_023.Upgrade</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D188" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E188" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F188" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189"/>
+      <x:c r="B189" t="str">
+        <x:v>Buqi.Content.Item.W8_024.Name</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>爆燃阵</x:v>
+      </x:c>
+      <x:c r="D189" t="str">
+        <x:v>Flashfire Array</x:v>
+      </x:c>
+      <x:c r="E189" t="str">
+        <x:v>爆燃阵</x:v>
+      </x:c>
+      <x:c r="F189" t="str">
+        <x:v>Flashfire Array</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190"/>
+      <x:c r="B190" t="str">
+        <x:v>Buqi.Content.Item.W8_024.Upgrade</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D190" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E190" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F190" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191"/>
+      <x:c r="B191" t="str">
+        <x:v>Buqi.Content.Item.W8_025.Name</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>寒镜</x:v>
+      </x:c>
+      <x:c r="D191" t="str">
+        <x:v>Frost Mirror</x:v>
+      </x:c>
+      <x:c r="E191" t="str">
+        <x:v>寒镜</x:v>
+      </x:c>
+      <x:c r="F191" t="str">
+        <x:v>Frost Mirror</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192"/>
+      <x:c r="B192" t="str">
+        <x:v>Buqi.Content.Item.W8_025.Upgrade</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D192" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E192" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F192" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193"/>
+      <x:c r="B193" t="str">
+        <x:v>Buqi.Content.Item.W8_026.Name</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>霜锁</x:v>
+      </x:c>
+      <x:c r="D193" t="str">
+        <x:v>Rime Lock</x:v>
+      </x:c>
+      <x:c r="E193" t="str">
+        <x:v>霜锁</x:v>
+      </x:c>
+      <x:c r="F193" t="str">
+        <x:v>Rime Lock</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194"/>
+      <x:c r="B194" t="str">
+        <x:v>Buqi.Content.Item.W8_026.Upgrade</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195"/>
+      <x:c r="B195" t="str">
+        <x:v>Buqi.Content.Item.W8_027.Name</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>冰封塔</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>Icebound Tower</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>冰封塔</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>Icebound Tower</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196"/>
+      <x:c r="B196" t="str">
+        <x:v>Buqi.Content.Item.W8_027.Upgrade</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197"/>
+      <x:c r="B197" t="str">
+        <x:v>Buqi.Content.Item.W8_028.Name</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>过载电池</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>Overload Cell</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>过载电池</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>Overload Cell</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198"/>
+      <x:c r="B198" t="str">
+        <x:v>Buqi.Content.Item.W8_028.Upgrade</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199"/>
+      <x:c r="B199" t="str">
+        <x:v>Buqi.Content.Item.W8_029.Name</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>泄压阀</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>Relief Valve</x:v>
+      </x:c>
+      <x:c r="E199" t="str">
+        <x:v>泄压阀</x:v>
+      </x:c>
+      <x:c r="F199" t="str">
+        <x:v>Relief Valve</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200"/>
+      <x:c r="B200" t="str">
+        <x:v>Buqi.Content.Item.W8_029.Upgrade</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E200" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F200" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201"/>
+      <x:c r="B201" t="str">
+        <x:v>Buqi.Content.Item.W8_030.Name</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>稳压核心</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>Stability Core</x:v>
+      </x:c>
+      <x:c r="E201" t="str">
+        <x:v>稳压核心</x:v>
+      </x:c>
+      <x:c r="F201" t="str">
+        <x:v>Stability Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202"/>
+      <x:c r="B202" t="str">
+        <x:v>Buqi.Content.Item.W8_030.Upgrade</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E202" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F202" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203"/>
+      <x:c r="B203" t="str">
+        <x:v>Buqi.Content.Item.W8_031.Name</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>走马铃</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
+        <x:v>Gallop Bell</x:v>
+      </x:c>
+      <x:c r="E203" t="str">
+        <x:v>走马铃</x:v>
+      </x:c>
+      <x:c r="F203" t="str">
+        <x:v>Gallop Bell</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204"/>
+      <x:c r="B204" t="str">
+        <x:v>Buqi.Content.Item.W8_031.Upgrade</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D204" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E204" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F204" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205"/>
+      <x:c r="B205" t="str">
+        <x:v>Buqi.Content.Item.W8_032.Name</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>借势扣</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
+        <x:v>Borrowed Force Clasp</x:v>
+      </x:c>
+      <x:c r="E205" t="str">
+        <x:v>借势扣</x:v>
+      </x:c>
+      <x:c r="F205" t="str">
+        <x:v>Borrowed Force Clasp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206"/>
+      <x:c r="B206" t="str">
+        <x:v>Buqi.Content.Item.W8_032.Upgrade</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E206" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F206" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207"/>
+      <x:c r="B207" t="str">
+        <x:v>Buqi.Content.Item.W8_033.Name</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>回锋匣</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>Returning Edge Coffer</x:v>
+      </x:c>
+      <x:c r="E207" t="str">
+        <x:v>回锋匣</x:v>
+      </x:c>
+      <x:c r="F207" t="str">
+        <x:v>Returning Edge Coffer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208"/>
+      <x:c r="B208" t="str">
+        <x:v>Buqi.Content.Item.W8_033.Upgrade</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E208" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F208" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209"/>
+      <x:c r="B209" t="str">
+        <x:v>Buqi.Content.Item.W8_034.Name</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>破阵锥</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>Formation Spike</x:v>
+      </x:c>
+      <x:c r="E209" t="str">
+        <x:v>破阵锥</x:v>
+      </x:c>
+      <x:c r="F209" t="str">
+        <x:v>Formation Spike</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210"/>
+      <x:c r="B210" t="str">
+        <x:v>Buqi.Content.Item.W8_034.Upgrade</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E210" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F210" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211"/>
+      <x:c r="B211" t="str">
+        <x:v>Buqi.Content.Item.W8_035.Name</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>试锋算盘</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>Trial Abacus</x:v>
+      </x:c>
+      <x:c r="E211" t="str">
+        <x:v>试锋算盘</x:v>
+      </x:c>
+      <x:c r="F211" t="str">
+        <x:v>Trial Abacus</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212"/>
+      <x:c r="B212" t="str">
+        <x:v>Buqi.Content.Item.W8_035.Upgrade</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E212" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F212" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213"/>
+      <x:c r="B213" t="str">
+        <x:v>Buqi.Content.Item.W8_036.Name</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>连垣扣</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
+        <x:v>Linked Rampart Clasp</x:v>
+      </x:c>
+      <x:c r="E213" t="str">
+        <x:v>连垣扣</x:v>
+      </x:c>
+      <x:c r="F213" t="str">
+        <x:v>Linked Rampart Clasp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214"/>
+      <x:c r="B214" t="str">
+        <x:v>Buqi.Content.Item.W8_036.Upgrade</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E214" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F214" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215"/>
+      <x:c r="B215" t="str">
+        <x:v>Buqi.Content.Item.W8_037.Name</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>蓄势砚</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>Stored Force Inkstone</x:v>
+      </x:c>
+      <x:c r="E215" t="str">
+        <x:v>蓄势砚</x:v>
+      </x:c>
+      <x:c r="F215" t="str">
+        <x:v>Stored Force Inkstone</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216"/>
+      <x:c r="B216" t="str">
+        <x:v>Buqi.Content.Item.W8_037.Upgrade</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E216" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F216" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217"/>
+      <x:c r="B217" t="str">
+        <x:v>Buqi.Content.Item.W8_038.Name</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>活门甲</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
+        <x:v>Living Gate Armor</x:v>
+      </x:c>
+      <x:c r="E217" t="str">
+        <x:v>活门甲</x:v>
+      </x:c>
+      <x:c r="F217" t="str">
+        <x:v>Living Gate Armor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218"/>
+      <x:c r="B218" t="str">
+        <x:v>Buqi.Content.Item.W8_038.Upgrade</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E218" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F218" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219"/>
+      <x:c r="B219" t="str">
+        <x:v>Buqi.Content.Item.W8_039.Name</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>净脉璧</x:v>
+      </x:c>
+      <x:c r="D219" t="str">
+        <x:v>Clear Vein Jade</x:v>
+      </x:c>
+      <x:c r="E219" t="str">
+        <x:v>净脉璧</x:v>
+      </x:c>
+      <x:c r="F219" t="str">
+        <x:v>Clear Vein Jade</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220"/>
+      <x:c r="B220" t="str">
+        <x:v>Buqi.Content.Item.W8_039.Upgrade</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D220" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E220" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F220" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221"/>
+      <x:c r="B221" t="str">
+        <x:v>Buqi.Content.Item.W8_040.Name</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>守成印</x:v>
+      </x:c>
+      <x:c r="D221" t="str">
+        <x:v>Steadfast Seal</x:v>
+      </x:c>
+      <x:c r="E221" t="str">
+        <x:v>守成印</x:v>
+      </x:c>
+      <x:c r="F221" t="str">
+        <x:v>Steadfast Seal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222"/>
+      <x:c r="B222" t="str">
+        <x:v>Buqi.Content.Item.W8_040.Upgrade</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D222" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E222" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F222" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223"/>
+      <x:c r="B223" t="str">
+        <x:v>Buqi.Content.Item.W8_041.Name</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>续脉灯</x:v>
+      </x:c>
+      <x:c r="D223" t="str">
+        <x:v>Pulse Lantern</x:v>
+      </x:c>
+      <x:c r="E223" t="str">
+        <x:v>续脉灯</x:v>
+      </x:c>
+      <x:c r="F223" t="str">
+        <x:v>Pulse Lantern</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224"/>
+      <x:c r="B224" t="str">
+        <x:v>Buqi.Content.Item.W8_041.Upgrade</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D224" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E224" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F224" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225"/>
+      <x:c r="B225" t="str">
+        <x:v>Buqi.Content.Item.W8_042.Name</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>调息枢</x:v>
+      </x:c>
+      <x:c r="D225" t="str">
+        <x:v>Breath Pivot</x:v>
+      </x:c>
+      <x:c r="E225" t="str">
+        <x:v>调息枢</x:v>
+      </x:c>
+      <x:c r="F225" t="str">
+        <x:v>Breath Pivot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226"/>
+      <x:c r="B226" t="str">
+        <x:v>Buqi.Content.Item.W8_042.Upgrade</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D226" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E226" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F226" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227"/>
+      <x:c r="B227" t="str">
+        <x:v>Buqi.Content.Item.W8_043.Name</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>回光鉴</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
+        <x:v>Last Light Mirror</x:v>
+      </x:c>
+      <x:c r="E227" t="str">
+        <x:v>回光鉴</x:v>
+      </x:c>
+      <x:c r="F227" t="str">
+        <x:v>Last Light Mirror</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228"/>
+      <x:c r="B228" t="str">
+        <x:v>Buqi.Content.Item.W8_043.Upgrade</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E228" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F228" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229"/>
+      <x:c r="B229" t="str">
+        <x:v>Buqi.Content.Item.W8_044.Name</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>护命佩</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
+        <x:v>Life Guard Pendant</x:v>
+      </x:c>
+      <x:c r="E229" t="str">
+        <x:v>护命佩</x:v>
+      </x:c>
+      <x:c r="F229" t="str">
+        <x:v>Life Guard Pendant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230"/>
+      <x:c r="B230" t="str">
+        <x:v>Buqi.Content.Item.W8_044.Upgrade</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D230" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E230" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F230" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231"/>
+      <x:c r="B231" t="str">
+        <x:v>Buqi.Content.Item.W8_045.Name</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>药引秤</x:v>
+      </x:c>
+      <x:c r="D231" t="str">
+        <x:v>Catalyst Scale</x:v>
+      </x:c>
+      <x:c r="E231" t="str">
+        <x:v>药引秤</x:v>
+      </x:c>
+      <x:c r="F231" t="str">
+        <x:v>Catalyst Scale</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232"/>
+      <x:c r="B232" t="str">
+        <x:v>Buqi.Content.Item.W8_045.Upgrade</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D232" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E232" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F232" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233"/>
+      <x:c r="B233" t="str">
+        <x:v>Buqi.Content.Item.W8_046.Name</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>同调尺</x:v>
+      </x:c>
+      <x:c r="D233" t="str">
+        <x:v>Resonance Rule</x:v>
+      </x:c>
+      <x:c r="E233" t="str">
+        <x:v>同调尺</x:v>
+      </x:c>
+      <x:c r="F233" t="str">
+        <x:v>Resonance Rule</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234"/>
+      <x:c r="B234" t="str">
+        <x:v>Buqi.Content.Item.W8_046.Upgrade</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D234" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E234" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F234" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235"/>
+      <x:c r="B235" t="str">
+        <x:v>Buqi.Content.Item.W8_047.Name</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>行脚账</x:v>
+      </x:c>
+      <x:c r="D235" t="str">
+        <x:v>Wayfarer Ledger</x:v>
+      </x:c>
+      <x:c r="E235" t="str">
+        <x:v>行脚账</x:v>
+      </x:c>
+      <x:c r="F235" t="str">
+        <x:v>Wayfarer Ledger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236"/>
+      <x:c r="B236" t="str">
+        <x:v>Buqi.Content.Item.W8_047.Upgrade</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D236" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E236" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F236" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237"/>
+      <x:c r="B237" t="str">
+        <x:v>Buqi.Content.Item.W8_048.Name</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>镇心铃</x:v>
+      </x:c>
+      <x:c r="D237" t="str">
+        <x:v>Calming Bell</x:v>
+      </x:c>
+      <x:c r="E237" t="str">
+        <x:v>镇心铃</x:v>
+      </x:c>
+      <x:c r="F237" t="str">
+        <x:v>Calming Bell</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238"/>
+      <x:c r="B238" t="str">
+        <x:v>Buqi.Content.Item.W8_048.Upgrade</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="D238" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+      <x:c r="E238" t="str">
+        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+      </x:c>
+      <x:c r="F238" t="str">
+        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239"/>
+      <x:c r="B239" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_edge.Name</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>砺锋散人·陆铮</x:v>
+      </x:c>
+      <x:c r="D239" t="str">
+        <x:v>Edge Hermit Lu Zheng</x:v>
+      </x:c>
+      <x:c r="E239" t="str">
+        <x:v>砺锋散人·陆铮</x:v>
+      </x:c>
+      <x:c r="F239" t="str">
+        <x:v>Edge Hermit Lu Zheng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240"/>
+      <x:c r="B240" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_bastion.Name</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>叠岳炉主·石岑</x:v>
+      </x:c>
+      <x:c r="D240" t="str">
+        <x:v>Bastion Smith Shi Cen</x:v>
+      </x:c>
+      <x:c r="E240" t="str">
+        <x:v>叠岳炉主·石岑</x:v>
+      </x:c>
+      <x:c r="F240" t="str">
+        <x:v>Bastion Smith Shi Cen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241"/>
+      <x:c r="B241" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_spring.Name</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>听泉药师·蘅青</x:v>
+      </x:c>
+      <x:c r="D241" t="str">
+        <x:v>Spring Apothecary Heng Qing</x:v>
+      </x:c>
+      <x:c r="E241" t="str">
+        <x:v>听泉药师·蘅青</x:v>
+      </x:c>
+      <x:c r="F241" t="str">
+        <x:v>Spring Apothecary Heng Qing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242"/>
+      <x:c r="B242" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_measure.Name</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>量位行者·尺素</x:v>
+      </x:c>
+      <x:c r="D242" t="str">
+        <x:v>Measure Walker Chi Su</x:v>
+      </x:c>
+      <x:c r="E242" t="str">
+        <x:v>量位行者·尺素</x:v>
+      </x:c>
+      <x:c r="F242" t="str">
+        <x:v>Measure Walker Chi Su</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243"/>
+      <x:c r="B243" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_gap.Name</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>照隙道人·闻缺</x:v>
+      </x:c>
+      <x:c r="D243" t="str">
+        <x:v>Gap Seer Wen Que</x:v>
+      </x:c>
+      <x:c r="E243" t="str">
+        <x:v>照隙道人·闻缺</x:v>
+      </x:c>
+      <x:c r="F243" t="str">
+        <x:v>Gap Seer Wen Que</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244"/>
+      <x:c r="B244" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_ledger.Name</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>行筹客·金复</x:v>
+      </x:c>
+      <x:c r="D244" t="str">
+        <x:v>Ledger Guest Jin Fu</x:v>
+      </x:c>
+      <x:c r="E244" t="str">
+        <x:v>行筹客·金复</x:v>
+      </x:c>
+      <x:c r="F244" t="str">
+        <x:v>Ledger Guest Jin Fu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245"/>
+      <x:c r="B245" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_grades.Name</x:v>
+      </x:c>
+      <x:c r="C245" t="str">
+        <x:v>三品鉴主·陶然</x:v>
+      </x:c>
+      <x:c r="D245" t="str">
+        <x:v>Three-Grade Appraiser Tao Ran</x:v>
+      </x:c>
+      <x:c r="E245" t="str">
+        <x:v>三品鉴主·陶然</x:v>
+      </x:c>
+      <x:c r="F245" t="str">
+        <x:v>Three-Grade Appraiser Tao Ran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246"/>
+      <x:c r="B246" t="str">
+        <x:v>Buqi.Content.Merchant.merchant_summit.Name</x:v>
+      </x:c>
+      <x:c r="C246" t="str">
+        <x:v>收山器君·莫停云</x:v>
+      </x:c>
+      <x:c r="D246" t="str">
+        <x:v>Summit Curator Mo Tingyun</x:v>
+      </x:c>
+      <x:c r="E246" t="str">
+        <x:v>收山器君·莫停云</x:v>
+      </x:c>
+      <x:c r="F246" t="str">
+        <x:v>Summit Curator Mo Tingyun</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247"/>
+      <x:c r="B247" t="str">
+        <x:v>Buqi.Content.Trainer.trainer_wind.Name</x:v>
+      </x:c>
+      <x:c r="C247" t="str">
+        <x:v>踏风教习·简行</x:v>
+      </x:c>
+      <x:c r="D247" t="str">
+        <x:v>Windstep Instructor Jian Xing</x:v>
+      </x:c>
+      <x:c r="E247" t="str">
+        <x:v>踏风教习·简行</x:v>
+      </x:c>
+      <x:c r="F247" t="str">
+        <x:v>Windstep Instructor Jian Xing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248"/>
+      <x:c r="B248" t="str">
+        <x:v>Buqi.Content.Trainer.trainer_ward.Name</x:v>
+      </x:c>
+      <x:c r="C248" t="str">
+        <x:v>垒山教习·岳定</x:v>
+      </x:c>
+      <x:c r="D248" t="str">
+        <x:v>Mountain Ward Instructor Yue Ding</x:v>
+      </x:c>
+      <x:c r="E248" t="str">
+        <x:v>垒山教习·岳定</x:v>
+      </x:c>
+      <x:c r="F248" t="str">
+        <x:v>Mountain Ward Instructor Yue Ding</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249"/>
+      <x:c r="B249" t="str">
+        <x:v>Buqi.Content.Trainer.trainer_pulse.Name</x:v>
+      </x:c>
+      <x:c r="C249" t="str">
+        <x:v>归脉教习·苏衡</x:v>
+      </x:c>
+      <x:c r="D249" t="str">
+        <x:v>Pulse Instructor Su Heng</x:v>
+      </x:c>
+      <x:c r="E249" t="str">
+        <x:v>归脉教习·苏衡</x:v>
+      </x:c>
+      <x:c r="F249" t="str">
+        <x:v>Pulse Instructor Su Heng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250"/>
+      <x:c r="B250" t="str">
+        <x:v>Buqi.Content.Trainer.trainer_craft.Name</x:v>
+      </x:c>
+      <x:c r="C250" t="str">
+        <x:v>百工教习·鲁知微</x:v>
+      </x:c>
+      <x:c r="D250" t="str">
+        <x:v>Hundred Crafts Instructor Lu Zhiwei</x:v>
+      </x:c>
+      <x:c r="E250" t="str">
+        <x:v>百工教习·鲁知微</x:v>
+      </x:c>
+      <x:c r="F250" t="str">
+        <x:v>Hundred Crafts Instructor Lu Zhiwei</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251"/>
+      <x:c r="B251" t="str">
+        <x:v>Buqi.Content.Training.training_wind_01.Name</x:v>
+      </x:c>
+      <x:c r="C251" t="str">
+        <x:v>疾行诀</x:v>
+      </x:c>
+      <x:c r="D251" t="str">
+        <x:v>Fleet Circuit</x:v>
+      </x:c>
+      <x:c r="E251" t="str">
+        <x:v>疾行诀</x:v>
+      </x:c>
+      <x:c r="F251" t="str">
+        <x:v>Fleet Circuit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252"/>
+      <x:c r="B252" t="str">
+        <x:v>Buqi.Content.Training.training_wind_01.Summary</x:v>
+      </x:c>
+      <x:c r="C252" t="str">
+        <x:v>All haste-tagged items have 10% lower base cooldown today.</x:v>
+      </x:c>
+      <x:c r="D252"/>
+      <x:c r="E252" t="str">
+        <x:v>All haste-tagged items have 10% lower base cooldown today.</x:v>
+      </x:c>
+      <x:c r="F252"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253"/>
+      <x:c r="B253" t="str">
+        <x:v>Buqi.Content.Training.training_wind_02.Name</x:v>
+      </x:c>
+      <x:c r="C253" t="str">
+        <x:v>开脉风</x:v>
+      </x:c>
+      <x:c r="D253" t="str">
+        <x:v>Opening Wind</x:v>
+      </x:c>
+      <x:c r="E253" t="str">
+        <x:v>开脉风</x:v>
+      </x:c>
+      <x:c r="F253" t="str">
+        <x:v>Opening Wind</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254"/>
+      <x:c r="B254" t="str">
+        <x:v>Buqi.Content.Training.training_wind_02.Summary</x:v>
+      </x:c>
+      <x:c r="C254" t="str">
+        <x:v>Next battle starts with 1000 haste on attack items for 30 ticks.</x:v>
+      </x:c>
+      <x:c r="D254"/>
+      <x:c r="E254" t="str">
+        <x:v>Next battle starts with 1000 haste on attack items for 30 ticks.</x:v>
+      </x:c>
+      <x:c r="F254"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255"/>
+      <x:c r="B255" t="str">
+        <x:v>Buqi.Content.Training.training_wind_03.Name</x:v>
+      </x:c>
+      <x:c r="C255" t="str">
+        <x:v>邻响步</x:v>
+      </x:c>
+      <x:c r="D255" t="str">
+        <x:v>Adjacent Step</x:v>
+      </x:c>
+      <x:c r="E255" t="str">
+        <x:v>邻响步</x:v>
+      </x:c>
+      <x:c r="F255" t="str">
+        <x:v>Adjacent Step</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256"/>
+      <x:c r="B256" t="str">
+        <x:v>Buqi.Content.Training.training_wind_03.Summary</x:v>
+      </x:c>
+      <x:c r="C256" t="str">
+        <x:v>After the first adjacent trigger next battle, adjacent items gain 800 haste for 30 ticks.</x:v>
+      </x:c>
+      <x:c r="D256"/>
+      <x:c r="E256" t="str">
+        <x:v>After the first adjacent trigger next battle, adjacent items gain 800 haste for 30 ticks.</x:v>
+      </x:c>
+      <x:c r="F256"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257"/>
+      <x:c r="B257" t="str">
+        <x:v>Buqi.Content.Training.training_ward_01.Name</x:v>
+      </x:c>
+      <x:c r="C257" t="str">
+        <x:v>垒息</x:v>
+      </x:c>
+      <x:c r="D257" t="str">
+        <x:v>Raised Ward</x:v>
+      </x:c>
+      <x:c r="E257" t="str">
+        <x:v>垒息</x:v>
+      </x:c>
+      <x:c r="F257" t="str">
+        <x:v>Raised Ward</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258"/>
+      <x:c r="B258" t="str">
+        <x:v>Buqi.Content.Training.training_ward_01.Summary</x:v>
+      </x:c>
+      <x:c r="C258" t="str">
+        <x:v>Gain 6 buffer at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="D258"/>
+      <x:c r="E258" t="str">
+        <x:v>Gain 6 buffer at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="F258"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259"/>
+      <x:c r="B259" t="str">
+        <x:v>Buqi.Content.Training.training_ward_02.Name</x:v>
+      </x:c>
+      <x:c r="C259" t="str">
+        <x:v>守势</x:v>
+      </x:c>
+      <x:c r="D259" t="str">
+        <x:v>Holding Form</x:v>
+      </x:c>
+      <x:c r="E259" t="str">
+        <x:v>守势</x:v>
+      </x:c>
+      <x:c r="F259" t="str">
+        <x:v>Holding Form</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260"/>
+      <x:c r="B260" t="str">
+        <x:v>Buqi.Content.Training.training_ward_02.Summary</x:v>
+      </x:c>
+      <x:c r="C260" t="str">
+        <x:v>Buffer gained is increased by 15% today.</x:v>
+      </x:c>
+      <x:c r="D260"/>
+      <x:c r="E260" t="str">
+        <x:v>Buffer gained is increased by 15% today.</x:v>
+      </x:c>
+      <x:c r="F260"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261"/>
+      <x:c r="B261" t="str">
+        <x:v>Buqi.Content.Training.training_ward_03.Name</x:v>
+      </x:c>
+      <x:c r="C261" t="str">
+        <x:v>定岳</x:v>
+      </x:c>
+      <x:c r="D261" t="str">
+        <x:v>Mountain Poise</x:v>
+      </x:c>
+      <x:c r="E261" t="str">
+        <x:v>定岳</x:v>
+      </x:c>
+      <x:c r="F261" t="str">
+        <x:v>Mountain Poise</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262"/>
+      <x:c r="B262" t="str">
+        <x:v>Buqi.Content.Training.training_ward_03.Summary</x:v>
+      </x:c>
+      <x:c r="C262" t="str">
+        <x:v>Gain 8 buffer when first interfered with next battle.</x:v>
+      </x:c>
+      <x:c r="D262"/>
+      <x:c r="E262" t="str">
+        <x:v>Gain 8 buffer when first interfered with next battle.</x:v>
+      </x:c>
+      <x:c r="F262"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263"/>
+      <x:c r="B263" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_01.Name</x:v>
+      </x:c>
+      <x:c r="C263" t="str">
+        <x:v>回气</x:v>
+      </x:c>
+      <x:c r="D263" t="str">
+        <x:v>Returning Breath</x:v>
+      </x:c>
+      <x:c r="E263" t="str">
+        <x:v>回气</x:v>
+      </x:c>
+      <x:c r="F263" t="str">
+        <x:v>Returning Breath</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264"/>
+      <x:c r="B264" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_01.Summary</x:v>
+      </x:c>
+      <x:c r="C264" t="str">
+        <x:v>Restore 6 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="D264"/>
+      <x:c r="E264" t="str">
+        <x:v>Restore 6 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="F264"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265"/>
+      <x:c r="B265" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_02.Name</x:v>
+      </x:c>
+      <x:c r="C265" t="str">
+        <x:v>续脉</x:v>
+      </x:c>
+      <x:c r="D265" t="str">
+        <x:v>Sustained Pulse</x:v>
+      </x:c>
+      <x:c r="E265" t="str">
+        <x:v>续脉</x:v>
+      </x:c>
+      <x:c r="F265" t="str">
+        <x:v>Sustained Pulse</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266"/>
+      <x:c r="B266" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_02.Summary</x:v>
+      </x:c>
+      <x:c r="C266" t="str">
+        <x:v>Effective healing is increased by 15% today.</x:v>
+      </x:c>
+      <x:c r="D266"/>
+      <x:c r="E266" t="str">
+        <x:v>Effective healing is increased by 15% today.</x:v>
+      </x:c>
+      <x:c r="F266"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267"/>
+      <x:c r="B267" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_03.Name</x:v>
+      </x:c>
+      <x:c r="C267" t="str">
+        <x:v>长息</x:v>
+      </x:c>
+      <x:c r="D267" t="str">
+        <x:v>Long Breath</x:v>
+      </x:c>
+      <x:c r="E267" t="str">
+        <x:v>长息</x:v>
+      </x:c>
+      <x:c r="F267" t="str">
+        <x:v>Long Breath</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268"/>
+      <x:c r="B268" t="str">
+        <x:v>Buqi.Content.Training.training_pulse_03.Summary</x:v>
+      </x:c>
+      <x:c r="C268" t="str">
+        <x:v>Regen effects last 20 ticks longer next battle.</x:v>
+      </x:c>
+      <x:c r="D268"/>
+      <x:c r="E268" t="str">
+        <x:v>Regen effects last 20 ticks longer next battle.</x:v>
+      </x:c>
+      <x:c r="F268"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269"/>
+      <x:c r="B269" t="str">
+        <x:v>Buqi.Content.Training.training_craft_01.Name</x:v>
+      </x:c>
+      <x:c r="C269" t="str">
+        <x:v>省材</x:v>
+      </x:c>
+      <x:c r="D269" t="str">
+        <x:v>Frugal Upgrade</x:v>
+      </x:c>
+      <x:c r="E269" t="str">
+        <x:v>省材</x:v>
+      </x:c>
+      <x:c r="F269" t="str">
+        <x:v>Frugal Upgrade</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270"/>
+      <x:c r="B270" t="str">
+        <x:v>Buqi.Content.Training.training_craft_01.Summary</x:v>
+      </x:c>
+      <x:c r="C270" t="str">
+        <x:v>The first upgrade today costs 1 less coin, minimum 1.</x:v>
+      </x:c>
+      <x:c r="D270"/>
+      <x:c r="E270" t="str">
+        <x:v>The first upgrade today costs 1 less coin, minimum 1.</x:v>
+      </x:c>
+      <x:c r="F270"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271"/>
+      <x:c r="B271" t="str">
+        <x:v>Buqi.Content.Training.training_craft_02.Name</x:v>
+      </x:c>
+      <x:c r="C271" t="str">
+        <x:v>净炉</x:v>
+      </x:c>
+      <x:c r="D271" t="str">
+        <x:v>Clear Furnace</x:v>
+      </x:c>
+      <x:c r="E271" t="str">
+        <x:v>净炉</x:v>
+      </x:c>
+      <x:c r="F271" t="str">
+        <x:v>Clear Furnace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272"/>
+      <x:c r="B272" t="str">
+        <x:v>Buqi.Content.Training.training_craft_02.Summary</x:v>
+      </x:c>
+      <x:c r="C272" t="str">
+        <x:v>The first refinement today costs 1 less coin, minimum 1.</x:v>
+      </x:c>
+      <x:c r="D272"/>
+      <x:c r="E272" t="str">
+        <x:v>The first refinement today costs 1 less coin, minimum 1.</x:v>
+      </x:c>
+      <x:c r="F272"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273"/>
+      <x:c r="B273" t="str">
+        <x:v>Buqi.Content.Training.training_craft_03.Name</x:v>
+      </x:c>
+      <x:c r="C273" t="str">
+        <x:v>识货</x:v>
+      </x:c>
+      <x:c r="D273" t="str">
+        <x:v>Keen Appraisal</x:v>
+      </x:c>
+      <x:c r="E273" t="str">
+        <x:v>识货</x:v>
+      </x:c>
+      <x:c r="F273" t="str">
+        <x:v>Keen Appraisal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274"/>
+      <x:c r="B274" t="str">
+        <x:v>Buqi.Content.Training.training_craft_03.Summary</x:v>
+      </x:c>
+      <x:c r="C274" t="str">
+        <x:v>Gain one free shop refresh today.</x:v>
+      </x:c>
+      <x:c r="D274"/>
+      <x:c r="E274" t="str">
+        <x:v>Gain one free shop refresh today.</x:v>
+      </x:c>
+      <x:c r="F274"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275"/>
+      <x:c r="B275" t="str">
+        <x:v>Buqi.Content.Event.event_trial_stele.Name</x:v>
+      </x:c>
+      <x:c r="C275" t="str">
+        <x:v>试锋碑</x:v>
+      </x:c>
+      <x:c r="D275" t="str">
+        <x:v>Edge-Trial Stele</x:v>
+      </x:c>
+      <x:c r="E275" t="str">
+        <x:v>试锋碑</x:v>
+      </x:c>
+      <x:c r="F275" t="str">
+        <x:v>Edge-Trial Stele</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276"/>
+      <x:c r="B276" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_read.Name</x:v>
+      </x:c>
+      <x:c r="C276" t="str">
+        <x:v>照刻试锋</x:v>
+      </x:c>
+      <x:c r="D276" t="str">
+        <x:v>Trace the Marks</x:v>
+      </x:c>
+      <x:c r="E276" t="str">
+        <x:v>照刻试锋</x:v>
+      </x:c>
+      <x:c r="F276" t="str">
+        <x:v>Trace the Marks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277"/>
+      <x:c r="B277" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_read.Summary</x:v>
+      </x:c>
+      <x:c r="C277" t="str">
+        <x:v>支付 1 灵石，从攻击子池获得一件普通小型器物。</x:v>
+      </x:c>
+      <x:c r="D277" t="str">
+        <x:v>Pay 1 coin to gain a Normal small item from the attack pool.</x:v>
+      </x:c>
+      <x:c r="E277" t="str">
+        <x:v>支付 1 灵石，从攻击子池获得一件普通小型器物。</x:v>
+      </x:c>
+      <x:c r="F277" t="str">
+        <x:v>Pay 1 coin to gain a Normal small item from the attack pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278"/>
+      <x:c r="B278" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Name</x:v>
+      </x:c>
+      <x:c r="C278" t="str">
+        <x:v>以盾拓印</x:v>
+      </x:c>
+      <x:c r="D278" t="str">
+        <x:v>Take a Ward Rubbing</x:v>
+      </x:c>
+      <x:c r="E278" t="str">
+        <x:v>以盾拓印</x:v>
+      </x:c>
+      <x:c r="F278" t="str">
+        <x:v>Take a Ward Rubbing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279"/>
+      <x:c r="B279" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Summary</x:v>
+      </x:c>
+      <x:c r="C279" t="str">
+        <x:v>下一战开场获得 6 点护体。</x:v>
+      </x:c>
+      <x:c r="D279" t="str">
+        <x:v>Gain 6 opening buffer next battle.</x:v>
+      </x:c>
+      <x:c r="E279" t="str">
+        <x:v>下一战开场获得 6 点护体。</x:v>
+      </x:c>
+      <x:c r="F279" t="str">
+        <x:v>Gain 6 opening buffer next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280"/>
+      <x:c r="B280" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Name</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>记下碑序</x:v>
+      </x:c>
+      <x:c r="D280" t="str">
+        <x:v>Record the Sequence</x:v>
+      </x:c>
+      <x:c r="E280" t="str">
+        <x:v>记下碑序</x:v>
+      </x:c>
+      <x:c r="F280" t="str">
+        <x:v>Record the Sequence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281"/>
+      <x:c r="B281" t="str">
+        <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Summary</x:v>
+      </x:c>
+      <x:c r="C281" t="str">
+        <x:v>获得 1 灵石。</x:v>
+      </x:c>
+      <x:c r="D281" t="str">
+        <x:v>Gain 1 coin.</x:v>
+      </x:c>
+      <x:c r="E281" t="str">
+        <x:v>获得 1 灵石。</x:v>
+      </x:c>
+      <x:c r="F281" t="str">
+        <x:v>Gain 1 coin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282"/>
+      <x:c r="B282" t="str">
+        <x:v>Buqi.Content.Event.event_herb_stall.Name</x:v>
+      </x:c>
+      <x:c r="C282" t="str">
+        <x:v>旧城药摊</x:v>
+      </x:c>
+      <x:c r="D282" t="str">
+        <x:v>Old City Herb Stall</x:v>
+      </x:c>
+      <x:c r="E282" t="str">
+        <x:v>旧城药摊</x:v>
+      </x:c>
+      <x:c r="F282" t="str">
+        <x:v>Old City Herb Stall</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283"/>
+      <x:c r="B283" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_dose.Name</x:v>
+      </x:c>
+      <x:c r="C283" t="str">
+        <x:v>买一剂</x:v>
+      </x:c>
+      <x:c r="D283" t="str">
+        <x:v>Buy a Dose</x:v>
+      </x:c>
+      <x:c r="E283" t="str">
+        <x:v>买一剂</x:v>
+      </x:c>
+      <x:c r="F283" t="str">
+        <x:v>Buy a Dose</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284"/>
+      <x:c r="B284" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_dose.Summary</x:v>
+      </x:c>
+      <x:c r="C284" t="str">
+        <x:v>下一战开场恢复 8 点生命。</x:v>
+      </x:c>
+      <x:c r="D284" t="str">
+        <x:v>Restore 8 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="E284" t="str">
+        <x:v>下一战开场恢复 8 点生命。</x:v>
+      </x:c>
+      <x:c r="F284" t="str">
+        <x:v>Restore 8 life at the start of the next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285"/>
+      <x:c r="B285" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Name</x:v>
+      </x:c>
+      <x:c r="C285" t="str">
+        <x:v>换取药种</x:v>
+      </x:c>
+      <x:c r="D285" t="str">
+        <x:v>Trade for Seeds</x:v>
+      </x:c>
+      <x:c r="E285" t="str">
+        <x:v>换取药种</x:v>
+      </x:c>
+      <x:c r="F285" t="str">
+        <x:v>Trade for Seeds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286"/>
+      <x:c r="B286" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Summary</x:v>
+      </x:c>
+      <x:c r="C286" t="str">
+        <x:v>支付 1 灵石，从恢复子池获得一件普通小型器物。</x:v>
+      </x:c>
+      <x:c r="D286" t="str">
+        <x:v>Pay 1 coin to gain a Normal small item from the sustain pool.</x:v>
+      </x:c>
+      <x:c r="E286" t="str">
+        <x:v>支付 1 灵石，从恢复子池获得一件普通小型器物。</x:v>
+      </x:c>
+      <x:c r="F286" t="str">
+        <x:v>Pay 1 coin to gain a Normal small item from the sustain pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287"/>
+      <x:c r="B287" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_work.Name</x:v>
+      </x:c>
+      <x:c r="C287" t="str">
+        <x:v>帮忙理药</x:v>
+      </x:c>
+      <x:c r="D287" t="str">
+        <x:v>Sort the Herbs</x:v>
+      </x:c>
+      <x:c r="E287" t="str">
+        <x:v>帮忙理药</x:v>
+      </x:c>
+      <x:c r="F287" t="str">
+        <x:v>Sort the Herbs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288"/>
+      <x:c r="B288" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_stall_work.Summary</x:v>
+      </x:c>
+      <x:c r="C288" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="D288" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+      <x:c r="E288" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="F288" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289"/>
+      <x:c r="B289" t="str">
+        <x:v>Buqi.Content.Event.event_broken_armor.Name</x:v>
+      </x:c>
+      <x:c r="C289" t="str">
+        <x:v>山门残甲</x:v>
+      </x:c>
+      <x:c r="D289" t="str">
+        <x:v>Gatehouse Relic Armor</x:v>
+      </x:c>
+      <x:c r="E289" t="str">
+        <x:v>山门残甲</x:v>
+      </x:c>
+      <x:c r="F289" t="str">
+        <x:v>Gatehouse Relic Armor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290"/>
+      <x:c r="B290" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Name</x:v>
+      </x:c>
+      <x:c r="C290" t="str">
+        <x:v>补上甲片</x:v>
+      </x:c>
+      <x:c r="D290" t="str">
+        <x:v>Fit the Plate</x:v>
+      </x:c>
+      <x:c r="E290" t="str">
+        <x:v>补上甲片</x:v>
+      </x:c>
+      <x:c r="F290" t="str">
+        <x:v>Fit the Plate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291"/>
+      <x:c r="B291" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Summary</x:v>
+      </x:c>
+      <x:c r="C291" t="str">
+        <x:v>支付 1 灵石，将一件普通护体器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="D291" t="str">
+        <x:v>Pay 1 coin to upgrade a Normal shield item to Improved.</x:v>
+      </x:c>
+      <x:c r="E291" t="str">
+        <x:v>支付 1 灵石，将一件普通护体器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="F291" t="str">
+        <x:v>Pay 1 coin to upgrade a Normal shield item to Improved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292"/>
+      <x:c r="B292" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Name</x:v>
+      </x:c>
+      <x:c r="C292" t="str">
+        <x:v>拆取护片</x:v>
+      </x:c>
+      <x:c r="D292" t="str">
+        <x:v>Salvage a Ward Plate</x:v>
+      </x:c>
+      <x:c r="E292" t="str">
+        <x:v>拆取护片</x:v>
+      </x:c>
+      <x:c r="F292" t="str">
+        <x:v>Salvage a Ward Plate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293"/>
+      <x:c r="B293" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Summary</x:v>
+      </x:c>
+      <x:c r="C293" t="str">
+        <x:v>带 1 点失衡进入下一战，获得一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="D293" t="str">
+        <x:v>Enter the next battle with 1 noise debt and gain a Normal shield item.</x:v>
+      </x:c>
+      <x:c r="E293" t="str">
+        <x:v>带 1 点失衡进入下一战，获得一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="F293" t="str">
+        <x:v>Enter the next battle with 1 noise debt and gain a Normal shield item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294"/>
+      <x:c r="B294" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Name</x:v>
+      </x:c>
+      <x:c r="C294" t="str">
+        <x:v>量下裂口</x:v>
+      </x:c>
+      <x:c r="D294" t="str">
+        <x:v>Measure the Crack</x:v>
+      </x:c>
+      <x:c r="E294" t="str">
+        <x:v>量下裂口</x:v>
+      </x:c>
+      <x:c r="F294" t="str">
+        <x:v>Measure the Crack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295"/>
+      <x:c r="B295" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Summary</x:v>
+      </x:c>
+      <x:c r="C295" t="str">
+        <x:v>本日下一件护体器物少花 1 灵石。</x:v>
+      </x:c>
+      <x:c r="D295" t="str">
+        <x:v>The next shield item bought today costs 1 less coin.</x:v>
+      </x:c>
+      <x:c r="E295" t="str">
+        <x:v>本日下一件护体器物少花 1 灵石。</x:v>
+      </x:c>
+      <x:c r="F295" t="str">
+        <x:v>The next shield item bought today costs 1 less coin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296"/>
+      <x:c r="B296" t="str">
+        <x:v>Buqi.Content.Event.event_cloud_peddler.Name</x:v>
+      </x:c>
+      <x:c r="C296" t="str">
+        <x:v>云脚行商</x:v>
+      </x:c>
+      <x:c r="D296" t="str">
+        <x:v>Cloudstep Peddler</x:v>
+      </x:c>
+      <x:c r="E296" t="str">
+        <x:v>云脚行商</x:v>
+      </x:c>
+      <x:c r="F296" t="str">
+        <x:v>Cloudstep Peddler</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297"/>
+      <x:c r="B297" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Name</x:v>
+      </x:c>
+      <x:c r="C297" t="str">
+        <x:v>买下杂包</x:v>
+      </x:c>
+      <x:c r="D297" t="str">
+        <x:v>Buy the Mixed Bundle</x:v>
+      </x:c>
+      <x:c r="E297" t="str">
+        <x:v>买下杂包</x:v>
+      </x:c>
+      <x:c r="F297" t="str">
+        <x:v>Buy the Mixed Bundle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298"/>
+      <x:c r="B298" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Summary</x:v>
+      </x:c>
+      <x:c r="C298" t="str">
+        <x:v>获得一件普通桥接器物。</x:v>
+      </x:c>
+      <x:c r="D298" t="str">
+        <x:v>Gain a Normal bridge item.</x:v>
+      </x:c>
+      <x:c r="E298" t="str">
+        <x:v>获得一件普通桥接器物。</x:v>
+      </x:c>
+      <x:c r="F298" t="str">
+        <x:v>Gain a Normal bridge item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299"/>
+      <x:c r="B299" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_map.Name</x:v>
+      </x:c>
+      <x:c r="C299" t="str">
+        <x:v>买路线图</x:v>
+      </x:c>
+      <x:c r="D299" t="str">
+        <x:v>Buy the Route Map</x:v>
+      </x:c>
+      <x:c r="E299" t="str">
+        <x:v>买路线图</x:v>
+      </x:c>
+      <x:c r="F299" t="str">
+        <x:v>Buy the Route Map</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300"/>
+      <x:c r="B300" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_map.Summary</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="D300" t="str">
+        <x:v>Gain one free shop refresh today.</x:v>
+      </x:c>
+      <x:c r="E300" t="str">
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="F300" t="str">
+        <x:v>Gain one free shop refresh today.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301"/>
+      <x:c r="B301" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Name</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>替他叫卖</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>Hawk His Wares</x:v>
+      </x:c>
+      <x:c r="E301" t="str">
+        <x:v>替他叫卖</x:v>
+      </x:c>
+      <x:c r="F301" t="str">
+        <x:v>Hawk His Wares</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302"/>
+      <x:c r="B302" t="str">
+        <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Summary</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="D302" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+      <x:c r="E302" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="F302" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303"/>
+      <x:c r="B303" t="str">
+        <x:v>Buqi.Content.Event.event_borrowed_flame.Name</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>借火炼器</x:v>
+      </x:c>
+      <x:c r="D303" t="str">
+        <x:v>Borrowed Flame</x:v>
+      </x:c>
+      <x:c r="E303" t="str">
+        <x:v>借火炼器</x:v>
+      </x:c>
+      <x:c r="F303" t="str">
+        <x:v>Borrowed Flame</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304"/>
+      <x:c r="B304" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Name</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>当场淬火</x:v>
+      </x:c>
+      <x:c r="D304" t="str">
+        <x:v>Temper It Now</x:v>
+      </x:c>
+      <x:c r="E304" t="str">
+        <x:v>当场淬火</x:v>
+      </x:c>
+      <x:c r="F304" t="str">
+        <x:v>Temper It Now</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305"/>
+      <x:c r="B305" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Summary</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>支付 2 灵石，将一件普通器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="D305" t="str">
+        <x:v>Pay 2 coins to upgrade one Normal item to Improved.</x:v>
+      </x:c>
+      <x:c r="E305" t="str">
+        <x:v>支付 2 灵石，将一件普通器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="F305" t="str">
+        <x:v>Pay 2 coins to upgrade one Normal item to Improved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306"/>
+      <x:c r="B306" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Name</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>借走火种</x:v>
+      </x:c>
+      <x:c r="D306" t="str">
+        <x:v>Carry the Ember</x:v>
+      </x:c>
+      <x:c r="E306" t="str">
+        <x:v>借走火种</x:v>
+      </x:c>
+      <x:c r="F306" t="str">
+        <x:v>Carry the Ember</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307"/>
+      <x:c r="B307" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Summary</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>未来两日首次升级少花 2 灵石；下一战增加 2 点失衡。</x:v>
+      </x:c>
+      <x:c r="D307" t="str">
+        <x:v>The first upgrade within two days costs 2 less; next battle starts with 2 noise debt.</x:v>
+      </x:c>
+      <x:c r="E307" t="str">
+        <x:v>未来两日首次升级少花 2 灵石；下一战增加 2 点失衡。</x:v>
+      </x:c>
+      <x:c r="F307" t="str">
+        <x:v>The first upgrade within two days costs 2 less; next battle starts with 2 noise debt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308"/>
+      <x:c r="B308" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Name</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>转卖余炭</x:v>
+      </x:c>
+      <x:c r="D308" t="str">
+        <x:v>Sell the Coals</x:v>
+      </x:c>
+      <x:c r="E308" t="str">
+        <x:v>转卖余炭</x:v>
+      </x:c>
+      <x:c r="F308" t="str">
+        <x:v>Sell the Coals</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309"/>
+      <x:c r="B309" t="str">
+        <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Summary</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="D309" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+      <x:c r="E309" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="F309" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310"/>
+      <x:c r="B310" t="str">
+        <x:v>Buqi.Content.Event.event_broken_mechanism.Name</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>断弦机括</x:v>
+      </x:c>
+      <x:c r="D310" t="str">
+        <x:v>Severed Mechanism</x:v>
+      </x:c>
+      <x:c r="E310" t="str">
+        <x:v>断弦机括</x:v>
+      </x:c>
+      <x:c r="F310" t="str">
+        <x:v>Severed Mechanism</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311"/>
+      <x:c r="B311" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Name</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>接回弦线</x:v>
+      </x:c>
+      <x:c r="D311" t="str">
+        <x:v>Reconnect the Cord</x:v>
+      </x:c>
+      <x:c r="E311" t="str">
+        <x:v>接回弦线</x:v>
+      </x:c>
+      <x:c r="F311" t="str">
+        <x:v>Reconnect the Cord</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312"/>
+      <x:c r="B312" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Summary</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>支付 1 灵石，将一件普通桥接器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="D312" t="str">
+        <x:v>Pay 1 coin to upgrade a Normal bridge item to Improved.</x:v>
+      </x:c>
+      <x:c r="E312" t="str">
+        <x:v>支付 1 灵石，将一件普通桥接器物提升为改良。</x:v>
+      </x:c>
+      <x:c r="F312" t="str">
+        <x:v>Pay 1 coin to upgrade a Normal bridge item to Improved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313"/>
+      <x:c r="B313" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Name</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>拆走转轴</x:v>
+      </x:c>
+      <x:c r="D313" t="str">
+        <x:v>Take the Pivot</x:v>
+      </x:c>
+      <x:c r="E313" t="str">
+        <x:v>拆走转轴</x:v>
+      </x:c>
+      <x:c r="F313" t="str">
+        <x:v>Take the Pivot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314"/>
+      <x:c r="B314" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Summary</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>获得一件普通桥接器物。</x:v>
+      </x:c>
+      <x:c r="D314" t="str">
+        <x:v>Gain a Normal bridge item.</x:v>
+      </x:c>
+      <x:c r="E314" t="str">
+        <x:v>获得一件普通桥接器物。</x:v>
+      </x:c>
+      <x:c r="F314" t="str">
+        <x:v>Gain a Normal bridge item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315"/>
+      <x:c r="B315" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Name</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>空转试机</x:v>
+      </x:c>
+      <x:c r="D315" t="str">
+        <x:v>Dry-Run the Device</x:v>
+      </x:c>
+      <x:c r="E315" t="str">
+        <x:v>空转试机</x:v>
+      </x:c>
+      <x:c r="F315" t="str">
+        <x:v>Dry-Run the Device</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316"/>
+      <x:c r="B316" t="str">
+        <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Summary</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>下一战增加 1 点失衡；相邻器物开场加速 800，持续 30 tick。</x:v>
+      </x:c>
+      <x:c r="D316" t="str">
+        <x:v>Next battle starts with 1 noise debt; adjacent items gain 800 haste for 30 ticks.</x:v>
+      </x:c>
+      <x:c r="E316" t="str">
+        <x:v>下一战增加 1 点失衡；相邻器物开场加速 800，持续 30 tick。</x:v>
+      </x:c>
+      <x:c r="F316" t="str">
+        <x:v>Next battle starts with 1 noise debt; adjacent items gain 800 haste for 30 ticks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317"/>
+      <x:c r="B317" t="str">
+        <x:v>Buqi.Content.Event.event_nameless_ledger.Name</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>无名账册</x:v>
+      </x:c>
+      <x:c r="D317" t="str">
+        <x:v>Nameless Ledger</x:v>
+      </x:c>
+      <x:c r="E317" t="str">
+        <x:v>无名账册</x:v>
+      </x:c>
+      <x:c r="F317" t="str">
+        <x:v>Nameless Ledger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318"/>
+      <x:c r="B318" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Name</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>记一笔赊账</x:v>
+      </x:c>
+      <x:c r="D318" t="str">
+        <x:v>Open a Credit Line</x:v>
+      </x:c>
+      <x:c r="E318" t="str">
+        <x:v>记一笔赊账</x:v>
+      </x:c>
+      <x:c r="F318" t="str">
+        <x:v>Open a Credit Line</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319"/>
+      <x:c r="B319" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Summary</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>获得 4 灵石；两日后账主回访。</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>Gain 4 coins; the ledger keeper returns in two days.</x:v>
+      </x:c>
+      <x:c r="E319" t="str">
+        <x:v>获得 4 灵石；两日后账主回访。</x:v>
+      </x:c>
+      <x:c r="F319" t="str">
+        <x:v>Gain 4 coins; the ledger keeper returns in two days.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320"/>
+      <x:c r="B320" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_audit.Name</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>替它清账</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>Audit the Ledger</x:v>
+      </x:c>
+      <x:c r="E320" t="str">
+        <x:v>替它清账</x:v>
+      </x:c>
+      <x:c r="F320" t="str">
+        <x:v>Audit the Ledger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321"/>
+      <x:c r="B321" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_audit.Summary</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="D321" t="str">
+        <x:v>Gain one free shop refresh on each of the next two days.</x:v>
+      </x:c>
+      <x:c r="E321" t="str">
+        <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="F321" t="str">
+        <x:v>Gain one free shop refresh on each of the next two days.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322"/>
+      <x:c r="B322" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Name</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>合上账册</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>Close the Book</x:v>
+      </x:c>
+      <x:c r="E322" t="str">
+        <x:v>合上账册</x:v>
+      </x:c>
+      <x:c r="F322" t="str">
+        <x:v>Close the Book</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323"/>
+      <x:c r="B323" t="str">
+        <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Summary</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>获得 1 灵石。</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>Gain 1 coin.</x:v>
+      </x:c>
+      <x:c r="E323" t="str">
+        <x:v>获得 1 灵石。</x:v>
+      </x:c>
+      <x:c r="F323" t="str">
+        <x:v>Gain 1 coin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324">
+      <x:c r="A324"/>
+      <x:c r="B324" t="str">
+        <x:v>Buqi.Content.Event.event_rain_umbrella.Name</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>雨夜借伞</x:v>
+      </x:c>
+      <x:c r="D324" t="str">
+        <x:v>Umbrella in the Rain</x:v>
+      </x:c>
+      <x:c r="E324" t="str">
+        <x:v>雨夜借伞</x:v>
+      </x:c>
+      <x:c r="F324" t="str">
+        <x:v>Umbrella in the Rain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325"/>
+      <x:c r="B325" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Name</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>借伞赶路</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>Borrow the Umbrella</x:v>
+      </x:c>
+      <x:c r="E325" t="str">
+        <x:v>借伞赶路</x:v>
+      </x:c>
+      <x:c r="F325" t="str">
+        <x:v>Borrow the Umbrella</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326"/>
+      <x:c r="B326" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Summary</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>下一战开场获得 8 点护体；两日后归伞人回访。</x:v>
+      </x:c>
+      <x:c r="D326" t="str">
+        <x:v>Gain 8 opening buffer next battle; the owner returns in two days.</x:v>
+      </x:c>
+      <x:c r="E326" t="str">
+        <x:v>下一战开场获得 8 点护体；两日后归伞人回访。</x:v>
+      </x:c>
+      <x:c r="F326" t="str">
+        <x:v>Gain 8 opening buffer next battle; the owner returns in two days.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327"/>
+      <x:c r="B327" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Name</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>买下旧伞</x:v>
+      </x:c>
+      <x:c r="D327" t="str">
+        <x:v>Buy the Old Umbrella</x:v>
+      </x:c>
+      <x:c r="E327" t="str">
+        <x:v>买下旧伞</x:v>
+      </x:c>
+      <x:c r="F327" t="str">
+        <x:v>Buy the Old Umbrella</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328"/>
+      <x:c r="B328" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Summary</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>获得一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>Gain a Normal shield item.</x:v>
+      </x:c>
+      <x:c r="E328" t="str">
+        <x:v>获得一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="F328" t="str">
+        <x:v>Gain a Normal shield item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329"/>
+      <x:c r="B329" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_wait.Name</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>檐下等雨</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>Wait Under the Eaves</x:v>
+      </x:c>
+      <x:c r="E329" t="str">
+        <x:v>檐下等雨</x:v>
+      </x:c>
+      <x:c r="F329" t="str">
+        <x:v>Wait Under the Eaves</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330"/>
+      <x:c r="B330" t="str">
+        <x:v>Buqi.Content.EventOption.event_rain_umbrella_wait.Summary</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>下一战开场恢复 5 点生命。</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>Restore 5 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="E330" t="str">
+        <x:v>下一战开场恢复 5 点生命。</x:v>
+      </x:c>
+      <x:c r="F330" t="str">
+        <x:v>Restore 5 life at the start of the next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331"/>
+      <x:c r="B331" t="str">
+        <x:v>Buqi.Content.Event.event_sword_echo.Name</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>剑痕回声</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>Echo of Sword Marks</x:v>
+      </x:c>
+      <x:c r="E331" t="str">
+        <x:v>剑痕回声</x:v>
+      </x:c>
+      <x:c r="F331" t="str">
+        <x:v>Echo of Sword Marks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332"/>
+      <x:c r="B332" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Name</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>循痕运刃</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>Follow the Cut</x:v>
+      </x:c>
+      <x:c r="E332" t="str">
+        <x:v>循痕运刃</x:v>
+      </x:c>
+      <x:c r="F332" t="str">
+        <x:v>Follow the Cut</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333"/>
+      <x:c r="B333" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Summary</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>支付 2 灵石，升级一件普通攻击器物。</x:v>
+      </x:c>
+      <x:c r="D333" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal attack item.</x:v>
+      </x:c>
+      <x:c r="E333" t="str">
+        <x:v>支付 2 灵石，升级一件普通攻击器物。</x:v>
+      </x:c>
+      <x:c r="F333" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal attack item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334"/>
+      <x:c r="B334" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Name</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>以甲受痕</x:v>
+      </x:c>
+      <x:c r="D334" t="str">
+        <x:v>Receive It on Armor</x:v>
+      </x:c>
+      <x:c r="E334" t="str">
+        <x:v>以甲受痕</x:v>
+      </x:c>
+      <x:c r="F334" t="str">
+        <x:v>Receive It on Armor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335"/>
+      <x:c r="B335" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Summary</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>下一战开场获得 10 点护体。</x:v>
+      </x:c>
+      <x:c r="D335" t="str">
+        <x:v>Gain 10 opening buffer next battle.</x:v>
+      </x:c>
+      <x:c r="E335" t="str">
+        <x:v>下一战开场获得 10 点护体。</x:v>
+      </x:c>
+      <x:c r="F335" t="str">
+        <x:v>Gain 10 opening buffer next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336"/>
+      <x:c r="B336" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Name</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>拓下剑路</x:v>
+      </x:c>
+      <x:c r="D336" t="str">
+        <x:v>Copy the Sword Path</x:v>
+      </x:c>
+      <x:c r="E336" t="str">
+        <x:v>拓下剑路</x:v>
+      </x:c>
+      <x:c r="F336" t="str">
+        <x:v>Copy the Sword Path</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337"/>
+      <x:c r="B337" t="str">
+        <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Summary</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>下一战增加 2 点失衡，获得加急精炼。</x:v>
+      </x:c>
+      <x:c r="D337" t="str">
+        <x:v>Start next battle with 2 noise debt and gain the Haste refinement.</x:v>
+      </x:c>
+      <x:c r="E337" t="str">
+        <x:v>下一战增加 2 点失衡，获得加急精炼。</x:v>
+      </x:c>
+      <x:c r="F337" t="str">
+        <x:v>Start next battle with 2 noise debt and gain the Haste refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338"/>
+      <x:c r="B338" t="str">
+        <x:v>Buqi.Content.Event.event_wall_fissure.Name</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>城墙裂隙</x:v>
+      </x:c>
+      <x:c r="D338" t="str">
+        <x:v>City Wall Fissure</x:v>
+      </x:c>
+      <x:c r="E338" t="str">
+        <x:v>城墙裂隙</x:v>
+      </x:c>
+      <x:c r="F338" t="str">
+        <x:v>City Wall Fissure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339"/>
+      <x:c r="B339" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Name</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>封住裂隙</x:v>
+      </x:c>
+      <x:c r="D339" t="str">
+        <x:v>Seal the Fissure</x:v>
+      </x:c>
+      <x:c r="E339" t="str">
+        <x:v>封住裂隙</x:v>
+      </x:c>
+      <x:c r="F339" t="str">
+        <x:v>Seal the Fissure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340"/>
+      <x:c r="B340" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Summary</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>支付 2 灵石，升级一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="D340" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal shield item.</x:v>
+      </x:c>
+      <x:c r="E340" t="str">
+        <x:v>支付 2 灵石，升级一件普通护体器物。</x:v>
+      </x:c>
+      <x:c r="F340" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal shield item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341"/>
+      <x:c r="B341" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Name</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>立临时支架</x:v>
+      </x:c>
+      <x:c r="D341" t="str">
+        <x:v>Raise a Brace</x:v>
+      </x:c>
+      <x:c r="E341" t="str">
+        <x:v>立临时支架</x:v>
+      </x:c>
+      <x:c r="F341" t="str">
+        <x:v>Raise a Brace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342"/>
+      <x:c r="B342" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Summary</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>下一战开场获得 12 点护体。</x:v>
+      </x:c>
+      <x:c r="D342" t="str">
+        <x:v>Gain 12 opening buffer next battle.</x:v>
+      </x:c>
+      <x:c r="E342" t="str">
+        <x:v>下一战开场获得 12 点护体。</x:v>
+      </x:c>
+      <x:c r="F342" t="str">
+        <x:v>Gain 12 opening buffer next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343"/>
+      <x:c r="B343" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Name</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>收走碎砖</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>Take the Fallen Bricks</x:v>
+      </x:c>
+      <x:c r="E343" t="str">
+        <x:v>收走碎砖</x:v>
+      </x:c>
+      <x:c r="F343" t="str">
+        <x:v>Take the Fallen Bricks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344"/>
+      <x:c r="B344" t="str">
+        <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Summary</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="D344" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+      <x:c r="E344" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="F344" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345"/>
+      <x:c r="B345" t="str">
+        <x:v>Buqi.Content.Event.event_herb_water.Name</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>药田争水</x:v>
+      </x:c>
+      <x:c r="D345" t="str">
+        <x:v>Water for the Herb Fields</x:v>
+      </x:c>
+      <x:c r="E345" t="str">
+        <x:v>药田争水</x:v>
+      </x:c>
+      <x:c r="F345" t="str">
+        <x:v>Water for the Herb Fields</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346"/>
+      <x:c r="B346" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_divert.Name</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>引水入田</x:v>
+      </x:c>
+      <x:c r="D346" t="str">
+        <x:v>Divert the Stream</x:v>
+      </x:c>
+      <x:c r="E346" t="str">
+        <x:v>引水入田</x:v>
+      </x:c>
+      <x:c r="F346" t="str">
+        <x:v>Divert the Stream</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347"/>
+      <x:c r="B347" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_divert.Summary</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>支付 2 灵石，升级一件普通恢复器物。</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal healing item.</x:v>
+      </x:c>
+      <x:c r="E347" t="str">
+        <x:v>支付 2 灵石，升级一件普通恢复器物。</x:v>
+      </x:c>
+      <x:c r="F347" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal healing item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348"/>
+      <x:c r="B348" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_share.Name</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>平分水渠</x:v>
+      </x:c>
+      <x:c r="D348" t="str">
+        <x:v>Share the Channel</x:v>
+      </x:c>
+      <x:c r="E348" t="str">
+        <x:v>平分水渠</x:v>
+      </x:c>
+      <x:c r="F348" t="str">
+        <x:v>Share the Channel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349"/>
+      <x:c r="B349" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_share.Summary</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>下一战开场恢复 10 点生命。</x:v>
+      </x:c>
+      <x:c r="D349" t="str">
+        <x:v>Restore 10 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="E349" t="str">
+        <x:v>下一战开场恢复 10 点生命。</x:v>
+      </x:c>
+      <x:c r="F349" t="str">
+        <x:v>Restore 10 life at the start of the next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350"/>
+      <x:c r="B350" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_sell.Name</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>卖出水权</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>Sell the Water Right</x:v>
+      </x:c>
+      <x:c r="E350" t="str">
+        <x:v>卖出水权</x:v>
+      </x:c>
+      <x:c r="F350" t="str">
+        <x:v>Sell the Water Right</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351"/>
+      <x:c r="B351" t="str">
+        <x:v>Buqi.Content.EventOption.event_herb_water_sell.Summary</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>失去 1 命，获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>Lose 1 life and gain 5 coins.</x:v>
+      </x:c>
+      <x:c r="E351" t="str">
+        <x:v>失去 1 命，获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="F351" t="str">
+        <x:v>Lose 1 life and gain 5 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352"/>
+      <x:c r="B352" t="str">
+        <x:v>Buqi.Content.Event.event_roving_furnace.Name</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>游炉换火</x:v>
+      </x:c>
+      <x:c r="D352" t="str">
+        <x:v>Roving Furnace Exchange</x:v>
+      </x:c>
+      <x:c r="E352" t="str">
+        <x:v>游炉换火</x:v>
+      </x:c>
+      <x:c r="F352" t="str">
+        <x:v>Roving Furnace Exchange</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353"/>
+      <x:c r="B353" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Name</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>归还火种</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>Return the Ember</x:v>
+      </x:c>
+      <x:c r="E353" t="str">
+        <x:v>归还火种</x:v>
+      </x:c>
+      <x:c r="F353" t="str">
+        <x:v>Return the Ember</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354"/>
+      <x:c r="B354" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Summary</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>支付 1 灵石归还火种，获得稳流精炼。</x:v>
+      </x:c>
+      <x:c r="D354" t="str">
+        <x:v>Pay 1 coin to return the ember and gain the Steady Flow refinement.</x:v>
+      </x:c>
+      <x:c r="E354" t="str">
+        <x:v>支付 1 灵石归还火种，获得稳流精炼。</x:v>
+      </x:c>
+      <x:c r="F354" t="str">
+        <x:v>Pay 1 coin to return the ember and gain the Steady Flow refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355"/>
+      <x:c r="B355" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Name</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>留下火种</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>Keep the Ember</x:v>
+      </x:c>
+      <x:c r="E355" t="str">
+        <x:v>留下火种</x:v>
+      </x:c>
+      <x:c r="F355" t="str">
+        <x:v>Keep the Ember</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356"/>
+      <x:c r="B356" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Summary</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>下一战增加 3 点失衡，升级一件灼烧器物。</x:v>
+      </x:c>
+      <x:c r="D356" t="str">
+        <x:v>Start next battle with 3 noise debt and upgrade one burn item.</x:v>
+      </x:c>
+      <x:c r="E356" t="str">
+        <x:v>下一战增加 3 点失衡，升级一件灼烧器物。</x:v>
+      </x:c>
+      <x:c r="F356" t="str">
+        <x:v>Start next battle with 3 noise debt and upgrade one burn item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357"/>
+      <x:c r="B357" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Name</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>换成灵石</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>Trade It Away</x:v>
+      </x:c>
+      <x:c r="E357" t="str">
+        <x:v>换成灵石</x:v>
+      </x:c>
+      <x:c r="F357" t="str">
+        <x:v>Trade It Away</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358"/>
+      <x:c r="B358" t="str">
+        <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Summary</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>获得 3 灵石并结清火种。</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>Gain 3 coins and close the ember debt.</x:v>
+      </x:c>
+      <x:c r="E358" t="str">
+        <x:v>获得 3 灵石并结清火种。</x:v>
+      </x:c>
+      <x:c r="F358" t="str">
+        <x:v>Gain 3 coins and close the ember debt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359"/>
+      <x:c r="B359" t="str">
+        <x:v>Buqi.Content.Event.event_ledger_collector.Name</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>欠账来客</x:v>
+      </x:c>
+      <x:c r="D359" t="str">
+        <x:v>The Ledger Collector</x:v>
+      </x:c>
+      <x:c r="E359" t="str">
+        <x:v>欠账来客</x:v>
+      </x:c>
+      <x:c r="F359" t="str">
+        <x:v>The Ledger Collector</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360"/>
+      <x:c r="B360" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Name</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>照数归还</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>Repay in Full</x:v>
+      </x:c>
+      <x:c r="E360" t="str">
+        <x:v>照数归还</x:v>
+      </x:c>
+      <x:c r="F360" t="str">
+        <x:v>Repay in Full</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361"/>
+      <x:c r="B361" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Summary</x:v>
+      </x:c>
+      <x:c r="C361" t="str">
+        <x:v>支付 3 灵石，本日获得 1 次免费刷新。</x:v>
+      </x:c>
+      <x:c r="D361" t="str">
+        <x:v>Pay 3 coins and gain one free refresh today.</x:v>
+      </x:c>
+      <x:c r="E361" t="str">
+        <x:v>支付 3 灵石，本日获得 1 次免费刷新。</x:v>
+      </x:c>
+      <x:c r="F361" t="str">
+        <x:v>Pay 3 coins and gain one free refresh today.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362"/>
+      <x:c r="B362" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Name</x:v>
+      </x:c>
+      <x:c r="C362" t="str">
+        <x:v>替他收账</x:v>
+      </x:c>
+      <x:c r="D362" t="str">
+        <x:v>Collect Another Debt</x:v>
+      </x:c>
+      <x:c r="E362" t="str">
+        <x:v>替他收账</x:v>
+      </x:c>
+      <x:c r="F362" t="str">
+        <x:v>Collect Another Debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363"/>
+      <x:c r="B363" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Summary</x:v>
+      </x:c>
+      <x:c r="C363" t="str">
+        <x:v>获得 1 灵石并结清账目。</x:v>
+      </x:c>
+      <x:c r="D363" t="str">
+        <x:v>Gain 1 coin and settle the account.</x:v>
+      </x:c>
+      <x:c r="E363" t="str">
+        <x:v>获得 1 灵石并结清账目。</x:v>
+      </x:c>
+      <x:c r="F363" t="str">
+        <x:v>Gain 1 coin and settle the account.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364"/>
+      <x:c r="B364" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Name</x:v>
+      </x:c>
+      <x:c r="C364" t="str">
+        <x:v>拒绝认账</x:v>
+      </x:c>
+      <x:c r="D364" t="str">
+        <x:v>Refuse the Debt</x:v>
+      </x:c>
+      <x:c r="E364" t="str">
+        <x:v>拒绝认账</x:v>
+      </x:c>
+      <x:c r="F364" t="str">
+        <x:v>Refuse the Debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365"/>
+      <x:c r="B365" t="str">
+        <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Summary</x:v>
+      </x:c>
+      <x:c r="C365" t="str">
+        <x:v>失去 1 命；下一战增加 2 点失衡。</x:v>
+      </x:c>
+      <x:c r="D365" t="str">
+        <x:v>Lose 1 life; next battle starts with 2 noise debt.</x:v>
+      </x:c>
+      <x:c r="E365" t="str">
+        <x:v>失去 1 命；下一战增加 2 点失衡。</x:v>
+      </x:c>
+      <x:c r="F365" t="str">
+        <x:v>Lose 1 life; next battle starts with 2 noise debt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366"/>
+      <x:c r="B366" t="str">
+        <x:v>Buqi.Content.Event.event_umbrella_return.Name</x:v>
+      </x:c>
+      <x:c r="C366" t="str">
+        <x:v>归伞人</x:v>
+      </x:c>
+      <x:c r="D366" t="str">
+        <x:v>The Umbrella's Owner</x:v>
+      </x:c>
+      <x:c r="E366" t="str">
+        <x:v>归伞人</x:v>
+      </x:c>
+      <x:c r="F366" t="str">
+        <x:v>The Umbrella's Owner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367"/>
+      <x:c r="B367" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Name</x:v>
+      </x:c>
+      <x:c r="C367" t="str">
+        <x:v>原样归还</x:v>
+      </x:c>
+      <x:c r="D367" t="str">
+        <x:v>Return It Intact</x:v>
+      </x:c>
+      <x:c r="E367" t="str">
+        <x:v>原样归还</x:v>
+      </x:c>
+      <x:c r="F367" t="str">
+        <x:v>Return It Intact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368"/>
+      <x:c r="B368" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Summary</x:v>
+      </x:c>
+      <x:c r="C368" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="D368" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+      <x:c r="E368" t="str">
+        <x:v>获得 2 灵石。</x:v>
+      </x:c>
+      <x:c r="F368" t="str">
+        <x:v>Gain 2 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369"/>
+      <x:c r="B369" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Name</x:v>
+      </x:c>
+      <x:c r="C369" t="str">
+        <x:v>修好再还</x:v>
+      </x:c>
+      <x:c r="D369" t="str">
+        <x:v>Repair Before Returning</x:v>
+      </x:c>
+      <x:c r="E369" t="str">
+        <x:v>修好再还</x:v>
+      </x:c>
+      <x:c r="F369" t="str">
+        <x:v>Repair Before Returning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370"/>
+      <x:c r="B370" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Summary</x:v>
+      </x:c>
+      <x:c r="C370" t="str">
+        <x:v>支付 1 灵石，获得可靠精炼。</x:v>
+      </x:c>
+      <x:c r="D370" t="str">
+        <x:v>Pay 1 coin and gain the Reliable refinement.</x:v>
+      </x:c>
+      <x:c r="E370" t="str">
+        <x:v>支付 1 灵石，获得可靠精炼。</x:v>
+      </x:c>
+      <x:c r="F370" t="str">
+        <x:v>Pay 1 coin and gain the Reliable refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371"/>
+      <x:c r="B371" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Name</x:v>
+      </x:c>
+      <x:c r="C371" t="str">
+        <x:v>留下旧伞</x:v>
+      </x:c>
+      <x:c r="D371" t="str">
+        <x:v>Keep the Umbrella</x:v>
+      </x:c>
+      <x:c r="E371" t="str">
+        <x:v>留下旧伞</x:v>
+      </x:c>
+      <x:c r="F371" t="str">
+        <x:v>Keep the Umbrella</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372"/>
+      <x:c r="B372" t="str">
+        <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Summary</x:v>
+      </x:c>
+      <x:c r="C372" t="str">
+        <x:v>失去 1 命，获得一件改良护体器物。</x:v>
+      </x:c>
+      <x:c r="D372" t="str">
+        <x:v>Lose 1 life and gain an Improved shield item.</x:v>
+      </x:c>
+      <x:c r="E372" t="str">
+        <x:v>失去 1 命，获得一件改良护体器物。</x:v>
+      </x:c>
+      <x:c r="F372" t="str">
+        <x:v>Lose 1 life and gain an Improved shield item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373"/>
+      <x:c r="B373" t="str">
+        <x:v>Buqi.Content.Event.event_headwind_array.Name</x:v>
+      </x:c>
+      <x:c r="C373" t="str">
+        <x:v>逆风试阵</x:v>
+      </x:c>
+      <x:c r="D373" t="str">
+        <x:v>Headwind Trial Array</x:v>
+      </x:c>
+      <x:c r="E373" t="str">
+        <x:v>逆风试阵</x:v>
+      </x:c>
+      <x:c r="F373" t="str">
+        <x:v>Headwind Trial Array</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374"/>
+      <x:c r="B374" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Name</x:v>
+      </x:c>
+      <x:c r="C374" t="str">
+        <x:v>正面入阵</x:v>
+      </x:c>
+      <x:c r="D374" t="str">
+        <x:v>Enter Head-On</x:v>
+      </x:c>
+      <x:c r="E374" t="str">
+        <x:v>正面入阵</x:v>
+      </x:c>
+      <x:c r="F374" t="str">
+        <x:v>Enter Head-On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375"/>
+      <x:c r="B375" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Summary</x:v>
+      </x:c>
+      <x:c r="C375" t="str">
+        <x:v>下一战增加 2 点失衡，升级一件反制器物。</x:v>
+      </x:c>
+      <x:c r="D375" t="str">
+        <x:v>Start next battle with 2 noise debt and upgrade one counter item.</x:v>
+      </x:c>
+      <x:c r="E375" t="str">
+        <x:v>下一战增加 2 点失衡，升级一件反制器物。</x:v>
+      </x:c>
+      <x:c r="F375" t="str">
+        <x:v>Start next battle with 2 noise debt and upgrade one counter item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376"/>
+      <x:c r="B376" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Name</x:v>
+      </x:c>
+      <x:c r="C376" t="str">
+        <x:v>以镇心铃定阵</x:v>
+      </x:c>
+      <x:c r="D376" t="str">
+        <x:v>Anchor with a Calming Bell</x:v>
+      </x:c>
+      <x:c r="E376" t="str">
+        <x:v>以镇心铃定阵</x:v>
+      </x:c>
+      <x:c r="F376" t="str">
+        <x:v>Anchor with a Calming Bell</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377"/>
+      <x:c r="B377" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Summary</x:v>
+      </x:c>
+      <x:c r="C377" t="str">
+        <x:v>支付 1 灵石；下一战相邻器物开场加速 1000。</x:v>
+      </x:c>
+      <x:c r="D377" t="str">
+        <x:v>Pay 1 coin; adjacent items gain 1000 opening haste next battle.</x:v>
+      </x:c>
+      <x:c r="E377" t="str">
+        <x:v>支付 1 灵石；下一战相邻器物开场加速 1000。</x:v>
+      </x:c>
+      <x:c r="F377" t="str">
+        <x:v>Pay 1 coin; adjacent items gain 1000 opening haste next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378"/>
+      <x:c r="B378" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Name</x:v>
+      </x:c>
+      <x:c r="C378" t="str">
+        <x:v>阵外观风</x:v>
+      </x:c>
+      <x:c r="D378" t="str">
+        <x:v>Study the Wind</x:v>
+      </x:c>
+      <x:c r="E378" t="str">
+        <x:v>阵外观风</x:v>
+      </x:c>
+      <x:c r="F378" t="str">
+        <x:v>Study the Wind</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379"/>
+      <x:c r="B379" t="str">
+        <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Summary</x:v>
+      </x:c>
+      <x:c r="C379" t="str">
+        <x:v>本日下一件反制器物少花 1 灵石。</x:v>
+      </x:c>
+      <x:c r="D379" t="str">
+        <x:v>The next counter item bought today costs 1 less coin.</x:v>
+      </x:c>
+      <x:c r="E379" t="str">
+        <x:v>本日下一件反制器物少花 1 灵石。</x:v>
+      </x:c>
+      <x:c r="F379" t="str">
+        <x:v>The next counter item bought today costs 1 less coin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380"/>
+      <x:c r="B380" t="str">
+        <x:v>Buqi.Content.Event.event_three_bidders.Name</x:v>
+      </x:c>
+      <x:c r="C380" t="str">
+        <x:v>三家竞价</x:v>
+      </x:c>
+      <x:c r="D380" t="str">
+        <x:v>Three Bidders</x:v>
+      </x:c>
+      <x:c r="E380" t="str">
+        <x:v>三家竞价</x:v>
+      </x:c>
+      <x:c r="F380" t="str">
+        <x:v>Three Bidders</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381"/>
+      <x:c r="B381" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Name</x:v>
+      </x:c>
+      <x:c r="C381" t="str">
+        <x:v>卖出闲器</x:v>
+      </x:c>
+      <x:c r="D381" t="str">
+        <x:v>Sell a Spare Item</x:v>
+      </x:c>
+      <x:c r="E381" t="str">
+        <x:v>卖出闲器</x:v>
+      </x:c>
+      <x:c r="F381" t="str">
+        <x:v>Sell a Spare Item</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382"/>
+      <x:c r="B382" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Summary</x:v>
+      </x:c>
+      <x:c r="C382" t="str">
+        <x:v>移除一件起手器物，获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="D382" t="str">
+        <x:v>Remove one starter item and gain 5 coins.</x:v>
+      </x:c>
+      <x:c r="E382" t="str">
+        <x:v>移除一件起手器物，获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="F382" t="str">
+        <x:v>Remove one starter item and gain 5 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383"/>
+      <x:c r="B383" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Name</x:v>
+      </x:c>
+      <x:c r="C383" t="str">
+        <x:v>压价竞买</x:v>
+      </x:c>
+      <x:c r="D383" t="str">
+        <x:v>Bid for a Bargain</x:v>
+      </x:c>
+      <x:c r="E383" t="str">
+        <x:v>压价竞买</x:v>
+      </x:c>
+      <x:c r="F383" t="str">
+        <x:v>Bid for a Bargain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384"/>
+      <x:c r="B384" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Summary</x:v>
+      </x:c>
+      <x:c r="C384" t="str">
+        <x:v>获得一件改良核心器物。</x:v>
+      </x:c>
+      <x:c r="D384" t="str">
+        <x:v>Gain an Improved core item.</x:v>
+      </x:c>
+      <x:c r="E384" t="str">
+        <x:v>获得一件改良核心器物。</x:v>
+      </x:c>
+      <x:c r="F384" t="str">
+        <x:v>Gain an Improved core item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385"/>
+      <x:c r="B385" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Name</x:v>
+      </x:c>
+      <x:c r="C385" t="str">
+        <x:v>押到第九日</x:v>
+      </x:c>
+      <x:c r="D385" t="str">
+        <x:v>Stake It to Day Nine</x:v>
+      </x:c>
+      <x:c r="E385" t="str">
+        <x:v>押到第九日</x:v>
+      </x:c>
+      <x:c r="F385" t="str">
+        <x:v>Stake It to Day Nine</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386"/>
+      <x:c r="B386" t="str">
+        <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Summary</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>支付 2 灵石，第九日按当前构筑回收。</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>Pay 2 coins for a Day Nine build-based settlement.</x:v>
+      </x:c>
+      <x:c r="E386" t="str">
+        <x:v>支付 2 灵石，第九日按当前构筑回收。</x:v>
+      </x:c>
+      <x:c r="F386" t="str">
+        <x:v>Pay 2 coins for a Day Nine build-based settlement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387"/>
+      <x:c r="B387" t="str">
+        <x:v>Buqi.Content.Event.event_heaven_gate.Name</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>天门校器</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>Heaven Gate Calibration</x:v>
+      </x:c>
+      <x:c r="E387" t="str">
+        <x:v>天门校器</x:v>
+      </x:c>
+      <x:c r="F387" t="str">
+        <x:v>Heaven Gate Calibration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388"/>
+      <x:c r="B388" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Name</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>校正攻势</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>Calibrate Offense</x:v>
+      </x:c>
+      <x:c r="E388" t="str">
+        <x:v>校正攻势</x:v>
+      </x:c>
+      <x:c r="F388" t="str">
+        <x:v>Calibrate Offense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389"/>
+      <x:c r="B389" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Summary</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>支付 4 灵石，从攻击子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the attack pool.</x:v>
+      </x:c>
+      <x:c r="E389" t="str">
+        <x:v>支付 4 灵石，从攻击子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="F389" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the attack pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390"/>
+      <x:c r="B390" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Name</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>校正节拍</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>Calibrate Tempo</x:v>
+      </x:c>
+      <x:c r="E390" t="str">
+        <x:v>校正节拍</x:v>
+      </x:c>
+      <x:c r="F390" t="str">
+        <x:v>Calibrate Tempo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391"/>
+      <x:c r="B391" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Summary</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>支付 2 灵石，获得加急精炼。</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>Pay 2 coins and gain the Haste refinement.</x:v>
+      </x:c>
+      <x:c r="E391" t="str">
+        <x:v>支付 2 灵石，获得加急精炼。</x:v>
+      </x:c>
+      <x:c r="F391" t="str">
+        <x:v>Pay 2 coins and gain the Haste refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392"/>
+      <x:c r="B392" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Name</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>留下余量</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>Keep the Margin</x:v>
+      </x:c>
+      <x:c r="E392" t="str">
+        <x:v>留下余量</x:v>
+      </x:c>
+      <x:c r="F392" t="str">
+        <x:v>Keep the Margin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393"/>
+      <x:c r="B393" t="str">
+        <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Summary</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>下一战攻击器物开场加速 1200。</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>Attack items gain 1200 opening haste next battle.</x:v>
+      </x:c>
+      <x:c r="E393" t="str">
+        <x:v>下一战攻击器物开场加速 1200。</x:v>
+      </x:c>
+      <x:c r="F393" t="str">
+        <x:v>Attack items gain 1200 opening haste next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394"/>
+      <x:c r="B394" t="str">
+        <x:v>Buqi.Content.Event.event_mountain_eye.Name</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>护山阵眼</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>Mountain Ward Eye</x:v>
+      </x:c>
+      <x:c r="E394" t="str">
+        <x:v>护山阵眼</x:v>
+      </x:c>
+      <x:c r="F394" t="str">
+        <x:v>Mountain Ward Eye</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395"/>
+      <x:c r="B395" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Name</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>封入堡垒</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>Seal It into the Bastion</x:v>
+      </x:c>
+      <x:c r="E395" t="str">
+        <x:v>封入堡垒</x:v>
+      </x:c>
+      <x:c r="F395" t="str">
+        <x:v>Seal It into the Bastion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396"/>
+      <x:c r="B396" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Summary</x:v>
+      </x:c>
+      <x:c r="C396" t="str">
+        <x:v>支付 4 灵石，从护体子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="D396" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the shield pool.</x:v>
+      </x:c>
+      <x:c r="E396" t="str">
+        <x:v>支付 4 灵石，从护体子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="F396" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the shield pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397"/>
+      <x:c r="B397" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Name</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>借阵护身</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>Borrow the Ward</x:v>
+      </x:c>
+      <x:c r="E397" t="str">
+        <x:v>借阵护身</x:v>
+      </x:c>
+      <x:c r="F397" t="str">
+        <x:v>Borrow the Ward</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398"/>
+      <x:c r="B398" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Summary</x:v>
+      </x:c>
+      <x:c r="C398" t="str">
+        <x:v>下一战开场获得 16 点护体。</x:v>
+      </x:c>
+      <x:c r="D398" t="str">
+        <x:v>Gain 16 opening buffer next battle.</x:v>
+      </x:c>
+      <x:c r="E398" t="str">
+        <x:v>下一战开场获得 16 点护体。</x:v>
+      </x:c>
+      <x:c r="F398" t="str">
+        <x:v>Gain 16 opening buffer next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399"/>
+      <x:c r="B399" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Name</x:v>
+      </x:c>
+      <x:c r="C399" t="str">
+        <x:v>取一枚阵石</x:v>
+      </x:c>
+      <x:c r="D399" t="str">
+        <x:v>Take an Array Stone</x:v>
+      </x:c>
+      <x:c r="E399" t="str">
+        <x:v>取一枚阵石</x:v>
+      </x:c>
+      <x:c r="F399" t="str">
+        <x:v>Take an Array Stone</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400"/>
+      <x:c r="B400" t="str">
+        <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Summary</x:v>
+      </x:c>
+      <x:c r="C400" t="str">
+        <x:v>下一战增加 2 点失衡，获得可靠精炼。</x:v>
+      </x:c>
+      <x:c r="D400" t="str">
+        <x:v>Start next battle with 2 noise debt and gain the Reliable refinement.</x:v>
+      </x:c>
+      <x:c r="E400" t="str">
+        <x:v>下一战增加 2 点失衡，获得可靠精炼。</x:v>
+      </x:c>
+      <x:c r="F400" t="str">
+        <x:v>Start next battle with 2 noise debt and gain the Reliable refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401"/>
+      <x:c r="B401" t="str">
+        <x:v>Buqi.Content.Event.event_herbs_return.Name</x:v>
+      </x:c>
+      <x:c r="C401" t="str">
+        <x:v>百草归元</x:v>
+      </x:c>
+      <x:c r="D401" t="str">
+        <x:v>Hundred Herbs Return</x:v>
+      </x:c>
+      <x:c r="E401" t="str">
+        <x:v>百草归元</x:v>
+      </x:c>
+      <x:c r="F401" t="str">
+        <x:v>Hundred Herbs Return</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402"/>
+      <x:c r="B402" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Name</x:v>
+      </x:c>
+      <x:c r="C402" t="str">
+        <x:v>合炼归元汤</x:v>
+      </x:c>
+      <x:c r="D402" t="str">
+        <x:v>Brew the Returning Draught</x:v>
+      </x:c>
+      <x:c r="E402" t="str">
+        <x:v>合炼归元汤</x:v>
+      </x:c>
+      <x:c r="F402" t="str">
+        <x:v>Brew the Returning Draught</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403"/>
+      <x:c r="B403" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Summary</x:v>
+      </x:c>
+      <x:c r="C403" t="str">
+        <x:v>支付 4 灵石，从恢复子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="D403" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the healing pool.</x:v>
+      </x:c>
+      <x:c r="E403" t="str">
+        <x:v>支付 4 灵石，从恢复子池获得一件定型收尾器物。</x:v>
+      </x:c>
+      <x:c r="F403" t="str">
+        <x:v>Pay 4 coins to gain a Fixed finisher from the healing pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404"/>
+      <x:c r="B404" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_share.Name</x:v>
+      </x:c>
+      <x:c r="C404" t="str">
+        <x:v>分饮药汤</x:v>
+      </x:c>
+      <x:c r="D404" t="str">
+        <x:v>Share the Draught</x:v>
+      </x:c>
+      <x:c r="E404" t="str">
+        <x:v>分饮药汤</x:v>
+      </x:c>
+      <x:c r="F404" t="str">
+        <x:v>Share the Draught</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405"/>
+      <x:c r="B405" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_share.Summary</x:v>
+      </x:c>
+      <x:c r="C405" t="str">
+        <x:v>下一战开场恢复 16 点生命。</x:v>
+      </x:c>
+      <x:c r="D405" t="str">
+        <x:v>Restore 16 life at the start of the next battle.</x:v>
+      </x:c>
+      <x:c r="E405" t="str">
+        <x:v>下一战开场恢复 16 点生命。</x:v>
+      </x:c>
+      <x:c r="F405" t="str">
+        <x:v>Restore 16 life at the start of the next battle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406"/>
+      <x:c r="B406" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Name</x:v>
+      </x:c>
+      <x:c r="C406" t="str">
+        <x:v>留下药引</x:v>
+      </x:c>
+      <x:c r="D406" t="str">
+        <x:v>Keep the Catalyst</x:v>
+      </x:c>
+      <x:c r="E406" t="str">
+        <x:v>留下药引</x:v>
+      </x:c>
+      <x:c r="F406" t="str">
+        <x:v>Keep the Catalyst</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407"/>
+      <x:c r="B407" t="str">
+        <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Summary</x:v>
+      </x:c>
+      <x:c r="C407" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="D407" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+      <x:c r="E407" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="F407" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408">
+      <x:c r="A408"/>
+      <x:c r="B408" t="str">
+        <x:v>Buqi.Content.Event.event_old_pacts.Name</x:v>
+      </x:c>
+      <x:c r="C408" t="str">
+        <x:v>旧约清算</x:v>
+      </x:c>
+      <x:c r="D408" t="str">
+        <x:v>Old Pacts Settled</x:v>
+      </x:c>
+      <x:c r="E408" t="str">
+        <x:v>旧约清算</x:v>
+      </x:c>
+      <x:c r="F408" t="str">
+        <x:v>Old Pacts Settled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409">
+      <x:c r="A409"/>
+      <x:c r="B409" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Name</x:v>
+      </x:c>
+      <x:c r="C409" t="str">
+        <x:v>清偿旧约</x:v>
+      </x:c>
+      <x:c r="D409" t="str">
+        <x:v>Settle the Pact</x:v>
+      </x:c>
+      <x:c r="E409" t="str">
+        <x:v>清偿旧约</x:v>
+      </x:c>
+      <x:c r="F409" t="str">
+        <x:v>Settle the Pact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410">
+      <x:c r="A410"/>
+      <x:c r="B410" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Summary</x:v>
+      </x:c>
+      <x:c r="C410" t="str">
+        <x:v>支付 3 灵石，清除账册与火种欠约。</x:v>
+      </x:c>
+      <x:c r="D410" t="str">
+        <x:v>Pay 3 coins to clear ledger and ember obligations.</x:v>
+      </x:c>
+      <x:c r="E410" t="str">
+        <x:v>支付 3 灵石，清除账册与火种欠约。</x:v>
+      </x:c>
+      <x:c r="F410" t="str">
+        <x:v>Pay 3 coins to clear ledger and ember obligations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411">
+      <x:c r="A411"/>
+      <x:c r="B411" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Name</x:v>
+      </x:c>
+      <x:c r="C411" t="str">
+        <x:v>带约入战</x:v>
+      </x:c>
+      <x:c r="D411" t="str">
+        <x:v>Carry the Pact</x:v>
+      </x:c>
+      <x:c r="E411" t="str">
+        <x:v>带约入战</x:v>
+      </x:c>
+      <x:c r="F411" t="str">
+        <x:v>Carry the Pact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412">
+      <x:c r="A412"/>
+      <x:c r="B412" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Summary</x:v>
+      </x:c>
+      <x:c r="C412" t="str">
+        <x:v>下一战增加 3 点失衡，获得超载精炼。</x:v>
+      </x:c>
+      <x:c r="D412" t="str">
+        <x:v>Start next battle with 3 noise debt and gain the Overload refinement.</x:v>
+      </x:c>
+      <x:c r="E412" t="str">
+        <x:v>下一战增加 3 点失衡，获得超载精炼。</x:v>
+      </x:c>
+      <x:c r="F412" t="str">
+        <x:v>Start next battle with 3 noise debt and gain the Overload refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413">
+      <x:c r="A413"/>
+      <x:c r="B413" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Name</x:v>
+      </x:c>
+      <x:c r="C413" t="str">
+        <x:v>重订条款</x:v>
+      </x:c>
+      <x:c r="D413" t="str">
+        <x:v>Rewrite the Terms</x:v>
+      </x:c>
+      <x:c r="E413" t="str">
+        <x:v>重订条款</x:v>
+      </x:c>
+      <x:c r="F413" t="str">
+        <x:v>Rewrite the Terms</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414">
+      <x:c r="A414"/>
+      <x:c r="B414" t="str">
+        <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Summary</x:v>
+      </x:c>
+      <x:c r="C414" t="str">
+        <x:v>支付 1 灵石，本日下一次购买少花 2 灵石。</x:v>
+      </x:c>
+      <x:c r="D414" t="str">
+        <x:v>Pay 1 coin; the next purchase today costs 2 less.</x:v>
+      </x:c>
+      <x:c r="E414" t="str">
+        <x:v>支付 1 灵石，本日下一次购买少花 2 灵石。</x:v>
+      </x:c>
+      <x:c r="F414" t="str">
+        <x:v>Pay 1 coin; the next purchase today costs 2 less.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415">
+      <x:c r="A415"/>
+      <x:c r="B415" t="str">
+        <x:v>Buqi.Content.Event.event_scrap_recovery.Name</x:v>
+      </x:c>
+      <x:c r="C415" t="str">
+        <x:v>回收残器</x:v>
+      </x:c>
+      <x:c r="D415" t="str">
+        <x:v>Relic Recovery</x:v>
+      </x:c>
+      <x:c r="E415" t="str">
+        <x:v>回收残器</x:v>
+      </x:c>
+      <x:c r="F415" t="str">
+        <x:v>Relic Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416">
+      <x:c r="A416"/>
+      <x:c r="B416" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Name</x:v>
+      </x:c>
+      <x:c r="C416" t="str">
+        <x:v>拆掉起手件</x:v>
+      </x:c>
+      <x:c r="D416" t="str">
+        <x:v>Strip a Starter</x:v>
+      </x:c>
+      <x:c r="E416" t="str">
+        <x:v>拆掉起手件</x:v>
+      </x:c>
+      <x:c r="F416" t="str">
+        <x:v>Strip a Starter</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417">
+      <x:c r="A417"/>
+      <x:c r="B417" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Summary</x:v>
+      </x:c>
+      <x:c r="C417" t="str">
+        <x:v>移除一件起手器物，获得 4 灵石。</x:v>
+      </x:c>
+      <x:c r="D417" t="str">
+        <x:v>Remove one starter item and gain 4 coins.</x:v>
+      </x:c>
+      <x:c r="E417" t="str">
+        <x:v>移除一件起手器物，获得 4 灵石。</x:v>
+      </x:c>
+      <x:c r="F417" t="str">
+        <x:v>Remove one starter item and gain 4 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418">
+      <x:c r="A418"/>
+      <x:c r="B418" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Name</x:v>
+      </x:c>
+      <x:c r="C418" t="str">
+        <x:v>以旧换新</x:v>
+      </x:c>
+      <x:c r="D418" t="str">
+        <x:v>Trade Old for New</x:v>
+      </x:c>
+      <x:c r="E418" t="str">
+        <x:v>以旧换新</x:v>
+      </x:c>
+      <x:c r="F418" t="str">
+        <x:v>Trade Old for New</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419">
+      <x:c r="A419"/>
+      <x:c r="B419" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Summary</x:v>
+      </x:c>
+      <x:c r="C419" t="str">
+        <x:v>移除一件转向器物，获得一件改良反制器物。</x:v>
+      </x:c>
+      <x:c r="D419" t="str">
+        <x:v>Remove one pivot item and gain an Improved counter item.</x:v>
+      </x:c>
+      <x:c r="E419" t="str">
+        <x:v>移除一件转向器物，获得一件改良反制器物。</x:v>
+      </x:c>
+      <x:c r="F419" t="str">
+        <x:v>Remove one pivot item and gain an Improved counter item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420">
+      <x:c r="A420"/>
+      <x:c r="B420" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Name</x:v>
+      </x:c>
+      <x:c r="C420" t="str">
+        <x:v>替人分拣</x:v>
+      </x:c>
+      <x:c r="D420" t="str">
+        <x:v>Sort the Salvage</x:v>
+      </x:c>
+      <x:c r="E420" t="str">
+        <x:v>替人分拣</x:v>
+      </x:c>
+      <x:c r="F420" t="str">
+        <x:v>Sort the Salvage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421">
+      <x:c r="A421"/>
+      <x:c r="B421" t="str">
+        <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Summary</x:v>
+      </x:c>
+      <x:c r="C421" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="D421" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+      <x:c r="E421" t="str">
+        <x:v>获得 3 灵石。</x:v>
+      </x:c>
+      <x:c r="F421" t="str">
+        <x:v>Gain 3 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422">
+      <x:c r="A422"/>
+      <x:c r="B422" t="str">
+        <x:v>Buqi.Content.Event.event_calming_chime.Name</x:v>
+      </x:c>
+      <x:c r="C422" t="str">
+        <x:v>镇心钟鸣</x:v>
+      </x:c>
+      <x:c r="D422" t="str">
+        <x:v>Calming Chime</x:v>
+      </x:c>
+      <x:c r="E422" t="str">
+        <x:v>镇心钟鸣</x:v>
+      </x:c>
+      <x:c r="F422" t="str">
+        <x:v>Calming Chime</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423">
+      <x:c r="A423"/>
+      <x:c r="B423" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Name</x:v>
+      </x:c>
+      <x:c r="C423" t="str">
+        <x:v>静听一刻</x:v>
+      </x:c>
+      <x:c r="D423" t="str">
+        <x:v>Listen in Stillness</x:v>
+      </x:c>
+      <x:c r="E423" t="str">
+        <x:v>静听一刻</x:v>
+      </x:c>
+      <x:c r="F423" t="str">
+        <x:v>Listen in Stillness</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424">
+      <x:c r="A424"/>
+      <x:c r="B424" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Summary</x:v>
+      </x:c>
+      <x:c r="C424" t="str">
+        <x:v>支付 1 灵石；下一战开场获得 10 护体并恢复 6 生命。</x:v>
+      </x:c>
+      <x:c r="D424" t="str">
+        <x:v>Pay 1 coin; next battle starts with 10 buffer and restores 6 life.</x:v>
+      </x:c>
+      <x:c r="E424" t="str">
+        <x:v>支付 1 灵石；下一战开场获得 10 护体并恢复 6 生命。</x:v>
+      </x:c>
+      <x:c r="F424" t="str">
+        <x:v>Pay 1 coin; next battle starts with 10 buffer and restores 6 life.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425">
+      <x:c r="A425"/>
+      <x:c r="B425" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Name</x:v>
+      </x:c>
+      <x:c r="C425" t="str">
+        <x:v>调准钟舌</x:v>
+      </x:c>
+      <x:c r="D425" t="str">
+        <x:v>Tune the Clapper</x:v>
+      </x:c>
+      <x:c r="E425" t="str">
+        <x:v>调准钟舌</x:v>
+      </x:c>
+      <x:c r="F425" t="str">
+        <x:v>Tune the Clapper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426"/>
+      <x:c r="B426" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Summary</x:v>
+      </x:c>
+      <x:c r="C426" t="str">
+        <x:v>支付 2 灵石，升级一件普通反制器物。</x:v>
+      </x:c>
+      <x:c r="D426" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal counter item.</x:v>
+      </x:c>
+      <x:c r="E426" t="str">
+        <x:v>支付 2 灵石，升级一件普通反制器物。</x:v>
+      </x:c>
+      <x:c r="F426" t="str">
+        <x:v>Pay 2 coins to upgrade a Normal counter item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427"/>
+      <x:c r="B427" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Name</x:v>
+      </x:c>
+      <x:c r="C427" t="str">
+        <x:v>记下钟律</x:v>
+      </x:c>
+      <x:c r="D427" t="str">
+        <x:v>Record the Chime</x:v>
+      </x:c>
+      <x:c r="E427" t="str">
+        <x:v>记下钟律</x:v>
+      </x:c>
+      <x:c r="F427" t="str">
+        <x:v>Record the Chime</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428"/>
+      <x:c r="B428" t="str">
+        <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Summary</x:v>
+      </x:c>
+      <x:c r="C428" t="str">
+        <x:v>下一战增加 2 点失衡，获得一件改良共享器物。</x:v>
+      </x:c>
+      <x:c r="D428" t="str">
+        <x:v>Start next battle with 2 noise debt and gain an Improved shared item.</x:v>
+      </x:c>
+      <x:c r="E428" t="str">
+        <x:v>下一战增加 2 点失衡，获得一件改良共享器物。</x:v>
+      </x:c>
+      <x:c r="F428" t="str">
+        <x:v>Start next battle with 2 noise debt and gain an Improved shared item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429"/>
+      <x:c r="B429" t="str">
+        <x:v>Buqi.Content.Event.event_day_nine_ledger.Name</x:v>
+      </x:c>
+      <x:c r="C429" t="str">
+        <x:v>九日归账</x:v>
+      </x:c>
+      <x:c r="D429" t="str">
+        <x:v>Day Nine Ledger</x:v>
+      </x:c>
+      <x:c r="E429" t="str">
+        <x:v>九日归账</x:v>
+      </x:c>
+      <x:c r="F429" t="str">
+        <x:v>Day Nine Ledger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430"/>
+      <x:c r="B430" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Name</x:v>
+      </x:c>
+      <x:c r="C430" t="str">
+        <x:v>按攻势结算</x:v>
+      </x:c>
+      <x:c r="D430" t="str">
+        <x:v>Settle by Offense</x:v>
+      </x:c>
+      <x:c r="E430" t="str">
+        <x:v>按攻势结算</x:v>
+      </x:c>
+      <x:c r="F430" t="str">
+        <x:v>Settle by Offense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431"/>
+      <x:c r="B431" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Summary</x:v>
+      </x:c>
+      <x:c r="C431" t="str">
+        <x:v>攻击构筑获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="D431" t="str">
+        <x:v>An attack build gains 5 coins.</x:v>
+      </x:c>
+      <x:c r="E431" t="str">
+        <x:v>攻击构筑获得 5 灵石。</x:v>
+      </x:c>
+      <x:c r="F431" t="str">
+        <x:v>An attack build gains 5 coins.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432"/>
+      <x:c r="B432" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Name</x:v>
+      </x:c>
+      <x:c r="C432" t="str">
+        <x:v>按守势结算</x:v>
+      </x:c>
+      <x:c r="D432" t="str">
+        <x:v>Settle by Defense</x:v>
+      </x:c>
+      <x:c r="E432" t="str">
+        <x:v>按守势结算</x:v>
+      </x:c>
+      <x:c r="F432" t="str">
+        <x:v>Settle by Defense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433"/>
+      <x:c r="B433" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Summary</x:v>
+      </x:c>
+      <x:c r="C433" t="str">
+        <x:v>护体构筑恢复 1 命。</x:v>
+      </x:c>
+      <x:c r="D433" t="str">
+        <x:v>A shield build restores 1 life.</x:v>
+      </x:c>
+      <x:c r="E433" t="str">
+        <x:v>护体构筑恢复 1 命。</x:v>
+      </x:c>
+      <x:c r="F433" t="str">
+        <x:v>A shield build restores 1 life.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434"/>
+      <x:c r="B434" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Name</x:v>
+      </x:c>
+      <x:c r="C434" t="str">
+        <x:v>按续航结算</x:v>
+      </x:c>
+      <x:c r="D434" t="str">
+        <x:v>Settle by Sustain</x:v>
+      </x:c>
+      <x:c r="E434" t="str">
+        <x:v>按续航结算</x:v>
+      </x:c>
+      <x:c r="F434" t="str">
+        <x:v>Settle by Sustain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435"/>
+      <x:c r="B435" t="str">
+        <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Summary</x:v>
+      </x:c>
+      <x:c r="C435" t="str">
+        <x:v>恢复构筑获得复写精炼。</x:v>
+      </x:c>
+      <x:c r="D435" t="str">
+        <x:v>A healing build gains the Echo refinement.</x:v>
+      </x:c>
+      <x:c r="E435" t="str">
+        <x:v>恢复构筑获得复写精炼。</x:v>
+      </x:c>
+      <x:c r="F435" t="str">
+        <x:v>A healing build gains the Echo refinement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436"/>
+      <x:c r="B436" t="str">
+        <x:v>Buqi.Content.Event.event_return_furnace.Name</x:v>
+      </x:c>
+      <x:c r="C436" t="str">
+        <x:v>不器归炉</x:v>
+      </x:c>
+      <x:c r="D436" t="str">
+        <x:v>Return to the Formless Furnace</x:v>
+      </x:c>
+      <x:c r="E436" t="str">
+        <x:v>不器归炉</x:v>
+      </x:c>
+      <x:c r="F436" t="str">
+        <x:v>Return to the Formless Furnace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437"/>
+      <x:c r="B437" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Name</x:v>
+      </x:c>
+      <x:c r="C437" t="str">
+        <x:v>熔去旧起手</x:v>
+      </x:c>
+      <x:c r="D437" t="str">
+        <x:v>Melt the Old Starter</x:v>
+      </x:c>
+      <x:c r="E437" t="str">
+        <x:v>熔去旧起手</x:v>
+      </x:c>
+      <x:c r="F437" t="str">
+        <x:v>Melt the Old Starter</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438">
+      <x:c r="A438"/>
+      <x:c r="B438" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Summary</x:v>
+      </x:c>
+      <x:c r="C438" t="str">
+        <x:v>移除一件起手器物，将一件收尾器物提升一级。</x:v>
+      </x:c>
+      <x:c r="D438" t="str">
+        <x:v>Remove one starter item and upgrade one finisher item.</x:v>
+      </x:c>
+      <x:c r="E438" t="str">
+        <x:v>移除一件起手器物，将一件收尾器物提升一级。</x:v>
+      </x:c>
+      <x:c r="F438" t="str">
+        <x:v>Remove one starter item and upgrade one finisher item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439"/>
+      <x:c r="B439" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Name</x:v>
+      </x:c>
+      <x:c r="C439" t="str">
+        <x:v>重排三路</x:v>
+      </x:c>
+      <x:c r="D439" t="str">
+        <x:v>Rebalance the Three Paths</x:v>
+      </x:c>
+      <x:c r="E439" t="str">
+        <x:v>重排三路</x:v>
+      </x:c>
+      <x:c r="F439" t="str">
+        <x:v>Rebalance the Three Paths</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440"/>
+      <x:c r="B440" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Summary</x:v>
+      </x:c>
+      <x:c r="C440" t="str">
+        <x:v>支付 2 灵石，获得一件定型转向器物。</x:v>
+      </x:c>
+      <x:c r="D440" t="str">
+        <x:v>Pay 2 coins to gain a Fixed pivot item.</x:v>
+      </x:c>
+      <x:c r="E440" t="str">
+        <x:v>支付 2 灵石，获得一件定型转向器物。</x:v>
+      </x:c>
+      <x:c r="F440" t="str">
+        <x:v>Pay 2 coins to gain a Fixed pivot item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441"/>
+      <x:c r="B441" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_close.Name</x:v>
+      </x:c>
+      <x:c r="C441" t="str">
+        <x:v>封存余火</x:v>
+      </x:c>
+      <x:c r="D441" t="str">
+        <x:v>Seal the Remaining Flame</x:v>
+      </x:c>
+      <x:c r="E441" t="str">
+        <x:v>封存余火</x:v>
+      </x:c>
+      <x:c r="F441" t="str">
+        <x:v>Seal the Remaining Flame</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442"/>
+      <x:c r="B442" t="str">
+        <x:v>Buqi.Content.EventOption.event_return_furnace_close.Summary</x:v>
+      </x:c>
+      <x:c r="C442" t="str">
+        <x:v>恢复 1 命并清除全部跨日约记。</x:v>
+      </x:c>
+      <x:c r="D442" t="str">
+        <x:v>Restore 1 life and clear all cross-day obligations.</x:v>
+      </x:c>
+      <x:c r="E442" t="str">
+        <x:v>恢复 1 命并清除全部跨日约记。</x:v>
+      </x:c>
+      <x:c r="F442" t="str">
+        <x:v>Restore 1 life and clear all cross-day obligations.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdce68705486742b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ff7df0f706e4a59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -897,16 +897,16 @@
         <x:v>Game.Name</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
-        <x:v>星际力量</x:v>
+        <x:v>不器</x:v>
       </x:c>
       <x:c r="D2" s="2" t="str">
-        <x:v>STAR FORCE</x:v>
+        <x:v>不器</x:v>
       </x:c>
       <x:c r="E2" s="2" t="str">
-        <x:v>星際力量</x:v>
+        <x:v>不器</x:v>
       </x:c>
       <x:c r="F2" s="2" t="str">
-        <x:v>게임 프레임워크</x:v>
+        <x:v>不器</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="3" customFormat="1" ht="17" customHeight="1">
@@ -915,16 +915,16 @@
         <x:v>Game.Description</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
-        <x:v>Game Framework 演示程序</x:v>
+        <x:v>不器游戏试玩版</x:v>
       </x:c>
       <x:c r="D3" s="2" t="str">
-        <x:v>Game Framework Demo Program</x:v>
+        <x:v>不器游戏试玩版</x:v>
       </x:c>
       <x:c r="E3" s="2" t="str">
-        <x:v>Game Framework 演示程式</x:v>
+        <x:v>不器游戏试玩版</x:v>
       </x:c>
       <x:c r="F3" s="2" t="str">
-        <x:v>Game Framework 데모 프로그램</x:v>
+        <x:v>不器游戏试玩版</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -951,16 +951,16 @@
         <x:v>Game.Summary</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>这是一个使用 Game Framework 游戏框架制作的游戏演示项目，目的是对此游戏框架的使用方法做一些示范，供使用者参考。</x:v>
+        <x:v>装备构筑、资源经营与自动战斗的试玩版。</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
-        <x:v>This project is a demo game made with Game Framework. It's intended to demonstrate how this game framework should be used for developers' reference.</x:v>
+        <x:v>装备构筑、资源经营与自动战斗的试玩版。</x:v>
       </x:c>
       <x:c r="E5" s="2" t="str">
-        <x:v>這是一個使用 Game Framework 遊戲框架製作的遊戲演示專案，目的是對此遊戲框架的使用方法做一些示範，供使用者參考。</x:v>
+        <x:v>装备构筑、资源经营与自动战斗的试玩版。</x:v>
       </x:c>
       <x:c r="F5" s="2" t="str">
-        <x:v>이 데모는 Game Framework 게임 시스템을 사용하여 만든 게임 데모 입니다.게임 시스템의 사용방법을 설명해 드리기 위해 예를 들어 만든 데모이기에 사용방법을 참조해 주시길 바랍니다.</x:v>
+        <x:v>装备构筑、资源经营与自动战斗的试玩版。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="3" customFormat="1" ht="17" customHeight="1">
@@ -969,16 +969,16 @@
         <x:v>Game.Introduction</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
-        <x:v>Game Framework 是基于 Unity 引擎的游戏框架，主要对游戏开发过程中常用模块进行了封装，很大程度地规范开发过程、加快开发速度并保证产品质量。</x:v>
+        <x:v>在九个回合中购买、强化并部署装备，通过自动战斗完成挑战。</x:v>
       </x:c>
       <x:c r="D6" s="2" t="str">
-        <x:v>Game Framework is literally a game framework, based on Unity game engine. It encapsulates commonly used game modules during development, and, to a large degree, standardises the process, enhances the development speed and ensures the product quality.</x:v>
+        <x:v>在九个回合中购买、强化并部署装备，通过自动战斗完成挑战。</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>Game Framework 是基於 Unity 引擎的遊戲框架，主要對遊戲開發過程中常用模組進行了封裝，很大程度地規範開發過程、加快開發速度並保證產品品質。</x:v>
+        <x:v>在九个回合中购买、强化并部署装备，通过自动战斗完成挑战。</x:v>
       </x:c>
       <x:c r="F6" s="2" t="str">
-        <x:v>Game Framework 는 유니티 엔진 Unity 버전을 이용한 게임 시스템 입니다. 주로 게임 개발과정에서 자주 사용하는 모듈을 캡슐화 하여 개발 과정을 규범화 하고 개발 속도를 높이며 게임의 콜리티를 보장해 드릴 수 있습니다.</x:v>
+        <x:v>在九个回合中购买、强化并部署装备，通过自动战斗完成挑战。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -990,13 +990,13 @@
         <x:v>开始</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
-        <x:v>START</x:v>
+        <x:v>开始</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>開始</x:v>
+        <x:v>开始</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
-        <x:v>시작</x:v>
+        <x:v>开始</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1008,13 +1008,13 @@
         <x:v>设置</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
-        <x:v>SETTINGS</x:v>
+        <x:v>设置</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>設置</x:v>
+        <x:v>设置</x:v>
       </x:c>
       <x:c r="F8" s="2" t="str">
-        <x:v>설정</x:v>
+        <x:v>设置</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1026,13 +1026,13 @@
         <x:v>关于</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>ABOUT</x:v>
+        <x:v>关于</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>關於</x:v>
+        <x:v>关于</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
-        <x:v>정보</x:v>
+        <x:v>关于</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1044,13 +1044,13 @@
         <x:v>退出</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
-        <x:v>QUIT</x:v>
+        <x:v>退出</x:v>
       </x:c>
       <x:c r="E10" s="2" t="str">
         <x:v>退出</x:v>
       </x:c>
       <x:c r="F10" s="2" t="str">
-        <x:v>아웃</x:v>
+        <x:v>退出</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1062,13 +1062,13 @@
         <x:v>确定</x:v>
       </x:c>
       <x:c r="D11" s="2" t="str">
-        <x:v>OK</x:v>
+        <x:v>确定</x:v>
       </x:c>
       <x:c r="E11" s="2" t="str">
-        <x:v>確定</x:v>
+        <x:v>确定</x:v>
       </x:c>
       <x:c r="F11" s="2" t="str">
-        <x:v>확인</x:v>
+        <x:v>确定</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1080,13 +1080,13 @@
         <x:v>取消</x:v>
       </x:c>
       <x:c r="D12" s="2" t="str">
-        <x:v>CANCEL</x:v>
+        <x:v>取消</x:v>
       </x:c>
       <x:c r="E12" s="2" t="str">
         <x:v>取消</x:v>
       </x:c>
       <x:c r="F12" s="2" t="str">
-        <x:v>취소</x:v>
+        <x:v>取消</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1098,13 +1098,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
-        <x:v>OTHER</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F13" s="2" t="str">
-        <x:v>기타</x:v>
+        <x:v>其他</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1116,13 +1116,13 @@
         <x:v>强制更新</x:v>
       </x:c>
       <x:c r="D14" s="2" t="str">
-        <x:v>OUT OF DATE</x:v>
+        <x:v>强制更新</x:v>
       </x:c>
       <x:c r="E14" s="2" t="str">
-        <x:v>強制更新</x:v>
+        <x:v>强制更新</x:v>
       </x:c>
       <x:c r="F14" s="2" t="str">
-        <x:v>필수 업데이트</x:v>
+        <x:v>强制更新</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="3" customFormat="1" ht="17" customHeight="1">
@@ -1134,13 +1134,13 @@
         <x:v>当前游戏版本过旧，是否前往更新？</x:v>
       </x:c>
       <x:c r="D15" s="2" t="str">
-        <x:v>The current game version is out-of-date. Would you like to go for update now?</x:v>
+        <x:v>当前游戏版本过旧，是否前往更新？</x:v>
       </x:c>
       <x:c r="E15" s="2" t="str">
-        <x:v>當前遊戲版本過舊，是否前往更新？</x:v>
+        <x:v>当前游戏版本过旧，是否前往更新？</x:v>
       </x:c>
       <x:c r="F15" s="2" t="str">
-        <x:v>새로운 게임 버전이 있는데 업데이트를 원하십니까?</x:v>
+        <x:v>当前游戏版本过旧，是否前往更新？</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1152,13 +1152,13 @@
         <x:v>更新</x:v>
       </x:c>
       <x:c r="D16" s="2" t="str">
-        <x:v>UPDATE</x:v>
+        <x:v>更新</x:v>
       </x:c>
       <x:c r="E16" s="2" t="str">
         <x:v>更新</x:v>
       </x:c>
       <x:c r="F16" s="2" t="str">
-        <x:v>업데이트</x:v>
+        <x:v>更新</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1170,13 +1170,13 @@
         <x:v>退出</x:v>
       </x:c>
       <x:c r="D17" s="2" t="str">
-        <x:v>QUIT</x:v>
+        <x:v>退出</x:v>
       </x:c>
       <x:c r="E17" s="2" t="str">
         <x:v>退出</x:v>
       </x:c>
       <x:c r="F17" s="2" t="str">
-        <x:v>아웃</x:v>
+        <x:v>退出</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1188,13 +1188,13 @@
         <x:v>确认退出</x:v>
       </x:c>
       <x:c r="D18" s="2" t="str">
-        <x:v>CONFIRM TO QUIT</x:v>
+        <x:v>确认退出</x:v>
       </x:c>
       <x:c r="E18" s="2" t="str">
-        <x:v>確認退出</x:v>
+        <x:v>确认退出</x:v>
       </x:c>
       <x:c r="F18" s="2" t="str">
-        <x:v>아웃 확인</x:v>
+        <x:v>确认退出</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="3" customFormat="1" ht="17" customHeight="1">
@@ -1206,13 +1206,13 @@
         <x:v>是否确认退出游戏？</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
-        <x:v>Are you sure to quit the game?</x:v>
+        <x:v>是否确认退出游戏？</x:v>
       </x:c>
       <x:c r="E19" s="2" t="str">
-        <x:v>是否確認退出遊戲？</x:v>
+        <x:v>是否确认退出游戏？</x:v>
       </x:c>
       <x:c r="F19" s="2" t="str">
-        <x:v>게임 로그아웃을 원하십니까?</x:v>
+        <x:v>是否确认退出游戏？</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1224,13 +1224,13 @@
         <x:v>设置</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:v>SETTINGS</x:v>
+        <x:v>设置</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:v>設置</x:v>
+        <x:v>设置</x:v>
       </x:c>
       <x:c r="F20" s="2" t="str">
-        <x:v>설정</x:v>
+        <x:v>设置</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1242,13 +1242,13 @@
         <x:v>音乐</x:v>
       </x:c>
       <x:c r="D21" s="2" t="str">
-        <x:v>Music</x:v>
+        <x:v>音乐</x:v>
       </x:c>
       <x:c r="E21" s="2" t="str">
-        <x:v>音樂</x:v>
+        <x:v>音乐</x:v>
       </x:c>
       <x:c r="F21" s="2" t="str">
-        <x:v>음악</x:v>
+        <x:v>音乐</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1260,13 +1260,13 @@
         <x:v>音效</x:v>
       </x:c>
       <x:c r="D22" s="2" t="str">
-        <x:v>Sound FX</x:v>
+        <x:v>音效</x:v>
       </x:c>
       <x:c r="E22" s="2" t="str">
         <x:v>音效</x:v>
       </x:c>
       <x:c r="F22" s="2" t="str">
-        <x:v>효과음</x:v>
+        <x:v>音效</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="3" customFormat="1" ht="17" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>界面音效</x:v>
       </x:c>
       <x:c r="D23" s="2" t="str">
-        <x:v>UI Sound FX</x:v>
+        <x:v>界面音效</x:v>
       </x:c>
       <x:c r="E23" s="2" t="str">
-        <x:v>介面音效</x:v>
+        <x:v>界面音效</x:v>
       </x:c>
       <x:c r="F23" s="2" t="str">
-        <x:v>UI 효과음</x:v>
+        <x:v>界面音效</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1296,13 +1296,13 @@
         <x:v>语言</x:v>
       </x:c>
       <x:c r="D24" s="2" t="str">
-        <x:v>Language</x:v>
+        <x:v>语言</x:v>
       </x:c>
       <x:c r="E24" s="2" t="str">
-        <x:v>語言</x:v>
+        <x:v>语言</x:v>
       </x:c>
       <x:c r="F24" s="2" t="str">
-        <x:v>언어</x:v>
+        <x:v>语言</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1314,13 +1314,13 @@
         <x:v>更改语言需要重启游戏</x:v>
       </x:c>
       <x:c r="D25" s="2" t="str">
-        <x:v>Language change demands restarting.</x:v>
+        <x:v>更改语言需要重启游戏</x:v>
       </x:c>
       <x:c r="E25" s="2" t="str">
-        <x:v>更改語言需要重啟遊戲</x:v>
+        <x:v>更改语言需要重启游戏</x:v>
       </x:c>
       <x:c r="F25" s="2" t="str">
-        <x:v>사용언어를 바꾼후 리부팅이 필요 합니다</x:v>
+        <x:v>更改语言需要重启游戏</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1329,16 +1329,16 @@
         <x:v>/apple</x:v>
       </x:c>
       <x:c r="C26" s="1" t="str">
-        <x:v>苹果</x:v>
+        <x:v>苹果版测试文本</x:v>
       </x:c>
       <x:c r="D26" s="1" t="str">
-        <x:v>Apple</x:v>
+        <x:v>苹果版测试文本</x:v>
       </x:c>
       <x:c r="E26" s="1" t="str">
-        <x:v>蘋果</x:v>
+        <x:v>苹果版测试文本</x:v>
       </x:c>
       <x:c r="F26" s="1" t="str">
-        <x:v>사과</x:v>
+        <x:v>苹果版测试文本</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1347,11 +1347,17 @@
         <x:v>test1</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>测试1</x:v>
-      </x:c>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
+        <x:v>测试文本一</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>测试文本一</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>测试文本一</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>测试文本一</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -1359,11 +1365,17 @@
         <x:v>test2</x:v>
       </x:c>
       <x:c r="C28" s="1" t="str">
-        <x:v>测试2</x:v>
-      </x:c>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
+        <x:v>测试文本二</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>测试文本二</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>测试文本二</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>测试文本二</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
@@ -1371,11 +1383,17 @@
         <x:v>1test</x:v>
       </x:c>
       <x:c r="C29" s="1" t="str">
-        <x:v>1测试</x:v>
-      </x:c>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
+        <x:v>测试文本三</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>测试文本三</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>测试文本三</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>测试文本三</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
@@ -1386,13 +1404,13 @@
         <x:v>确认操作</x:v>
       </x:c>
       <x:c r="D30" s="1" t="str">
-        <x:v>Confirm Action</x:v>
+        <x:v>确认操作</x:v>
       </x:c>
       <x:c r="E30" s="1" t="str">
-        <x:v>確認操作</x:v>
+        <x:v>确认操作</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>작업 확인</x:v>
+        <x:v>确认操作</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1404,13 +1422,13 @@
         <x:v>确认</x:v>
       </x:c>
       <x:c r="D31" s="1" t="str">
-        <x:v>Confirm</x:v>
+        <x:v>确认</x:v>
       </x:c>
       <x:c r="E31" s="1" t="str">
-        <x:v>確認</x:v>
+        <x:v>确认</x:v>
       </x:c>
       <x:c r="F31" s="1" t="str">
-        <x:v>확인</x:v>
+        <x:v>确认</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1422,13 +1440,13 @@
         <x:v>取消</x:v>
       </x:c>
       <x:c r="D32" s="1" t="str">
-        <x:v>Cancel</x:v>
+        <x:v>取消</x:v>
       </x:c>
       <x:c r="E32" s="1" t="str">
         <x:v>取消</x:v>
       </x:c>
       <x:c r="F32" s="1" t="str">
-        <x:v>취소</x:v>
+        <x:v>取消</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1440,13 +1458,13 @@
         <x:v>放置校验</x:v>
       </x:c>
       <x:c r="D33" s="1" t="str">
-        <x:v>Placement Check</x:v>
+        <x:v>放置校验</x:v>
       </x:c>
       <x:c r="E33" s="1" t="str">
-        <x:v>放置校驗</x:v>
+        <x:v>放置校验</x:v>
       </x:c>
       <x:c r="F33" s="1" t="str">
-        <x:v>배치 검증</x:v>
+        <x:v>放置校验</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1455,16 +1473,16 @@
         <x:v>Buqi.Deploy.ItemDetail</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
-        <x:v>道具详情</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
       <x:c r="D34" s="1" t="str">
-        <x:v>Item Detail</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>道具詳情</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>아이템 상세</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1476,13 +1494,13 @@
         <x:v>确认上阵</x:v>
       </x:c>
       <x:c r="D35" s="1" t="str">
-        <x:v>Confirm Deployment</x:v>
+        <x:v>确认上阵</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
-        <x:v>確認上陣</x:v>
+        <x:v>确认上阵</x:v>
       </x:c>
       <x:c r="F35" s="1" t="str">
-        <x:v>배치 확인</x:v>
+        <x:v>确认上阵</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1491,16 +1509,16 @@
         <x:v>Buqi.Deploy.PendingItems</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
-        <x:v>待上阵道具</x:v>
+        <x:v>待上阵装备</x:v>
       </x:c>
       <x:c r="D36" s="1" t="str">
-        <x:v>Pending Items</x:v>
+        <x:v>待上阵装备</x:v>
       </x:c>
       <x:c r="E36" s="1" t="str">
-        <x:v>待上陣道具</x:v>
+        <x:v>待上阵装备</x:v>
       </x:c>
       <x:c r="F36" s="1" t="str">
-        <x:v>대기 아이템</x:v>
+        <x:v>待上阵装备</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1512,13 +1530,13 @@
         <x:v>取消</x:v>
       </x:c>
       <x:c r="D37" s="1" t="str">
-        <x:v>Cancel</x:v>
+        <x:v>取消</x:v>
       </x:c>
       <x:c r="E37" s="1" t="str">
         <x:v>取消</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>취소</x:v>
+        <x:v>取消</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1527,16 +1545,16 @@
         <x:v>Buqi.Deploy.Header</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
-        <x:v>仓库  &gt;  阵列  |  拖动调整位置  |  拖回仓库撤下</x:v>
+        <x:v>仓库 &gt; 八格装备栏 | 拖动调整位置 | 拖回仓库卸下</x:v>
       </x:c>
       <x:c r="D38" s="1" t="str">
-        <x:v>Storage &gt; Board | Drag to rearrange | Drag back to storage to unequip</x:v>
+        <x:v>仓库 &gt; 八格装备栏 | 拖动调整位置 | 拖回仓库卸下</x:v>
       </x:c>
       <x:c r="E38" s="1" t="str">
-        <x:v>倉庫  &gt;  陣列  |  拖動調整位置  |  拖回倉庫卸下</x:v>
+        <x:v>仓库 &gt; 八格装备栏 | 拖动调整位置 | 拖回仓库卸下</x:v>
       </x:c>
       <x:c r="F38" s="1" t="str">
-        <x:v>창고 &gt; 배열 | 드래그로 위치 조정 | 창고로 되돌려 해제</x:v>
+        <x:v>仓库 &gt; 八格装备栏 | 拖动调整位置 | 拖回仓库卸下</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1545,16 +1563,16 @@
         <x:v>Buqi.Deploy.Title</x:v>
       </x:c>
       <x:c r="C39" s="1" t="str">
-        <x:v>不器阵列</x:v>
+        <x:v>八格装备栏</x:v>
       </x:c>
       <x:c r="D39" s="1" t="str">
-        <x:v>Buqi Formation</x:v>
+        <x:v>八格装备栏</x:v>
       </x:c>
       <x:c r="E39" s="1" t="str">
-        <x:v>不器陣列</x:v>
+        <x:v>八格装备栏</x:v>
       </x:c>
       <x:c r="F39" s="1" t="str">
-        <x:v>부기 배열</x:v>
+        <x:v>八格装备栏</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1566,13 +1584,13 @@
         <x:v>拖拽上阵</x:v>
       </x:c>
       <x:c r="D40" s="1" t="str">
-        <x:v>Drag to Deploy</x:v>
+        <x:v>拖拽上阵</x:v>
       </x:c>
       <x:c r="E40" s="1" t="str">
-        <x:v>拖拽上陣</x:v>
+        <x:v>拖拽上阵</x:v>
       </x:c>
       <x:c r="F40" s="1" t="str">
-        <x:v>드래그 배치</x:v>
+        <x:v>拖拽上阵</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1584,13 +1602,13 @@
         <x:v>阵容编辑</x:v>
       </x:c>
       <x:c r="D41" s="1" t="str">
-        <x:v>Deck Edit</x:v>
+        <x:v>阵容编辑</x:v>
       </x:c>
       <x:c r="E41" s="1" t="str">
-        <x:v>陣容編輯</x:v>
+        <x:v>阵容编辑</x:v>
       </x:c>
       <x:c r="F41" s="1" t="str">
-        <x:v>덱 편집</x:v>
+        <x:v>阵容编辑</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1602,13 +1620,13 @@
         <x:v>选择一件装备查看详情</x:v>
       </x:c>
       <x:c r="D42" s="1" t="str">
-        <x:v>Select an item to view details</x:v>
+        <x:v>选择一件装备查看详情</x:v>
       </x:c>
       <x:c r="E42" s="1" t="str">
-        <x:v>選擇一件裝備查看詳情</x:v>
+        <x:v>选择一件装备查看详情</x:v>
       </x:c>
       <x:c r="F42" s="1" t="str">
-        <x:v>아이템을 선택해 상세를 확인하세요</x:v>
+        <x:v>选择一件装备查看详情</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1635,16 +1653,16 @@
         <x:v>Buqi.Deploy.ApplyHint</x:v>
       </x:c>
       <x:c r="C44" s="1" t="str">
-        <x:v>阵列变更仅在确认后生效</x:v>
+        <x:v>装备栏变更仅在确认后生效</x:v>
       </x:c>
       <x:c r="D44" s="1" t="str">
-        <x:v>Formation changes take effect after confirmation</x:v>
+        <x:v>装备栏变更仅在确认后生效</x:v>
       </x:c>
       <x:c r="E44" s="1" t="str">
-        <x:v>陣列變更僅在確認後生效</x:v>
+        <x:v>装备栏变更仅在确认后生效</x:v>
       </x:c>
       <x:c r="F44" s="1" t="str">
-        <x:v>배열 변경은 확인 후 적용됩니다</x:v>
+        <x:v>装备栏变更仅在确认后生效</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1653,16 +1671,16 @@
         <x:v>Buqi.Deploy.Context</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
-        <x:v>第 3 回合  |  金币 12  |  胜场 4  |  生命 2  |  对手 清虚真人</x:v>
+        <x:v>第 3 回合 | 金币 12 | 胜场 4 | 生命 2 | 对手 训练对手</x:v>
       </x:c>
       <x:c r="D45" s="1" t="str">
-        <x:v>Round 3 | Coins 12 | Wins 4 | Life 2 | Opponent Qingxu Zhenren</x:v>
+        <x:v>第 3 回合 | 金币 12 | 胜场 4 | 生命 2 | 对手 训练对手</x:v>
       </x:c>
       <x:c r="E45" s="1" t="str">
-        <x:v>第 3 回合  |  金幣 12  |  勝場 4  |  生命 2  |  對手 清虛真人</x:v>
+        <x:v>第 3 回合 | 金币 12 | 胜场 4 | 生命 2 | 对手 训练对手</x:v>
       </x:c>
       <x:c r="F45" s="1" t="str">
-        <x:v>3라운드 | 코인 12 | 승리 4 | 생명 2 | 상대 청허진인</x:v>
+        <x:v>第 3 回合 | 金币 12 | 胜场 4 | 生命 2 | 对手 训练对手</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1674,13 +1692,13 @@
         <x:v>重置</x:v>
       </x:c>
       <x:c r="D46" s="1" t="str">
-        <x:v>Reset</x:v>
+        <x:v>重置</x:v>
       </x:c>
       <x:c r="E46" s="1" t="str">
         <x:v>重置</x:v>
       </x:c>
       <x:c r="F46" s="1" t="str">
-        <x:v>초기화</x:v>
+        <x:v>重置</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1692,13 +1710,13 @@
         <x:v>装备详情</x:v>
       </x:c>
       <x:c r="D47" s="1" t="str">
-        <x:v>Item Detail</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
       <x:c r="E47" s="1" t="str">
-        <x:v>裝備詳情</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
       <x:c r="F47" s="1" t="str">
-        <x:v>아이템 상세</x:v>
+        <x:v>装备详情</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1710,13 +1728,13 @@
         <x:v>关闭</x:v>
       </x:c>
       <x:c r="D48" s="1" t="str">
-        <x:v>Close</x:v>
+        <x:v>关闭</x:v>
       </x:c>
       <x:c r="E48" s="1" t="str">
-        <x:v>關閉</x:v>
+        <x:v>关闭</x:v>
       </x:c>
       <x:c r="F48" s="1" t="str">
-        <x:v>닫기</x:v>
+        <x:v>关闭</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1728,13 +1746,13 @@
         <x:v>无改造</x:v>
       </x:c>
       <x:c r="D49" s="1" t="str">
-        <x:v>No Refinement</x:v>
+        <x:v>无改造</x:v>
       </x:c>
       <x:c r="E49" s="1" t="str">
-        <x:v>無改造</x:v>
+        <x:v>无改造</x:v>
       </x:c>
       <x:c r="F49" s="1" t="str">
-        <x:v>개조 없음</x:v>
+        <x:v>无改造</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1743,16 +1761,16 @@
         <x:v>Buqi.ItemDetail.DamageTag</x:v>
       </x:c>
       <x:c r="C50" s="1" t="str">
-        <x:v>Damage</x:v>
+        <x:v>伤害</x:v>
       </x:c>
       <x:c r="D50" s="1" t="str">
-        <x:v>Damage</x:v>
+        <x:v>伤害</x:v>
       </x:c>
       <x:c r="E50" s="1" t="str">
-        <x:v>Damage</x:v>
+        <x:v>伤害</x:v>
       </x:c>
       <x:c r="F50" s="1" t="str">
-        <x:v>Damage</x:v>
+        <x:v>伤害</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1761,16 +1779,16 @@
         <x:v>Buqi.ItemDetail.SampleId</x:v>
       </x:c>
       <x:c r="C51" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="D51" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="E51" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="F51" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1779,16 +1797,16 @@
         <x:v>Buqi.Message.InfoTag</x:v>
       </x:c>
       <x:c r="C52" s="1" t="str">
-        <x:v>INFO</x:v>
+        <x:v>提示</x:v>
       </x:c>
       <x:c r="D52" s="1" t="str">
-        <x:v>INFO</x:v>
+        <x:v>提示</x:v>
       </x:c>
       <x:c r="E52" s="1" t="str">
-        <x:v>INFO</x:v>
+        <x:v>提示</x:v>
       </x:c>
       <x:c r="F52" s="1" t="str">
-        <x:v>INFO</x:v>
+        <x:v>提示</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1797,16 +1815,16 @@
         <x:v>Buqi.RunShell.Title</x:v>
       </x:c>
       <x:c r="C53" s="1" t="str">
-        <x:v>不器  |  DEMO UI GALLERY</x:v>
+        <x:v>不器 · 九日试炼</x:v>
       </x:c>
       <x:c r="D53" s="1" t="str">
-        <x:v>Buqi | DEMO UI GALLERY</x:v>
+        <x:v>不器 · 九日试炼</x:v>
       </x:c>
       <x:c r="E53" s="1" t="str">
-        <x:v>不器  |  DEMO UI GALLERY</x:v>
+        <x:v>不器 · 九日试炼</x:v>
       </x:c>
       <x:c r="F53" s="1" t="str">
-        <x:v>부기 | DEMO UI GALLERY</x:v>
+        <x:v>不器 · 九日试炼</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1815,16 +1833,16 @@
         <x:v>Buqi.RunShell.RestartTag</x:v>
       </x:c>
       <x:c r="C54" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="D54" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="E54" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="F54" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1836,13 +1854,13 @@
         <x:v>继续</x:v>
       </x:c>
       <x:c r="D55" s="1" t="str">
-        <x:v>Continue</x:v>
+        <x:v>继续</x:v>
       </x:c>
       <x:c r="E55" s="1" t="str">
-        <x:v>繼續</x:v>
+        <x:v>继续</x:v>
       </x:c>
       <x:c r="F55" s="1" t="str">
-        <x:v>계속</x:v>
+        <x:v>继续</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1872,13 +1890,13 @@
         <x:v>当前阶段</x:v>
       </x:c>
       <x:c r="D57" s="1" t="str">
-        <x:v>Current Phase</x:v>
+        <x:v>当前阶段</x:v>
       </x:c>
       <x:c r="E57" s="1" t="str">
-        <x:v>當前階段</x:v>
+        <x:v>当前阶段</x:v>
       </x:c>
       <x:c r="F57" s="1" t="str">
-        <x:v>현재 단계</x:v>
+        <x:v>当前阶段</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1890,13 +1908,13 @@
         <x:v>空位</x:v>
       </x:c>
       <x:c r="D58" s="1" t="str">
-        <x:v>Empty</x:v>
+        <x:v>空位</x:v>
       </x:c>
       <x:c r="E58" s="1" t="str">
         <x:v>空位</x:v>
       </x:c>
       <x:c r="F58" s="1" t="str">
-        <x:v>빈 칸</x:v>
+        <x:v>空位</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1941,16 +1959,16 @@
         <x:v>Buqi.Item.SampleId</x:v>
       </x:c>
       <x:c r="C61" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="D61" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="E61" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
       <x:c r="F61" s="1" t="str">
-        <x:v>W8-000</x:v>
+        <x:v>示例装备</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1962,13 +1980,13 @@
         <x:v>仓库 01</x:v>
       </x:c>
       <x:c r="D62" s="1" t="str">
-        <x:v>Storage 01</x:v>
+        <x:v>仓库 01</x:v>
       </x:c>
       <x:c r="E62" s="1" t="str">
-        <x:v>倉庫 01</x:v>
+        <x:v>仓库 01</x:v>
       </x:c>
       <x:c r="F62" s="1" t="str">
-        <x:v>창고 01</x:v>
+        <x:v>仓库 01</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1980,13 +1998,13 @@
         <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="D63" s="1" t="str">
-        <x:v>Occupies 1 slot</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="E63" s="1" t="str">
-        <x:v>佔用 1 格</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="F63" s="1" t="str">
-        <x:v>1칸 차지</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1998,13 +2016,13 @@
         <x:v>不器 · 战斗回放</x:v>
       </x:c>
       <x:c r="D64" s="1" t="str">
-        <x:v>Buqi · Battle Replay</x:v>
+        <x:v>不器 · 战斗回放</x:v>
       </x:c>
       <x:c r="E64" s="1" t="str">
-        <x:v>不器 · 戰鬥回放</x:v>
+        <x:v>不器 · 战斗回放</x:v>
       </x:c>
       <x:c r="F64" s="1" t="str">
-        <x:v>부기 · 전투 리플레이</x:v>
+        <x:v>不器 · 战斗回放</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2016,13 +2034,13 @@
         <x:v>左侧构筑</x:v>
       </x:c>
       <x:c r="D65" s="1" t="str">
-        <x:v>Left Build</x:v>
+        <x:v>左侧构筑</x:v>
       </x:c>
       <x:c r="E65" s="1" t="str">
-        <x:v>左側構築</x:v>
+        <x:v>左侧构筑</x:v>
       </x:c>
       <x:c r="F65" s="1" t="str">
-        <x:v>좌측 빌드</x:v>
+        <x:v>左侧构筑</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -2034,13 +2052,13 @@
         <x:v>右侧构筑</x:v>
       </x:c>
       <x:c r="D66" s="1" t="str">
-        <x:v>Right Build</x:v>
+        <x:v>右侧构筑</x:v>
       </x:c>
       <x:c r="E66" s="1" t="str">
-        <x:v>右側構築</x:v>
+        <x:v>右侧构筑</x:v>
       </x:c>
       <x:c r="F66" s="1" t="str">
-        <x:v>우측 빌드</x:v>
+        <x:v>右侧构筑</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -2052,13 +2070,13 @@
         <x:v>战斗证据</x:v>
       </x:c>
       <x:c r="D67" s="1" t="str">
-        <x:v>Battle Evidence</x:v>
+        <x:v>战斗证据</x:v>
       </x:c>
       <x:c r="E67" s="1" t="str">
-        <x:v>戰鬥證據</x:v>
+        <x:v>战斗证据</x:v>
       </x:c>
       <x:c r="F67" s="1" t="str">
-        <x:v>전투 증거</x:v>
+        <x:v>战斗证据</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -2070,13 +2088,13 @@
         <x:v>终局事实</x:v>
       </x:c>
       <x:c r="D68" s="1" t="str">
-        <x:v>Final Facts</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
       <x:c r="E68" s="1" t="str">
-        <x:v>終局事實</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
       <x:c r="F68" s="1" t="str">
-        <x:v>최종 사실</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -2088,13 +2106,13 @@
         <x:v>尚无事件</x:v>
       </x:c>
       <x:c r="D69" s="1" t="str">
-        <x:v>No Events</x:v>
+        <x:v>尚无事件</x:v>
       </x:c>
       <x:c r="E69" s="1" t="str">
-        <x:v>尚無事件</x:v>
+        <x:v>尚无事件</x:v>
       </x:c>
       <x:c r="F69" s="1" t="str">
-        <x:v>이벤트 없음</x:v>
+        <x:v>尚无事件</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -2106,13 +2124,13 @@
         <x:v>战斗推演中</x:v>
       </x:c>
       <x:c r="D70" s="1" t="str">
-        <x:v>Simulating</x:v>
+        <x:v>战斗推演中</x:v>
       </x:c>
       <x:c r="E70" s="1" t="str">
-        <x:v>戰鬥推演中</x:v>
+        <x:v>战斗推演中</x:v>
       </x:c>
       <x:c r="F70" s="1" t="str">
-        <x:v>전투 시뮬레이션 중</x:v>
+        <x:v>战斗推演中</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -2124,13 +2142,13 @@
         <x:v>暂停</x:v>
       </x:c>
       <x:c r="D71" s="1" t="str">
-        <x:v>Pause</x:v>
+        <x:v>暂停</x:v>
       </x:c>
       <x:c r="E71" s="1" t="str">
-        <x:v>暫停</x:v>
+        <x:v>暂停</x:v>
       </x:c>
       <x:c r="F71" s="1" t="str">
-        <x:v>일시정지</x:v>
+        <x:v>暂停</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -2142,13 +2160,13 @@
         <x:v>继续</x:v>
       </x:c>
       <x:c r="D72" s="1" t="str">
-        <x:v>Continue</x:v>
+        <x:v>继续</x:v>
       </x:c>
       <x:c r="E72" s="1" t="str">
-        <x:v>繼續</x:v>
+        <x:v>继续</x:v>
       </x:c>
       <x:c r="F72" s="1" t="str">
-        <x:v>계속</x:v>
+        <x:v>继续</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -2160,13 +2178,13 @@
         <x:v>实时</x:v>
       </x:c>
       <x:c r="D73" s="1" t="str">
-        <x:v>Live</x:v>
+        <x:v>实时</x:v>
       </x:c>
       <x:c r="E73" s="1" t="str">
-        <x:v>即時</x:v>
+        <x:v>实时</x:v>
       </x:c>
       <x:c r="F73" s="1" t="str">
-        <x:v>실시간</x:v>
+        <x:v>实时</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -2178,13 +2196,13 @@
         <x:v>未知的战斗回放错误。</x:v>
       </x:c>
       <x:c r="D74" s="1" t="str">
-        <x:v>Unknown battle replay error.</x:v>
+        <x:v>未知的战斗回放错误。</x:v>
       </x:c>
       <x:c r="E74" s="1" t="str">
-        <x:v>未知的戰鬥回放錯誤。</x:v>
+        <x:v>未知的战斗回放错误。</x:v>
       </x:c>
       <x:c r="F74" s="1" t="str">
-        <x:v>알 수 없는 전투 리플레이 오류.</x:v>
+        <x:v>未知的战斗回放错误。</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -2193,16 +2211,16 @@
         <x:v>Buqi.Battle.Speed1x</x:v>
       </x:c>
       <x:c r="C75" s="1" t="str">
-        <x:v>1x</x:v>
+        <x:v>1 倍</x:v>
       </x:c>
       <x:c r="D75" s="1" t="str">
-        <x:v>1x</x:v>
+        <x:v>1 倍</x:v>
       </x:c>
       <x:c r="E75" s="1" t="str">
-        <x:v>1x</x:v>
+        <x:v>1 倍</x:v>
       </x:c>
       <x:c r="F75" s="1" t="str">
-        <x:v>1x</x:v>
+        <x:v>1 倍</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -2211,16 +2229,16 @@
         <x:v>Buqi.Battle.Speed2x</x:v>
       </x:c>
       <x:c r="C76" s="1" t="str">
-        <x:v>2x</x:v>
+        <x:v>2 倍</x:v>
       </x:c>
       <x:c r="D76" s="1" t="str">
-        <x:v>2x</x:v>
+        <x:v>2 倍</x:v>
       </x:c>
       <x:c r="E76" s="1" t="str">
-        <x:v>2x</x:v>
+        <x:v>2 倍</x:v>
       </x:c>
       <x:c r="F76" s="1" t="str">
-        <x:v>2x</x:v>
+        <x:v>2 倍</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -2229,16 +2247,16 @@
         <x:v>Buqi.Battle.Speed4x</x:v>
       </x:c>
       <x:c r="C77" s="1" t="str">
-        <x:v>4x</x:v>
+        <x:v>4 倍</x:v>
       </x:c>
       <x:c r="D77" s="1" t="str">
-        <x:v>4x</x:v>
+        <x:v>4 倍</x:v>
       </x:c>
       <x:c r="E77" s="1" t="str">
-        <x:v>4x</x:v>
+        <x:v>4 倍</x:v>
       </x:c>
       <x:c r="F77" s="1" t="str">
-        <x:v>4x</x:v>
+        <x:v>4 倍</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -2247,16 +2265,16 @@
         <x:v>Buqi.Battle.LiveBadge</x:v>
       </x:c>
       <x:c r="C78" s="1" t="str">
-        <x:v>LIVE</x:v>
+        <x:v>实时</x:v>
       </x:c>
       <x:c r="D78" s="1" t="str">
-        <x:v>LIVE</x:v>
+        <x:v>实时</x:v>
       </x:c>
       <x:c r="E78" s="1" t="str">
-        <x:v>LIVE</x:v>
+        <x:v>实时</x:v>
       </x:c>
       <x:c r="F78" s="1" t="str">
-        <x:v>LIVE</x:v>
+        <x:v>实时</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -2265,16 +2283,16 @@
         <x:v>Buqi.Battle.TickPlaceholder</x:v>
       </x:c>
       <x:c r="C79" s="1" t="str">
-        <x:v>TICK 000 / 000</x:v>
+        <x:v>进度 000 / 000</x:v>
       </x:c>
       <x:c r="D79" s="1" t="str">
-        <x:v>TICK 000 / 000</x:v>
+        <x:v>进度 000 / 000</x:v>
       </x:c>
       <x:c r="E79" s="1" t="str">
-        <x:v>TICK 000 / 000</x:v>
+        <x:v>进度 000 / 000</x:v>
       </x:c>
       <x:c r="F79" s="1" t="str">
-        <x:v>TICK 000 / 000</x:v>
+        <x:v>进度 000 / 000</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -2286,13 +2304,13 @@
         <x:v>生命值 --  护盾 --  过载 --</x:v>
       </x:c>
       <x:c r="D80" s="1" t="str">
-        <x:v>HP --  Shield --  Overload --</x:v>
+        <x:v>生命值 --  护盾 --  过载 --</x:v>
       </x:c>
       <x:c r="E80" s="1" t="str">
-        <x:v>生命值 --  護盾 --  過載 --</x:v>
+        <x:v>生命值 --  护盾 --  过载 --</x:v>
       </x:c>
       <x:c r="F80" s="1" t="str">
-        <x:v>체력 --  보호막 --  과부하 --</x:v>
+        <x:v>生命值 --  护盾 --  过载 --</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -2355,16 +2373,16 @@
         <x:v>Buqi.Battle.RestartTag</x:v>
       </x:c>
       <x:c r="C84" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="D84" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="E84" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
       <x:c r="F84" s="1" t="str">
-        <x:v>R</x:v>
+        <x:v>↻</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -2373,16 +2391,16 @@
         <x:v>Buqi.Log.Placeholder</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>T000  --  0</x:v>
+        <x:v>时刻 000  --  0</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>T000  --  0</x:v>
+        <x:v>时刻 000  --  0</x:v>
       </x:c>
       <x:c r="E85" t="str">
-        <x:v>T000  --  0</x:v>
+        <x:v>时刻 000  --  0</x:v>
       </x:c>
       <x:c r="F85" t="str">
-        <x:v>T000  --  0</x:v>
+        <x:v>时刻 000  --  0</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -2391,16 +2409,16 @@
         <x:v>Buqi.BoardSlot.Locked</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="E86" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="F86" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -2409,16 +2427,16 @@
         <x:v>Buqi.BoardSlot.Size1</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>SIZE 1</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="D87" t="str">
-        <x:v>SIZE 1</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="E87" t="str">
-        <x:v>SIZE 1</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
       <x:c r="F87" t="str">
-        <x:v>SIZE 1</x:v>
+        <x:v>占用 1 格</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -2427,16 +2445,16 @@
         <x:v>Buqi.BoardSlot.Item</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>ITEM</x:v>
+        <x:v>装备</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>ITEM</x:v>
+        <x:v>装备</x:v>
       </x:c>
       <x:c r="E88" t="str">
-        <x:v>ITEM</x:v>
+        <x:v>装备</x:v>
       </x:c>
       <x:c r="F88" t="str">
-        <x:v>ITEM</x:v>
+        <x:v>装备</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -2445,16 +2463,16 @@
         <x:v>Buqi.BoardSlot.SlotLabel</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>SLOT 01</x:v>
+        <x:v>位置 01</x:v>
       </x:c>
       <x:c r="D89" t="str">
-        <x:v>SLOT 01</x:v>
+        <x:v>位置 01</x:v>
       </x:c>
       <x:c r="E89" t="str">
-        <x:v>SLOT 01</x:v>
+        <x:v>位置 01</x:v>
       </x:c>
       <x:c r="F89" t="str">
-        <x:v>SLOT 01</x:v>
+        <x:v>位置 01</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -2463,16 +2481,16 @@
         <x:v>Buqi.Choice.Cost0</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>COST 0</x:v>
+        <x:v>花费 0</x:v>
       </x:c>
       <x:c r="D90" t="str">
-        <x:v>COST 0</x:v>
+        <x:v>花费 0</x:v>
       </x:c>
       <x:c r="E90" t="str">
-        <x:v>COST 0</x:v>
+        <x:v>花费 0</x:v>
       </x:c>
       <x:c r="F90" t="str">
-        <x:v>COST 0</x:v>
+        <x:v>花费 0</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -2481,16 +2499,16 @@
         <x:v>Buqi.Choice.Unavailable</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>UNAVAILABLE</x:v>
+        <x:v>当前不可选</x:v>
       </x:c>
       <x:c r="D91" t="str">
-        <x:v>UNAVAILABLE</x:v>
+        <x:v>当前不可选</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>UNAVAILABLE</x:v>
+        <x:v>当前不可选</x:v>
       </x:c>
       <x:c r="F91" t="str">
-        <x:v>UNAVAILABLE</x:v>
+        <x:v>当前不可选</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -2499,16 +2517,16 @@
         <x:v>Buqi.Choice.Title</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>CHOICE</x:v>
+        <x:v>可选内容</x:v>
       </x:c>
       <x:c r="D92" t="str">
-        <x:v>CHOICE</x:v>
+        <x:v>可选内容</x:v>
       </x:c>
       <x:c r="E92" t="str">
-        <x:v>CHOICE</x:v>
+        <x:v>可选内容</x:v>
       </x:c>
       <x:c r="F92" t="str">
-        <x:v>CHOICE</x:v>
+        <x:v>可选内容</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -2517,16 +2535,16 @@
         <x:v>Buqi.Choice.Description</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>Choice description</x:v>
+        <x:v>选择一项继续</x:v>
       </x:c>
       <x:c r="D93" t="str">
-        <x:v>Choice description</x:v>
+        <x:v>选择一项继续</x:v>
       </x:c>
       <x:c r="E93" t="str">
-        <x:v>Choice description</x:v>
+        <x:v>选择一项继续</x:v>
       </x:c>
       <x:c r="F93" t="str">
-        <x:v>Choice description</x:v>
+        <x:v>选择一项继续</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -2538,13 +2556,13 @@
         <x:v>关键装备完成有效伤害</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>Key item dealt effective damage</x:v>
+        <x:v>关键装备完成有效伤害</x:v>
       </x:c>
       <x:c r="E94" t="str">
-        <x:v>關鍵裝備完成有效傷害</x:v>
+        <x:v>关键装备完成有效伤害</x:v>
       </x:c>
       <x:c r="F94" t="str">
-        <x:v>핵심 장비가 유효 피해를 입혔습니다</x:v>
+        <x:v>关键装备完成有效伤害</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -2553,16 +2571,16 @@
         <x:v>Buqi.Fact.JumpTo</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>跳到 T000</x:v>
+        <x:v>跳到时刻 000</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>Jump to T000</x:v>
+        <x:v>跳到时刻 000</x:v>
       </x:c>
       <x:c r="E95" t="str">
-        <x:v>跳到 T000</x:v>
+        <x:v>跳到时刻 000</x:v>
       </x:c>
       <x:c r="F95" t="str">
-        <x:v>T000으로 이동</x:v>
+        <x:v>跳到时刻 000</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -2574,13 +2592,13 @@
         <x:v>终局事实</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>Final Facts</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
       <x:c r="E96" t="str">
-        <x:v>終局事實</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
       <x:c r="F96" t="str">
-        <x:v>최종 사실</x:v>
+        <x:v>终局事实</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -2592,13 +2610,13 @@
         <x:v>冻</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>Frozen</x:v>
+        <x:v>冻</x:v>
       </x:c>
       <x:c r="E97" t="str">
-        <x:v>凍</x:v>
+        <x:v>冻</x:v>
       </x:c>
       <x:c r="F97" t="str">
-        <x:v>빙결</x:v>
+        <x:v>冻</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -2610,13 +2628,13 @@
         <x:v>1格  充能 0  冻结 0</x:v>
       </x:c>
       <x:c r="D98" t="str">
-        <x:v>1 slot  Charge 0  Freeze 0</x:v>
+        <x:v>1格  充能 0  冻结 0</x:v>
       </x:c>
       <x:c r="E98" t="str">
-        <x:v>1格  充能 0  凍結 0</x:v>
+        <x:v>1格  充能 0  冻结 0</x:v>
       </x:c>
       <x:c r="F98" t="str">
-        <x:v>1칸  충전 0  빙결 0</x:v>
+        <x:v>1格  充能 0  冻结 0</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -2625,16 +2643,16 @@
         <x:v>Buqi.Offer.Sold</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>SOLD</x:v>
+        <x:v>已售出</x:v>
       </x:c>
       <x:c r="D99" t="str">
-        <x:v>SOLD</x:v>
+        <x:v>已售出</x:v>
       </x:c>
       <x:c r="E99" t="str">
-        <x:v>SOLD</x:v>
+        <x:v>已售出</x:v>
       </x:c>
       <x:c r="F99" t="str">
-        <x:v>SOLD</x:v>
+        <x:v>已售出</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -2643,16 +2661,16 @@
         <x:v>Buqi.Offer.Price0</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>PRICE 0</x:v>
+        <x:v>价格 0</x:v>
       </x:c>
       <x:c r="D100" t="str">
-        <x:v>PRICE 0</x:v>
+        <x:v>价格 0</x:v>
       </x:c>
       <x:c r="E100" t="str">
-        <x:v>PRICE 0</x:v>
+        <x:v>价格 0</x:v>
       </x:c>
       <x:c r="F100" t="str">
-        <x:v>PRICE 0</x:v>
+        <x:v>价格 0</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -2661,16 +2679,16 @@
         <x:v>Buqi.Offer.Locked</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="D101" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="E101" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
       <x:c r="F101" t="str">
-        <x:v>LOCKED</x:v>
+        <x:v>已锁定</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2679,16 +2697,16 @@
         <x:v>Buqi.Offer.Title</x:v>
       </x:c>
       <x:c r="C102" t="str">
-        <x:v>OFFER</x:v>
+        <x:v>商品</x:v>
       </x:c>
       <x:c r="D102" t="str">
-        <x:v>OFFER</x:v>
+        <x:v>商品</x:v>
       </x:c>
       <x:c r="E102" t="str">
-        <x:v>OFFER</x:v>
+        <x:v>商品</x:v>
       </x:c>
       <x:c r="F102" t="str">
-        <x:v>OFFER</x:v>
+        <x:v>商品</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2697,16 +2715,16 @@
         <x:v>Buqi.Offer.Buy</x:v>
       </x:c>
       <x:c r="C103" t="str">
-        <x:v>BUY</x:v>
+        <x:v>购买</x:v>
       </x:c>
       <x:c r="D103" t="str">
-        <x:v>BUY</x:v>
+        <x:v>购买</x:v>
       </x:c>
       <x:c r="E103" t="str">
-        <x:v>BUY</x:v>
+        <x:v>购买</x:v>
       </x:c>
       <x:c r="F103" t="str">
-        <x:v>BUY</x:v>
+        <x:v>购买</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2715,16 +2733,16 @@
         <x:v>Buqi.Offer.Details</x:v>
       </x:c>
       <x:c r="C104" t="str">
-        <x:v>DETAILS</x:v>
+        <x:v>详情</x:v>
       </x:c>
       <x:c r="D104" t="str">
-        <x:v>DETAILS</x:v>
+        <x:v>详情</x:v>
       </x:c>
       <x:c r="E104" t="str">
-        <x:v>DETAILS</x:v>
+        <x:v>详情</x:v>
       </x:c>
       <x:c r="F104" t="str">
-        <x:v>DETAILS</x:v>
+        <x:v>详情</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2733,16 +2751,16 @@
         <x:v>Buqi.Offer.Description</x:v>
       </x:c>
       <x:c r="C105" t="str">
-        <x:v>Offer description</x:v>
+        <x:v>查看商品说明</x:v>
       </x:c>
       <x:c r="D105" t="str">
-        <x:v>Offer description</x:v>
+        <x:v>查看商品说明</x:v>
       </x:c>
       <x:c r="E105" t="str">
-        <x:v>Offer description</x:v>
+        <x:v>查看商品说明</x:v>
       </x:c>
       <x:c r="F105" t="str">
-        <x:v>Offer description</x:v>
+        <x:v>查看商品说明</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -2754,13 +2772,13 @@
         <x:v>空置</x:v>
       </x:c>
       <x:c r="D106" t="str">
-        <x:v>Empty</x:v>
+        <x:v>空置</x:v>
       </x:c>
       <x:c r="E106" t="str">
         <x:v>空置</x:v>
       </x:c>
       <x:c r="F106" t="str">
-        <x:v>빈 칸</x:v>
+        <x:v>空置</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -2772,13 +2790,13 @@
         <x:v>主要威胁：公开装备触发关系</x:v>
       </x:c>
       <x:c r="D107" t="str">
-        <x:v>Main threat: public item triggers</x:v>
+        <x:v>主要威胁：公开装备触发关系</x:v>
       </x:c>
       <x:c r="E107" t="str">
-        <x:v>主要威脅：公開裝備觸發關係</x:v>
+        <x:v>主要威胁：公开装备触发关系</x:v>
       </x:c>
       <x:c r="F107" t="str">
-        <x:v>주요 위협: 공개 장비 트리거</x:v>
+        <x:v>主要威胁：公开装备触发关系</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -2790,13 +2808,13 @@
         <x:v>连续 8 格构筑  ·  公开情报</x:v>
       </x:c>
       <x:c r="D108" t="str">
-        <x:v>8-slot formation · Public intel</x:v>
+        <x:v>连续 8 格构筑  ·  公开情报</x:v>
       </x:c>
       <x:c r="E108" t="str">
-        <x:v>連續 8 格構築  ·  公開情報</x:v>
+        <x:v>连续 8 格构筑  ·  公开情报</x:v>
       </x:c>
       <x:c r="F108" t="str">
-        <x:v>연속 8칸 구성 · 공개 정보</x:v>
+        <x:v>连续 8 格构筑  ·  公开情报</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -2808,13 +2826,13 @@
         <x:v>已知风险：未公开改造</x:v>
       </x:c>
       <x:c r="D109" t="str">
-        <x:v>Known risk: hidden refinements</x:v>
+        <x:v>已知风险：未公开改造</x:v>
       </x:c>
       <x:c r="E109" t="str">
-        <x:v>已知風險：未公開改造</x:v>
+        <x:v>已知风险：未公开改造</x:v>
       </x:c>
       <x:c r="F109" t="str">
-        <x:v>알려진 위험: 미공개 개조</x:v>
+        <x:v>已知风险：未公开改造</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2826,13 +2844,13 @@
         <x:v>方向  高速构筑</x:v>
       </x:c>
       <x:c r="D110" t="str">
-        <x:v>Direction: Fast build</x:v>
+        <x:v>方向  高速构筑</x:v>
       </x:c>
       <x:c r="E110" t="str">
-        <x:v>方向  高速構築</x:v>
+        <x:v>方向  高速构筑</x:v>
       </x:c>
       <x:c r="F110" t="str">
-        <x:v>방향: 고속 구성</x:v>
+        <x:v>方向  高速构筑</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2844,13 +2862,13 @@
         <x:v>对手快照</x:v>
       </x:c>
       <x:c r="D111" t="str">
-        <x:v>Opponent Snapshot</x:v>
+        <x:v>对手快照</x:v>
       </x:c>
       <x:c r="E111" t="str">
-        <x:v>對手快照</x:v>
+        <x:v>对手快照</x:v>
       </x:c>
       <x:c r="F111" t="str">
-        <x:v>상대 스냅샷</x:v>
+        <x:v>对手快照</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2862,13 +2880,13 @@
         <x:v>起始选择</x:v>
       </x:c>
       <x:c r="D112" t="str">
-        <x:v>Starting Choice</x:v>
+        <x:v>起始选择</x:v>
       </x:c>
       <x:c r="E112" t="str">
-        <x:v>起始選擇</x:v>
+        <x:v>起始选择</x:v>
       </x:c>
       <x:c r="F112" t="str">
-        <x:v>시작 선택</x:v>
+        <x:v>起始选择</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2934,13 +2952,13 @@
         <x:v>金币</x:v>
       </x:c>
       <x:c r="D116" t="str">
-        <x:v>Coins</x:v>
+        <x:v>金币</x:v>
       </x:c>
       <x:c r="E116" t="str">
-        <x:v>金幣</x:v>
+        <x:v>金币</x:v>
       </x:c>
       <x:c r="F116" t="str">
-        <x:v>코인</x:v>
+        <x:v>金币</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2952,13 +2970,13 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="D117" t="str">
-        <x:v>Normal</x:v>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="E117" t="str">
         <x:v>正常</x:v>
       </x:c>
       <x:c r="F117" t="str">
-        <x:v>정상</x:v>
+        <x:v>正常</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -3003,16 +3021,16 @@
         <x:v>Buqi.Common.DemoTag</x:v>
       </x:c>
       <x:c r="C120" t="str">
-        <x:v>DEMO</x:v>
+        <x:v>试玩版</x:v>
       </x:c>
       <x:c r="D120" t="str">
-        <x:v>DEMO</x:v>
+        <x:v>试玩版</x:v>
       </x:c>
       <x:c r="E120" t="str">
-        <x:v>DEMO</x:v>
+        <x:v>试玩版</x:v>
       </x:c>
       <x:c r="F120" t="str">
-        <x:v>DEMO</x:v>
+        <x:v>试玩版</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -3024,13 +3042,13 @@
         <x:v>选择本局的第一件装备。</x:v>
       </x:c>
       <x:c r="D121" t="str">
-        <x:v>Choose the first item for this run.</x:v>
+        <x:v>选择本局的第一件装备。</x:v>
       </x:c>
       <x:c r="E121" t="str">
-        <x:v>選擇本局的第一件裝備。</x:v>
+        <x:v>选择本局的第一件装备。</x:v>
       </x:c>
       <x:c r="F121" t="str">
-        <x:v>이번 플레이의 첫 장비를 선택하세요.</x:v>
+        <x:v>选择本局的第一件装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -3042,13 +3060,13 @@
         <x:v>只展示公开的棋盘和构筑信息。</x:v>
       </x:c>
       <x:c r="D122" t="str">
-        <x:v>Only public board and build information is shown.</x:v>
+        <x:v>只展示公开的棋盘和构筑信息。</x:v>
       </x:c>
       <x:c r="E122" t="str">
-        <x:v>只展示公開的棋盤和構築資訊。</x:v>
+        <x:v>只展示公开的棋盘和构筑信息。</x:v>
       </x:c>
       <x:c r="F122" t="str">
-        <x:v>공개된 보드와 구성 정보만 표시합니다.</x:v>
+        <x:v>只展示公开的棋盘和构筑信息。</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3060,13 +3078,13 @@
         <x:v>战前准备</x:v>
       </x:c>
       <x:c r="D123" t="str">
-        <x:v>Pre-Battle Preparation</x:v>
+        <x:v>战前准备</x:v>
       </x:c>
       <x:c r="E123" t="str">
-        <x:v>戰前準備</x:v>
+        <x:v>战前准备</x:v>
       </x:c>
       <x:c r="F123" t="str">
-        <x:v>전투 준비</x:v>
+        <x:v>战前准备</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3078,13 +3096,13 @@
         <x:v>选择本回合的准备收益。</x:v>
       </x:c>
       <x:c r="D124" t="str">
-        <x:v>Choose the preparation reward for this round.</x:v>
+        <x:v>选择本回合的准备收益。</x:v>
       </x:c>
       <x:c r="E124" t="str">
-        <x:v>選擇本回合的準備收益。</x:v>
+        <x:v>选择本回合的准备收益。</x:v>
       </x:c>
       <x:c r="F124" t="str">
-        <x:v>이번 라운드의 준비 보상을 선택하세요.</x:v>
+        <x:v>选择本回合的准备收益。</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3096,13 +3114,13 @@
         <x:v>商店</x:v>
       </x:c>
       <x:c r="D125" t="str">
-        <x:v>Shop</x:v>
+        <x:v>商店</x:v>
       </x:c>
       <x:c r="E125" t="str">
         <x:v>商店</x:v>
       </x:c>
       <x:c r="F125" t="str">
-        <x:v>상점</x:v>
+        <x:v>商店</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3114,13 +3132,13 @@
         <x:v>购买装备、刷新或锁定当前报价。</x:v>
       </x:c>
       <x:c r="D126" t="str">
-        <x:v>Buy items, refresh, or lock the current offers.</x:v>
+        <x:v>购买装备、刷新或锁定当前报价。</x:v>
       </x:c>
       <x:c r="E126" t="str">
-        <x:v>購買裝備、刷新或鎖定當前報價。</x:v>
+        <x:v>购买装备、刷新或锁定当前报价。</x:v>
       </x:c>
       <x:c r="F126" t="str">
-        <x:v>장비를 구매하고 새로고침하거나 현재 제안을 잠급니다.</x:v>
+        <x:v>购买装备、刷新或锁定当前报价。</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3132,13 +3150,13 @@
         <x:v>事件</x:v>
       </x:c>
       <x:c r="D127" t="str">
-        <x:v>Event</x:v>
+        <x:v>事件</x:v>
       </x:c>
       <x:c r="E127" t="str">
         <x:v>事件</x:v>
       </x:c>
       <x:c r="F127" t="str">
-        <x:v>이벤트</x:v>
+        <x:v>事件</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3150,13 +3168,13 @@
         <x:v>在收益与风险之间做出选择。</x:v>
       </x:c>
       <x:c r="D128" t="str">
-        <x:v>Choose between reward and risk.</x:v>
+        <x:v>在收益与风险之间做出选择。</x:v>
       </x:c>
       <x:c r="E128" t="str">
-        <x:v>在收益與風險之間做出選擇。</x:v>
+        <x:v>在收益与风险之间做出选择。</x:v>
       </x:c>
       <x:c r="F128" t="str">
-        <x:v>보상과 위험 사이에서 선택하세요.</x:v>
+        <x:v>在收益与风险之间做出选择。</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3168,13 +3186,13 @@
         <x:v>改造</x:v>
       </x:c>
       <x:c r="D129" t="str">
-        <x:v>Modification</x:v>
+        <x:v>改造</x:v>
       </x:c>
       <x:c r="E129" t="str">
         <x:v>改造</x:v>
       </x:c>
       <x:c r="F129" t="str">
-        <x:v>개조</x:v>
+        <x:v>改造</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3186,13 +3204,13 @@
         <x:v>为装备添加收益与代价并存的改造。</x:v>
       </x:c>
       <x:c r="D130" t="str">
-        <x:v>Add a modification that brings both benefits and costs.</x:v>
+        <x:v>为装备添加收益与代价并存的改造。</x:v>
       </x:c>
       <x:c r="E130" t="str">
-        <x:v>為裝備添加收益與代價並存的改造。</x:v>
+        <x:v>为装备添加收益与代价并存的改造。</x:v>
       </x:c>
       <x:c r="F130" t="str">
-        <x:v>장비에 보상과 대가가 공존하는 개조를 추가합니다.</x:v>
+        <x:v>为装备添加收益与代价并存的改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3204,13 +3222,13 @@
         <x:v>棋盘编辑</x:v>
       </x:c>
       <x:c r="D131" t="str">
-        <x:v>Board Editor</x:v>
+        <x:v>棋盘编辑</x:v>
       </x:c>
       <x:c r="E131" t="str">
-        <x:v>棋盤編輯</x:v>
+        <x:v>棋盘编辑</x:v>
       </x:c>
       <x:c r="F131" t="str">
-        <x:v>보드 편집</x:v>
+        <x:v>棋盘编辑</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3222,13 +3240,13 @@
         <x:v>点选装备，再选择 8 格棋盘中的目标位。</x:v>
       </x:c>
       <x:c r="D132" t="str">
-        <x:v>Select an item, then choose a target slot on the 8-slot board.</x:v>
+        <x:v>点选装备，再选择 8 格棋盘中的目标位。</x:v>
       </x:c>
       <x:c r="E132" t="str">
-        <x:v>點選裝備，再選擇 8 格棋盤中的目標位。</x:v>
+        <x:v>点选装备，再选择 8 格棋盘中的目标位。</x:v>
       </x:c>
       <x:c r="F132" t="str">
-        <x:v>장비를 선택한 다음 8칸 보드에서 목표 위치를 선택하세요.</x:v>
+        <x:v>点选装备，再选择 8 格棋盘中的目标位。</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3240,13 +3258,13 @@
         <x:v>胜负预测</x:v>
       </x:c>
       <x:c r="D133" t="str">
-        <x:v>Outcome Prediction</x:v>
+        <x:v>胜负预测</x:v>
       </x:c>
       <x:c r="E133" t="str">
-        <x:v>勝負預測</x:v>
+        <x:v>胜负预测</x:v>
       </x:c>
       <x:c r="F133" t="str">
-        <x:v>승패 예측</x:v>
+        <x:v>胜负预测</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3258,13 +3276,13 @@
         <x:v>战斗前记录你对结果的判断。</x:v>
       </x:c>
       <x:c r="D134" t="str">
-        <x:v>Record your predicted outcome before the battle.</x:v>
+        <x:v>战斗前记录你对结果的判断。</x:v>
       </x:c>
       <x:c r="E134" t="str">
-        <x:v>戰鬥前記錄你對結果的判斷。</x:v>
+        <x:v>战斗前记录你对结果的判断。</x:v>
       </x:c>
       <x:c r="F134" t="str">
-        <x:v>전투 전에 결과에 대한 예측을 기록하세요.</x:v>
+        <x:v>战斗前记录你对结果的判断。</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3276,13 +3294,13 @@
         <x:v>战斗总结</x:v>
       </x:c>
       <x:c r="D135" t="str">
-        <x:v>Battle Summary</x:v>
+        <x:v>战斗总结</x:v>
       </x:c>
       <x:c r="E135" t="str">
-        <x:v>戰鬥總結</x:v>
+        <x:v>战斗总结</x:v>
       </x:c>
       <x:c r="F135" t="str">
-        <x:v>전투 요약</x:v>
+        <x:v>战斗总结</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3294,13 +3312,13 @@
         <x:v>从真实战斗日志中提取可回溯事实。</x:v>
       </x:c>
       <x:c r="D136" t="str">
-        <x:v>Extract traceable facts from the actual battle log.</x:v>
+        <x:v>从真实战斗日志中提取可回溯事实。</x:v>
       </x:c>
       <x:c r="E136" t="str">
-        <x:v>從真實戰鬥日誌中提取可回溯事實。</x:v>
+        <x:v>从真实战斗日志中提取可回溯事实。</x:v>
       </x:c>
       <x:c r="F136" t="str">
-        <x:v>실제 전투 로그에서 추적 가능한 사실을 추출합니다.</x:v>
+        <x:v>从真实战斗日志中提取可回溯事实。</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3312,13 +3330,13 @@
         <x:v>回合结算</x:v>
       </x:c>
       <x:c r="D137" t="str">
-        <x:v>Round Settlement</x:v>
+        <x:v>回合结算</x:v>
       </x:c>
       <x:c r="E137" t="str">
-        <x:v>回合結算</x:v>
+        <x:v>回合结算</x:v>
       </x:c>
       <x:c r="F137" t="str">
-        <x:v>라운드 정산</x:v>
+        <x:v>回合结算</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3330,13 +3348,13 @@
         <x:v>结算胜场、单局生命与金币变化。</x:v>
       </x:c>
       <x:c r="D138" t="str">
-        <x:v>Settle wins, run life, and coin changes.</x:v>
+        <x:v>结算胜场、单局生命与金币变化。</x:v>
       </x:c>
       <x:c r="E138" t="str">
-        <x:v>結算勝場、單局生命與金幣變化。</x:v>
+        <x:v>结算胜场、单局生命与金币变化。</x:v>
       </x:c>
       <x:c r="F138" t="str">
-        <x:v>승리 수, 플레이 생명, 코인 변화를 정산합니다.</x:v>
+        <x:v>结算胜场、单局生命与金币变化。</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3348,13 +3366,13 @@
         <x:v>单局结束</x:v>
       </x:c>
       <x:c r="D139" t="str">
-        <x:v>Run Complete</x:v>
+        <x:v>单局结束</x:v>
       </x:c>
       <x:c r="E139" t="str">
-        <x:v>單局結束</x:v>
+        <x:v>单局结束</x:v>
       </x:c>
       <x:c r="F139" t="str">
-        <x:v>플레이 종료</x:v>
+        <x:v>单局结束</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3366,13 +3384,13 @@
         <x:v>查看本局构筑摘要并重新开始。</x:v>
       </x:c>
       <x:c r="D140" t="str">
-        <x:v>Review this run's build summary and start again.</x:v>
+        <x:v>查看本局构筑摘要并重新开始。</x:v>
       </x:c>
       <x:c r="E140" t="str">
-        <x:v>查看本局構築摘要並重新開始。</x:v>
+        <x:v>查看本局构筑摘要并重新开始。</x:v>
       </x:c>
       <x:c r="F140" t="str">
-        <x:v>이번 플레이의 구성 요약을 확인하고 다시 시작하세요.</x:v>
+        <x:v>查看本局构筑摘要并重新开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3381,16 +3399,16 @@
         <x:v>Buqi.Stage.OperationChoice.Description</x:v>
       </x:c>
       <x:c r="C141" t="str">
-        <x:v>选择坊市、机缘或静修；当前周天保持可见。</x:v>
+        <x:v>选择商店、事件或训练；当前装备栏保持可见。</x:v>
       </x:c>
       <x:c r="D141" t="str">
-        <x:v>Choose the bazaar, an encounter, or cultivation; the current cycle remains visible.</x:v>
+        <x:v>选择商店、事件或训练；当前装备栏保持可见。</x:v>
       </x:c>
       <x:c r="E141" t="str">
-        <x:v>選擇坊市、機緣或靜修；目前周天保持可見。</x:v>
+        <x:v>选择商店、事件或训练；当前装备栏保持可见。</x:v>
       </x:c>
       <x:c r="F141" t="str">
-        <x:v>상점, 기연 또는 수련을 선택하세요. 현재 주천은 계속 표시됩니다.</x:v>
+        <x:v>选择商店、事件或训练；当前装备栏保持可见。</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3402,13 +3420,13 @@
         <x:v>经营选择</x:v>
       </x:c>
       <x:c r="D142" t="str">
-        <x:v>Operation Choice</x:v>
+        <x:v>经营选择</x:v>
       </x:c>
       <x:c r="E142" t="str">
-        <x:v>經營選擇</x:v>
+        <x:v>经营选择</x:v>
       </x:c>
       <x:c r="F142" t="str">
-        <x:v>운영 선택</x:v>
+        <x:v>经营选择</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3417,16 +3435,16 @@
         <x:v>Buqi.Stage.PveSelection.Description</x:v>
       </x:c>
       <x:c r="C143" t="str">
-        <x:v>选择初阶、进阶或险阶后直接进入战斗。</x:v>
+        <x:v>选择初级、中级或高难挑战后直接进入战斗。</x:v>
       </x:c>
       <x:c r="D143" t="str">
-        <x:v>Choose Novice, Advanced, or Perilous, then enter battle.</x:v>
+        <x:v>选择初级、中级或高难挑战后直接进入战斗。</x:v>
       </x:c>
       <x:c r="E143" t="str">
-        <x:v>選擇初階、進階或險階後直接進入戰鬥。</x:v>
+        <x:v>选择初级、中级或高难挑战后直接进入战斗。</x:v>
       </x:c>
       <x:c r="F143" t="str">
-        <x:v>초급, 중급 또는 위험 단계를 선택한 뒤 바로 전투에 진입하세요.</x:v>
+        <x:v>选择初级、中级或高难挑战后直接进入战斗。</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3435,16 +3453,16 @@
         <x:v>Buqi.Stage.PveSelection.Title</x:v>
       </x:c>
       <x:c r="C144" t="str">
-        <x:v>PVE 选关</x:v>
+        <x:v>电脑对战选择</x:v>
       </x:c>
       <x:c r="D144" t="str">
-        <x:v>PVE Selection</x:v>
+        <x:v>电脑对战选择</x:v>
       </x:c>
       <x:c r="E144" t="str">
-        <x:v>PVE 選關</x:v>
+        <x:v>电脑对战选择</x:v>
       </x:c>
       <x:c r="F144" t="str">
-        <x:v>PVE 선택</x:v>
+        <x:v>电脑对战选择</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3453,16 +3471,16 @@
         <x:v>Buqi.Stage.TribulationRoute.Description</x:v>
       </x:c>
       <x:c r="C145" t="str">
-        <x:v>九日夜战后选择一条渡劫路线。</x:v>
+        <x:v>第九回合战斗后选择一条最终挑战路线。</x:v>
       </x:c>
       <x:c r="D145" t="str">
-        <x:v>After the ninth night's battle, choose a tribulation route.</x:v>
+        <x:v>第九回合战斗后选择一条最终挑战路线。</x:v>
       </x:c>
       <x:c r="E145" t="str">
-        <x:v>九日夜戰後選擇一條渡劫路線。</x:v>
+        <x:v>第九回合战斗后选择一条最终挑战路线。</x:v>
       </x:c>
       <x:c r="F145" t="str">
-        <x:v>9일째 야간 전투 후 천겁 경로를 하나 선택하세요.</x:v>
+        <x:v>第九回合战斗后选择一条最终挑战路线。</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3471,16 +3489,16 @@
         <x:v>Buqi.Stage.TribulationRoute.Title</x:v>
       </x:c>
       <x:c r="C146" t="str">
-        <x:v>渡劫路线</x:v>
+        <x:v>最终挑战路线 · 九日试炼</x:v>
       </x:c>
       <x:c r="D146" t="str">
-        <x:v>Tribulation Route</x:v>
+        <x:v>最终挑战路线 · 九日试炼</x:v>
       </x:c>
       <x:c r="E146" t="str">
-        <x:v>渡劫路線</x:v>
+        <x:v>最终挑战路线 · 九日试炼</x:v>
       </x:c>
       <x:c r="F146" t="str">
-        <x:v>천겁 경로</x:v>
+        <x:v>最终挑战路线 · 九日试炼</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3489,16 +3507,16 @@
         <x:v>Buqi.Stage.TribulationStage.Description</x:v>
       </x:c>
       <x:c r="C147" t="str">
-        <x:v>应劫并推进当前阶段。</x:v>
+        <x:v>完成挑战并推进当前阶段。</x:v>
       </x:c>
       <x:c r="D147" t="str">
-        <x:v>Face the tribulation and advance the current stage.</x:v>
+        <x:v>完成挑战并推进当前阶段。</x:v>
       </x:c>
       <x:c r="E147" t="str">
-        <x:v>應劫並推進目前階段。</x:v>
+        <x:v>完成挑战并推进当前阶段。</x:v>
       </x:c>
       <x:c r="F147" t="str">
-        <x:v>천겁에 맞서 현재 단계를 진행하세요.</x:v>
+        <x:v>完成挑战并推进当前阶段。</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3507,16 +3525,16 @@
         <x:v>Buqi.Stage.TribulationStage.Title</x:v>
       </x:c>
       <x:c r="C148" t="str">
-        <x:v>三阶段天劫</x:v>
+        <x:v>三阶段挑战 · 天劫</x:v>
       </x:c>
       <x:c r="D148" t="str">
-        <x:v>Three-Stage Tribulation</x:v>
+        <x:v>三阶段挑战 · 天劫</x:v>
       </x:c>
       <x:c r="E148" t="str">
-        <x:v>三階段天劫</x:v>
+        <x:v>三阶段挑战 · 天劫</x:v>
       </x:c>
       <x:c r="F148" t="str">
-        <x:v>3단계 천겁</x:v>
+        <x:v>三阶段挑战 · 天劫</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3528,13 +3546,13 @@
         <x:v>日记录</x:v>
       </x:c>
       <x:c r="D149" t="str">
-        <x:v>Day Record</x:v>
+        <x:v>日记录</x:v>
       </x:c>
       <x:c r="E149" t="str">
-        <x:v>日記錄</x:v>
+        <x:v>日记录</x:v>
       </x:c>
       <x:c r="F149" t="str">
-        <x:v>일일 기록</x:v>
+        <x:v>日记录</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3543,16 +3561,16 @@
         <x:v>Buqi.RunShell.MorningOperation</x:v>
       </x:c>
       <x:c r="C150" t="str">
-        <x:v>晨 · 经营</x:v>
+        <x:v>晨 · 经营阶段</x:v>
       </x:c>
       <x:c r="D150" t="str">
-        <x:v>Morning · Operation</x:v>
+        <x:v>晨 · 经营阶段</x:v>
       </x:c>
       <x:c r="E150" t="str">
-        <x:v>晨 · 經營</x:v>
+        <x:v>晨 · 经营阶段</x:v>
       </x:c>
       <x:c r="F150" t="str">
-        <x:v>아침 · 경영</x:v>
+        <x:v>晨 · 经营阶段</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3561,16 +3579,16 @@
         <x:v>Buqi.RunShell.NoonOperation</x:v>
       </x:c>
       <x:c r="C151" t="str">
-        <x:v>昼 · 经营</x:v>
+        <x:v>昼 · 经营阶段</x:v>
       </x:c>
       <x:c r="D151" t="str">
-        <x:v>Noon · Operation</x:v>
+        <x:v>昼 · 经营阶段</x:v>
       </x:c>
       <x:c r="E151" t="str">
-        <x:v>晝 · 經營</x:v>
+        <x:v>昼 · 经营阶段</x:v>
       </x:c>
       <x:c r="F151" t="str">
-        <x:v>낮 · 경영</x:v>
+        <x:v>昼 · 经营阶段</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3579,16 +3597,16 @@
         <x:v>Buqi.RunShell.DuskPve</x:v>
       </x:c>
       <x:c r="C152" t="str">
-        <x:v>昏 · PVE</x:v>
+        <x:v>昏 · 电脑对战</x:v>
       </x:c>
       <x:c r="D152" t="str">
-        <x:v>Dusk · PVE</x:v>
+        <x:v>昏 · 电脑对战</x:v>
       </x:c>
       <x:c r="E152" t="str">
-        <x:v>昏 · PVE</x:v>
+        <x:v>昏 · 电脑对战</x:v>
       </x:c>
       <x:c r="F152" t="str">
-        <x:v>해질녘 · PVE</x:v>
+        <x:v>昏 · 电脑对战</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3597,16 +3615,16 @@
         <x:v>Buqi.RunShell.NightPvp</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>夜 · 异步 PVP</x:v>
+        <x:v>夜 · 异步对战</x:v>
       </x:c>
       <x:c r="D153" t="str">
-        <x:v>Night · Async PVP</x:v>
+        <x:v>夜 · 异步对战</x:v>
       </x:c>
       <x:c r="E153" t="str">
-        <x:v>夜 · 非同步 PVP</x:v>
+        <x:v>夜 · 异步对战</x:v>
       </x:c>
       <x:c r="F153" t="str">
-        <x:v>밤 · 비동기 PVP</x:v>
+        <x:v>夜 · 异步对战</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3615,16 +3633,16 @@
         <x:v>Buqi.Stage.Shared.CurrentBoard</x:v>
       </x:c>
       <x:c r="C154" t="str">
-        <x:v>当前周天</x:v>
+        <x:v>当前装备栏</x:v>
       </x:c>
       <x:c r="D154" t="str">
-        <x:v>Current Cycle Board</x:v>
+        <x:v>当前装备栏</x:v>
       </x:c>
       <x:c r="E154" t="str">
-        <x:v>當前周天</x:v>
+        <x:v>当前装备栏</x:v>
       </x:c>
       <x:c r="F154" t="str">
-        <x:v>현재 주천</x:v>
+        <x:v>当前装备栏</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3636,13 +3654,13 @@
         <x:v>急攻令</x:v>
       </x:c>
       <x:c r="D155" t="str">
-        <x:v>Rapid Writ</x:v>
+        <x:v>急攻令</x:v>
       </x:c>
       <x:c r="E155" t="str">
         <x:v>急攻令</x:v>
       </x:c>
       <x:c r="F155" t="str">
-        <x:v>Rapid Writ</x:v>
+        <x:v>急攻令</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3651,16 +3669,16 @@
         <x:v>Buqi.Content.Item.W8_003.Upgrade</x:v>
       </x:c>
       <x:c r="C156" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D156" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E156" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F156" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -3672,13 +3690,13 @@
         <x:v>冲锋看板</x:v>
       </x:c>
       <x:c r="D157" t="str">
-        <x:v>Charge Ledger</x:v>
+        <x:v>冲锋看板</x:v>
       </x:c>
       <x:c r="E157" t="str">
         <x:v>冲锋看板</x:v>
       </x:c>
       <x:c r="F157" t="str">
-        <x:v>Charge Ledger</x:v>
+        <x:v>冲锋看板</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -3687,16 +3705,16 @@
         <x:v>Buqi.Content.Item.W8_005.Upgrade</x:v>
       </x:c>
       <x:c r="C158" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D158" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E158" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F158" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -3708,13 +3726,13 @@
         <x:v>终局重锤</x:v>
       </x:c>
       <x:c r="D159" t="str">
-        <x:v>Final Maul</x:v>
+        <x:v>终局重锤</x:v>
       </x:c>
       <x:c r="E159" t="str">
         <x:v>终局重锤</x:v>
       </x:c>
       <x:c r="F159" t="str">
-        <x:v>Final Maul</x:v>
+        <x:v>终局重锤</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3723,16 +3741,16 @@
         <x:v>Buqi.Content.Item.W8_006.Upgrade</x:v>
       </x:c>
       <x:c r="C160" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D160" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E160" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F160" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -3744,13 +3762,13 @@
         <x:v>小护盾</x:v>
       </x:c>
       <x:c r="D161" t="str">
-        <x:v>Ward Tile</x:v>
+        <x:v>小护盾</x:v>
       </x:c>
       <x:c r="E161" t="str">
         <x:v>小护盾</x:v>
       </x:c>
       <x:c r="F161" t="str">
-        <x:v>Ward Tile</x:v>
+        <x:v>小护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -3759,16 +3777,16 @@
         <x:v>Buqi.Content.Item.W8_007.Upgrade</x:v>
       </x:c>
       <x:c r="C162" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D162" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E162" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F162" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -3780,13 +3798,13 @@
         <x:v>破盾清单</x:v>
       </x:c>
       <x:c r="D163" t="str">
-        <x:v>Rupture List</x:v>
+        <x:v>破盾清单</x:v>
       </x:c>
       <x:c r="E163" t="str">
         <x:v>破盾清单</x:v>
       </x:c>
       <x:c r="F163" t="str">
-        <x:v>Rupture List</x:v>
+        <x:v>破盾清单</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -3795,16 +3813,16 @@
         <x:v>Buqi.Content.Item.W8_008.Upgrade</x:v>
       </x:c>
       <x:c r="C164" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D164" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E164" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F164" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -3816,13 +3834,13 @@
         <x:v>堡垒核心</x:v>
       </x:c>
       <x:c r="D165" t="str">
-        <x:v>Bastion Core</x:v>
+        <x:v>堡垒核心</x:v>
       </x:c>
       <x:c r="E165" t="str">
         <x:v>堡垒核心</x:v>
       </x:c>
       <x:c r="F165" t="str">
-        <x:v>Bastion Core</x:v>
+        <x:v>堡垒核心</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -3831,16 +3849,16 @@
         <x:v>Buqi.Content.Item.W8_012.Upgrade</x:v>
       </x:c>
       <x:c r="C166" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D166" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E166" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F166" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -3852,13 +3870,13 @@
         <x:v>传能接线</x:v>
       </x:c>
       <x:c r="D167" t="str">
-        <x:v>Conduction Lead</x:v>
+        <x:v>传能接线</x:v>
       </x:c>
       <x:c r="E167" t="str">
         <x:v>传能接线</x:v>
       </x:c>
       <x:c r="F167" t="str">
-        <x:v>Conduction Lead</x:v>
+        <x:v>传能接线</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -3867,16 +3885,16 @@
         <x:v>Buqi.Content.Item.W8_013.Upgrade</x:v>
       </x:c>
       <x:c r="C168" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D168" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E168" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F168" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -3888,13 +3906,13 @@
         <x:v>连击印</x:v>
       </x:c>
       <x:c r="D169" t="str">
-        <x:v>Chain Seal</x:v>
+        <x:v>连击印</x:v>
       </x:c>
       <x:c r="E169" t="str">
         <x:v>连击印</x:v>
       </x:c>
       <x:c r="F169" t="str">
-        <x:v>Chain Seal</x:v>
+        <x:v>连击印</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -3903,16 +3921,16 @@
         <x:v>Buqi.Content.Item.W8_014.Upgrade</x:v>
       </x:c>
       <x:c r="C170" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D170" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E170" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F170" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -3924,13 +3942,13 @@
         <x:v>节奏节点</x:v>
       </x:c>
       <x:c r="D171" t="str">
-        <x:v>Cadence Node</x:v>
+        <x:v>节奏节点</x:v>
       </x:c>
       <x:c r="E171" t="str">
         <x:v>节奏节点</x:v>
       </x:c>
       <x:c r="F171" t="str">
-        <x:v>Cadence Node</x:v>
+        <x:v>节奏节点</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -3939,16 +3957,16 @@
         <x:v>Buqi.Content.Item.W8_015.Upgrade</x:v>
       </x:c>
       <x:c r="C172" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D172" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E172" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F172" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -3960,13 +3978,13 @@
         <x:v>急救包</x:v>
       </x:c>
       <x:c r="D173" t="str">
-        <x:v>First Aid Satchel</x:v>
+        <x:v>急救包</x:v>
       </x:c>
       <x:c r="E173" t="str">
         <x:v>急救包</x:v>
       </x:c>
       <x:c r="F173" t="str">
-        <x:v>First Aid Satchel</x:v>
+        <x:v>急救包</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -3975,16 +3993,16 @@
         <x:v>Buqi.Content.Item.W8_016.Upgrade</x:v>
       </x:c>
       <x:c r="C174" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D174" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E174" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F174" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -3996,13 +4014,13 @@
         <x:v>回春泉</x:v>
       </x:c>
       <x:c r="D175" t="str">
-        <x:v>Renewal Spring</x:v>
+        <x:v>回春泉</x:v>
       </x:c>
       <x:c r="E175" t="str">
         <x:v>回春泉</x:v>
       </x:c>
       <x:c r="F175" t="str">
-        <x:v>Renewal Spring</x:v>
+        <x:v>回春泉</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4011,16 +4029,16 @@
         <x:v>Buqi.Content.Item.W8_017.Upgrade</x:v>
       </x:c>
       <x:c r="C176" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D176" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E176" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F176" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4032,13 +4050,13 @@
         <x:v>救援旗</x:v>
       </x:c>
       <x:c r="D177" t="str">
-        <x:v>Rescue Banner</x:v>
+        <x:v>救援旗</x:v>
       </x:c>
       <x:c r="E177" t="str">
         <x:v>救援旗</x:v>
       </x:c>
       <x:c r="F177" t="str">
-        <x:v>Rescue Banner</x:v>
+        <x:v>救援旗</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4047,16 +4065,16 @@
         <x:v>Buqi.Content.Item.W8_018.Upgrade</x:v>
       </x:c>
       <x:c r="C178" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D178" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E178" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F178" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -4068,13 +4086,13 @@
         <x:v>毒针</x:v>
       </x:c>
       <x:c r="D179" t="str">
-        <x:v>Venom Needle</x:v>
+        <x:v>毒针</x:v>
       </x:c>
       <x:c r="E179" t="str">
         <x:v>毒针</x:v>
       </x:c>
       <x:c r="F179" t="str">
-        <x:v>Venom Needle</x:v>
+        <x:v>毒针</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -4083,16 +4101,16 @@
         <x:v>Buqi.Content.Item.W8_019.Upgrade</x:v>
       </x:c>
       <x:c r="C180" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D180" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E180" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F180" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -4104,13 +4122,13 @@
         <x:v>腐蚀瓶</x:v>
       </x:c>
       <x:c r="D181" t="str">
-        <x:v>Corrosion Flask</x:v>
+        <x:v>腐蚀瓶</x:v>
       </x:c>
       <x:c r="E181" t="str">
         <x:v>腐蚀瓶</x:v>
       </x:c>
       <x:c r="F181" t="str">
-        <x:v>Corrosion Flask</x:v>
+        <x:v>腐蚀瓶</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -4119,16 +4137,16 @@
         <x:v>Buqi.Content.Item.W8_020.Upgrade</x:v>
       </x:c>
       <x:c r="C182" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D182" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E182" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F182" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -4140,13 +4158,13 @@
         <x:v>毒雾炉</x:v>
       </x:c>
       <x:c r="D183" t="str">
-        <x:v>Miasma Furnace</x:v>
+        <x:v>毒雾炉</x:v>
       </x:c>
       <x:c r="E183" t="str">
         <x:v>毒雾炉</x:v>
       </x:c>
       <x:c r="F183" t="str">
-        <x:v>Miasma Furnace</x:v>
+        <x:v>毒雾炉</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -4155,16 +4173,16 @@
         <x:v>Buqi.Content.Item.W8_021.Upgrade</x:v>
       </x:c>
       <x:c r="C184" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D184" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E184" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F184" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -4176,13 +4194,13 @@
         <x:v>火花符</x:v>
       </x:c>
       <x:c r="D185" t="str">
-        <x:v>Spark Talisman</x:v>
+        <x:v>火花符</x:v>
       </x:c>
       <x:c r="E185" t="str">
         <x:v>火花符</x:v>
       </x:c>
       <x:c r="F185" t="str">
-        <x:v>Spark Talisman</x:v>
+        <x:v>火花符</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -4191,16 +4209,16 @@
         <x:v>Buqi.Content.Item.W8_022.Upgrade</x:v>
       </x:c>
       <x:c r="C186" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D186" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E186" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F186" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -4212,13 +4230,13 @@
         <x:v>炽焰炉</x:v>
       </x:c>
       <x:c r="D187" t="str">
-        <x:v>Ember Furnace</x:v>
+        <x:v>炽焰炉</x:v>
       </x:c>
       <x:c r="E187" t="str">
         <x:v>炽焰炉</x:v>
       </x:c>
       <x:c r="F187" t="str">
-        <x:v>Ember Furnace</x:v>
+        <x:v>炽焰炉</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -4227,16 +4245,16 @@
         <x:v>Buqi.Content.Item.W8_023.Upgrade</x:v>
       </x:c>
       <x:c r="C188" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D188" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E188" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F188" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -4248,13 +4266,13 @@
         <x:v>爆燃阵</x:v>
       </x:c>
       <x:c r="D189" t="str">
-        <x:v>Flashfire Array</x:v>
+        <x:v>爆燃阵</x:v>
       </x:c>
       <x:c r="E189" t="str">
         <x:v>爆燃阵</x:v>
       </x:c>
       <x:c r="F189" t="str">
-        <x:v>Flashfire Array</x:v>
+        <x:v>爆燃阵</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -4263,16 +4281,16 @@
         <x:v>Buqi.Content.Item.W8_024.Upgrade</x:v>
       </x:c>
       <x:c r="C190" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D190" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E190" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F190" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -4284,13 +4302,13 @@
         <x:v>寒镜</x:v>
       </x:c>
       <x:c r="D191" t="str">
-        <x:v>Frost Mirror</x:v>
+        <x:v>寒镜</x:v>
       </x:c>
       <x:c r="E191" t="str">
         <x:v>寒镜</x:v>
       </x:c>
       <x:c r="F191" t="str">
-        <x:v>Frost Mirror</x:v>
+        <x:v>寒镜</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -4299,16 +4317,16 @@
         <x:v>Buqi.Content.Item.W8_025.Upgrade</x:v>
       </x:c>
       <x:c r="C192" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D192" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E192" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F192" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -4320,13 +4338,13 @@
         <x:v>霜锁</x:v>
       </x:c>
       <x:c r="D193" t="str">
-        <x:v>Rime Lock</x:v>
+        <x:v>霜锁</x:v>
       </x:c>
       <x:c r="E193" t="str">
         <x:v>霜锁</x:v>
       </x:c>
       <x:c r="F193" t="str">
-        <x:v>Rime Lock</x:v>
+        <x:v>霜锁</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -4335,16 +4353,16 @@
         <x:v>Buqi.Content.Item.W8_026.Upgrade</x:v>
       </x:c>
       <x:c r="C194" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D194" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E194" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F194" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -4356,13 +4374,13 @@
         <x:v>冰封塔</x:v>
       </x:c>
       <x:c r="D195" t="str">
-        <x:v>Icebound Tower</x:v>
+        <x:v>冰封塔</x:v>
       </x:c>
       <x:c r="E195" t="str">
         <x:v>冰封塔</x:v>
       </x:c>
       <x:c r="F195" t="str">
-        <x:v>Icebound Tower</x:v>
+        <x:v>冰封塔</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -4371,16 +4389,16 @@
         <x:v>Buqi.Content.Item.W8_027.Upgrade</x:v>
       </x:c>
       <x:c r="C196" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D196" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E196" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F196" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -4392,13 +4410,13 @@
         <x:v>过载电池</x:v>
       </x:c>
       <x:c r="D197" t="str">
-        <x:v>Overload Cell</x:v>
+        <x:v>过载电池</x:v>
       </x:c>
       <x:c r="E197" t="str">
         <x:v>过载电池</x:v>
       </x:c>
       <x:c r="F197" t="str">
-        <x:v>Overload Cell</x:v>
+        <x:v>过载电池</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -4407,16 +4425,16 @@
         <x:v>Buqi.Content.Item.W8_028.Upgrade</x:v>
       </x:c>
       <x:c r="C198" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D198" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E198" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F198" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -4428,13 +4446,13 @@
         <x:v>泄压阀</x:v>
       </x:c>
       <x:c r="D199" t="str">
-        <x:v>Relief Valve</x:v>
+        <x:v>泄压阀</x:v>
       </x:c>
       <x:c r="E199" t="str">
         <x:v>泄压阀</x:v>
       </x:c>
       <x:c r="F199" t="str">
-        <x:v>Relief Valve</x:v>
+        <x:v>泄压阀</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -4443,16 +4461,16 @@
         <x:v>Buqi.Content.Item.W8_029.Upgrade</x:v>
       </x:c>
       <x:c r="C200" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D200" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E200" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F200" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -4464,13 +4482,13 @@
         <x:v>稳压核心</x:v>
       </x:c>
       <x:c r="D201" t="str">
-        <x:v>Stability Core</x:v>
+        <x:v>稳压核心</x:v>
       </x:c>
       <x:c r="E201" t="str">
         <x:v>稳压核心</x:v>
       </x:c>
       <x:c r="F201" t="str">
-        <x:v>Stability Core</x:v>
+        <x:v>稳压核心</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -4479,16 +4497,16 @@
         <x:v>Buqi.Content.Item.W8_030.Upgrade</x:v>
       </x:c>
       <x:c r="C202" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D202" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E202" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F202" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -4500,13 +4518,13 @@
         <x:v>走马铃</x:v>
       </x:c>
       <x:c r="D203" t="str">
-        <x:v>Gallop Bell</x:v>
+        <x:v>走马铃</x:v>
       </x:c>
       <x:c r="E203" t="str">
         <x:v>走马铃</x:v>
       </x:c>
       <x:c r="F203" t="str">
-        <x:v>Gallop Bell</x:v>
+        <x:v>走马铃</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -4515,16 +4533,16 @@
         <x:v>Buqi.Content.Item.W8_031.Upgrade</x:v>
       </x:c>
       <x:c r="C204" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D204" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E204" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F204" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -4536,13 +4554,13 @@
         <x:v>借势扣</x:v>
       </x:c>
       <x:c r="D205" t="str">
-        <x:v>Borrowed Force Clasp</x:v>
+        <x:v>借势扣</x:v>
       </x:c>
       <x:c r="E205" t="str">
         <x:v>借势扣</x:v>
       </x:c>
       <x:c r="F205" t="str">
-        <x:v>Borrowed Force Clasp</x:v>
+        <x:v>借势扣</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -4551,16 +4569,16 @@
         <x:v>Buqi.Content.Item.W8_032.Upgrade</x:v>
       </x:c>
       <x:c r="C206" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D206" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E206" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F206" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -4572,13 +4590,13 @@
         <x:v>回锋匣</x:v>
       </x:c>
       <x:c r="D207" t="str">
-        <x:v>Returning Edge Coffer</x:v>
+        <x:v>回锋匣</x:v>
       </x:c>
       <x:c r="E207" t="str">
         <x:v>回锋匣</x:v>
       </x:c>
       <x:c r="F207" t="str">
-        <x:v>Returning Edge Coffer</x:v>
+        <x:v>回锋匣</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -4587,16 +4605,16 @@
         <x:v>Buqi.Content.Item.W8_033.Upgrade</x:v>
       </x:c>
       <x:c r="C208" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D208" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E208" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F208" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -4608,13 +4626,13 @@
         <x:v>破阵锥</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Formation Spike</x:v>
+        <x:v>破阵锥</x:v>
       </x:c>
       <x:c r="E209" t="str">
         <x:v>破阵锥</x:v>
       </x:c>
       <x:c r="F209" t="str">
-        <x:v>Formation Spike</x:v>
+        <x:v>破阵锥</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -4623,16 +4641,16 @@
         <x:v>Buqi.Content.Item.W8_034.Upgrade</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E210" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F210" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -4644,13 +4662,13 @@
         <x:v>试锋算盘</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Trial Abacus</x:v>
+        <x:v>试锋算盘</x:v>
       </x:c>
       <x:c r="E211" t="str">
         <x:v>试锋算盘</x:v>
       </x:c>
       <x:c r="F211" t="str">
-        <x:v>Trial Abacus</x:v>
+        <x:v>试锋算盘</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -4659,16 +4677,16 @@
         <x:v>Buqi.Content.Item.W8_035.Upgrade</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E212" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F212" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -4680,13 +4698,13 @@
         <x:v>连垣扣</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Linked Rampart Clasp</x:v>
+        <x:v>连垣扣</x:v>
       </x:c>
       <x:c r="E213" t="str">
         <x:v>连垣扣</x:v>
       </x:c>
       <x:c r="F213" t="str">
-        <x:v>Linked Rampart Clasp</x:v>
+        <x:v>连垣扣</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -4695,16 +4713,16 @@
         <x:v>Buqi.Content.Item.W8_036.Upgrade</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E214" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F214" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -4716,13 +4734,13 @@
         <x:v>蓄势砚</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Stored Force Inkstone</x:v>
+        <x:v>蓄势砚</x:v>
       </x:c>
       <x:c r="E215" t="str">
         <x:v>蓄势砚</x:v>
       </x:c>
       <x:c r="F215" t="str">
-        <x:v>Stored Force Inkstone</x:v>
+        <x:v>蓄势砚</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -4731,16 +4749,16 @@
         <x:v>Buqi.Content.Item.W8_037.Upgrade</x:v>
       </x:c>
       <x:c r="C216" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E216" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F216" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -4752,13 +4770,13 @@
         <x:v>活门甲</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Living Gate Armor</x:v>
+        <x:v>活门甲</x:v>
       </x:c>
       <x:c r="E217" t="str">
         <x:v>活门甲</x:v>
       </x:c>
       <x:c r="F217" t="str">
-        <x:v>Living Gate Armor</x:v>
+        <x:v>活门甲</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -4767,16 +4785,16 @@
         <x:v>Buqi.Content.Item.W8_038.Upgrade</x:v>
       </x:c>
       <x:c r="C218" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E218" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F218" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -4788,13 +4806,13 @@
         <x:v>净脉璧</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Clear Vein Jade</x:v>
+        <x:v>净脉璧</x:v>
       </x:c>
       <x:c r="E219" t="str">
         <x:v>净脉璧</x:v>
       </x:c>
       <x:c r="F219" t="str">
-        <x:v>Clear Vein Jade</x:v>
+        <x:v>净脉璧</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -4803,16 +4821,16 @@
         <x:v>Buqi.Content.Item.W8_039.Upgrade</x:v>
       </x:c>
       <x:c r="C220" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D220" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E220" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F220" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -4824,13 +4842,13 @@
         <x:v>守成印</x:v>
       </x:c>
       <x:c r="D221" t="str">
-        <x:v>Steadfast Seal</x:v>
+        <x:v>守成印</x:v>
       </x:c>
       <x:c r="E221" t="str">
         <x:v>守成印</x:v>
       </x:c>
       <x:c r="F221" t="str">
-        <x:v>Steadfast Seal</x:v>
+        <x:v>守成印</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -4839,16 +4857,16 @@
         <x:v>Buqi.Content.Item.W8_040.Upgrade</x:v>
       </x:c>
       <x:c r="C222" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D222" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E222" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F222" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -4860,13 +4878,13 @@
         <x:v>续脉灯</x:v>
       </x:c>
       <x:c r="D223" t="str">
-        <x:v>Pulse Lantern</x:v>
+        <x:v>续脉灯</x:v>
       </x:c>
       <x:c r="E223" t="str">
         <x:v>续脉灯</x:v>
       </x:c>
       <x:c r="F223" t="str">
-        <x:v>Pulse Lantern</x:v>
+        <x:v>续脉灯</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -4875,16 +4893,16 @@
         <x:v>Buqi.Content.Item.W8_041.Upgrade</x:v>
       </x:c>
       <x:c r="C224" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D224" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E224" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F224" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -4896,13 +4914,13 @@
         <x:v>调息枢</x:v>
       </x:c>
       <x:c r="D225" t="str">
-        <x:v>Breath Pivot</x:v>
+        <x:v>调息枢</x:v>
       </x:c>
       <x:c r="E225" t="str">
         <x:v>调息枢</x:v>
       </x:c>
       <x:c r="F225" t="str">
-        <x:v>Breath Pivot</x:v>
+        <x:v>调息枢</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -4911,16 +4929,16 @@
         <x:v>Buqi.Content.Item.W8_042.Upgrade</x:v>
       </x:c>
       <x:c r="C226" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D226" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E226" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F226" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -4932,13 +4950,13 @@
         <x:v>回光鉴</x:v>
       </x:c>
       <x:c r="D227" t="str">
-        <x:v>Last Light Mirror</x:v>
+        <x:v>回光鉴</x:v>
       </x:c>
       <x:c r="E227" t="str">
         <x:v>回光鉴</x:v>
       </x:c>
       <x:c r="F227" t="str">
-        <x:v>Last Light Mirror</x:v>
+        <x:v>回光鉴</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -4947,16 +4965,16 @@
         <x:v>Buqi.Content.Item.W8_043.Upgrade</x:v>
       </x:c>
       <x:c r="C228" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D228" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E228" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F228" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -4968,13 +4986,13 @@
         <x:v>护命佩</x:v>
       </x:c>
       <x:c r="D229" t="str">
-        <x:v>Life Guard Pendant</x:v>
+        <x:v>护命佩</x:v>
       </x:c>
       <x:c r="E229" t="str">
         <x:v>护命佩</x:v>
       </x:c>
       <x:c r="F229" t="str">
-        <x:v>Life Guard Pendant</x:v>
+        <x:v>护命佩</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -4983,16 +5001,16 @@
         <x:v>Buqi.Content.Item.W8_044.Upgrade</x:v>
       </x:c>
       <x:c r="C230" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D230" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E230" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F230" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -5004,13 +5022,13 @@
         <x:v>药引秤</x:v>
       </x:c>
       <x:c r="D231" t="str">
-        <x:v>Catalyst Scale</x:v>
+        <x:v>药引秤</x:v>
       </x:c>
       <x:c r="E231" t="str">
         <x:v>药引秤</x:v>
       </x:c>
       <x:c r="F231" t="str">
-        <x:v>Catalyst Scale</x:v>
+        <x:v>药引秤</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -5019,16 +5037,16 @@
         <x:v>Buqi.Content.Item.W8_045.Upgrade</x:v>
       </x:c>
       <x:c r="C232" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D232" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E232" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F232" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -5040,13 +5058,13 @@
         <x:v>同调尺</x:v>
       </x:c>
       <x:c r="D233" t="str">
-        <x:v>Resonance Rule</x:v>
+        <x:v>同调尺</x:v>
       </x:c>
       <x:c r="E233" t="str">
         <x:v>同调尺</x:v>
       </x:c>
       <x:c r="F233" t="str">
-        <x:v>Resonance Rule</x:v>
+        <x:v>同调尺</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -5055,16 +5073,16 @@
         <x:v>Buqi.Content.Item.W8_046.Upgrade</x:v>
       </x:c>
       <x:c r="C234" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D234" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E234" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F234" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -5076,13 +5094,13 @@
         <x:v>行脚账</x:v>
       </x:c>
       <x:c r="D235" t="str">
-        <x:v>Wayfarer Ledger</x:v>
+        <x:v>行脚账</x:v>
       </x:c>
       <x:c r="E235" t="str">
         <x:v>行脚账</x:v>
       </x:c>
       <x:c r="F235" t="str">
-        <x:v>Wayfarer Ledger</x:v>
+        <x:v>行脚账</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -5091,16 +5109,16 @@
         <x:v>Buqi.Content.Item.W8_047.Upgrade</x:v>
       </x:c>
       <x:c r="C236" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D236" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E236" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F236" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -5112,13 +5130,13 @@
         <x:v>镇心铃</x:v>
       </x:c>
       <x:c r="D237" t="str">
-        <x:v>Calming Bell</x:v>
+        <x:v>镇心铃</x:v>
       </x:c>
       <x:c r="E237" t="str">
         <x:v>镇心铃</x:v>
       </x:c>
       <x:c r="F237" t="str">
-        <x:v>Calming Bell</x:v>
+        <x:v>镇心铃</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -5127,16 +5145,16 @@
         <x:v>Buqi.Content.Item.W8_048.Upgrade</x:v>
       </x:c>
       <x:c r="C238" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="D238" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="E238" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="F238" t="str">
-        <x:v>Improved scales effect values to 1.6x; Fixed scales them to 2.4x; cooldown is unchanged.</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -5145,16 +5163,16 @@
         <x:v>Buqi.Content.Merchant.merchant_edge.Name</x:v>
       </x:c>
       <x:c r="C239" t="str">
-        <x:v>砺锋散人·陆铮</x:v>
+        <x:v>攻击装备商人 · 陆铮</x:v>
       </x:c>
       <x:c r="D239" t="str">
-        <x:v>Edge Hermit Lu Zheng</x:v>
+        <x:v>攻击装备商人 · 陆铮</x:v>
       </x:c>
       <x:c r="E239" t="str">
-        <x:v>砺锋散人·陆铮</x:v>
+        <x:v>攻击装备商人 · 陆铮</x:v>
       </x:c>
       <x:c r="F239" t="str">
-        <x:v>Edge Hermit Lu Zheng</x:v>
+        <x:v>攻击装备商人 · 陆铮</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -5163,16 +5181,16 @@
         <x:v>Buqi.Content.Merchant.merchant_bastion.Name</x:v>
       </x:c>
       <x:c r="C240" t="str">
-        <x:v>叠岳炉主·石岑</x:v>
+        <x:v>护盾装备商人 · 石岑</x:v>
       </x:c>
       <x:c r="D240" t="str">
-        <x:v>Bastion Smith Shi Cen</x:v>
+        <x:v>护盾装备商人 · 石岑</x:v>
       </x:c>
       <x:c r="E240" t="str">
-        <x:v>叠岳炉主·石岑</x:v>
+        <x:v>护盾装备商人 · 石岑</x:v>
       </x:c>
       <x:c r="F240" t="str">
-        <x:v>Bastion Smith Shi Cen</x:v>
+        <x:v>护盾装备商人 · 石岑</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -5181,16 +5199,16 @@
         <x:v>Buqi.Content.Merchant.merchant_spring.Name</x:v>
       </x:c>
       <x:c r="C241" t="str">
-        <x:v>听泉药师·蘅青</x:v>
+        <x:v>恢复装备商人 · 蘅青</x:v>
       </x:c>
       <x:c r="D241" t="str">
-        <x:v>Spring Apothecary Heng Qing</x:v>
+        <x:v>恢复装备商人 · 蘅青</x:v>
       </x:c>
       <x:c r="E241" t="str">
-        <x:v>听泉药师·蘅青</x:v>
+        <x:v>恢复装备商人 · 蘅青</x:v>
       </x:c>
       <x:c r="F241" t="str">
-        <x:v>Spring Apothecary Heng Qing</x:v>
+        <x:v>恢复装备商人 · 蘅青</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -5199,16 +5217,16 @@
         <x:v>Buqi.Content.Merchant.merchant_measure.Name</x:v>
       </x:c>
       <x:c r="C242" t="str">
-        <x:v>量位行者·尺素</x:v>
+        <x:v>小型装备商人 · 尺素</x:v>
       </x:c>
       <x:c r="D242" t="str">
-        <x:v>Measure Walker Chi Su</x:v>
+        <x:v>小型装备商人 · 尺素</x:v>
       </x:c>
       <x:c r="E242" t="str">
-        <x:v>量位行者·尺素</x:v>
+        <x:v>小型装备商人 · 尺素</x:v>
       </x:c>
       <x:c r="F242" t="str">
-        <x:v>Measure Walker Chi Su</x:v>
+        <x:v>小型装备商人 · 尺素</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -5217,16 +5235,16 @@
         <x:v>Buqi.Content.Merchant.merchant_gap.Name</x:v>
       </x:c>
       <x:c r="C243" t="str">
-        <x:v>照隙道人·闻缺</x:v>
+        <x:v>反制装备商人 · 闻缺</x:v>
       </x:c>
       <x:c r="D243" t="str">
-        <x:v>Gap Seer Wen Que</x:v>
+        <x:v>反制装备商人 · 闻缺</x:v>
       </x:c>
       <x:c r="E243" t="str">
-        <x:v>照隙道人·闻缺</x:v>
+        <x:v>反制装备商人 · 闻缺</x:v>
       </x:c>
       <x:c r="F243" t="str">
-        <x:v>Gap Seer Wen Que</x:v>
+        <x:v>反制装备商人 · 闻缺</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -5235,16 +5253,16 @@
         <x:v>Buqi.Content.Merchant.merchant_ledger.Name</x:v>
       </x:c>
       <x:c r="C244" t="str">
-        <x:v>行筹客·金复</x:v>
+        <x:v>经济装备商人 · 金复</x:v>
       </x:c>
       <x:c r="D244" t="str">
-        <x:v>Ledger Guest Jin Fu</x:v>
+        <x:v>经济装备商人 · 金复</x:v>
       </x:c>
       <x:c r="E244" t="str">
-        <x:v>行筹客·金复</x:v>
+        <x:v>经济装备商人 · 金复</x:v>
       </x:c>
       <x:c r="F244" t="str">
-        <x:v>Ledger Guest Jin Fu</x:v>
+        <x:v>经济装备商人 · 金复</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -5253,16 +5271,16 @@
         <x:v>Buqi.Content.Merchant.merchant_grades.Name</x:v>
       </x:c>
       <x:c r="C245" t="str">
-        <x:v>三品鉴主·陶然</x:v>
+        <x:v>品质装备商人 · 陶然</x:v>
       </x:c>
       <x:c r="D245" t="str">
-        <x:v>Three-Grade Appraiser Tao Ran</x:v>
+        <x:v>品质装备商人 · 陶然</x:v>
       </x:c>
       <x:c r="E245" t="str">
-        <x:v>三品鉴主·陶然</x:v>
+        <x:v>品质装备商人 · 陶然</x:v>
       </x:c>
       <x:c r="F245" t="str">
-        <x:v>Three-Grade Appraiser Tao Ran</x:v>
+        <x:v>品质装备商人 · 陶然</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -5271,16 +5289,16 @@
         <x:v>Buqi.Content.Merchant.merchant_summit.Name</x:v>
       </x:c>
       <x:c r="C246" t="str">
-        <x:v>收山器君·莫停云</x:v>
+        <x:v>高级装备商人 · 莫停云</x:v>
       </x:c>
       <x:c r="D246" t="str">
-        <x:v>Summit Curator Mo Tingyun</x:v>
+        <x:v>高级装备商人 · 莫停云</x:v>
       </x:c>
       <x:c r="E246" t="str">
-        <x:v>收山器君·莫停云</x:v>
+        <x:v>高级装备商人 · 莫停云</x:v>
       </x:c>
       <x:c r="F246" t="str">
-        <x:v>Summit Curator Mo Tingyun</x:v>
+        <x:v>高级装备商人 · 莫停云</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -5289,16 +5307,16 @@
         <x:v>Buqi.Content.Trainer.trainer_wind.Name</x:v>
       </x:c>
       <x:c r="C247" t="str">
-        <x:v>踏风教习·简行</x:v>
+        <x:v>加速训练师 · 简行</x:v>
       </x:c>
       <x:c r="D247" t="str">
-        <x:v>Windstep Instructor Jian Xing</x:v>
+        <x:v>加速训练师 · 简行</x:v>
       </x:c>
       <x:c r="E247" t="str">
-        <x:v>踏风教习·简行</x:v>
+        <x:v>加速训练师 · 简行</x:v>
       </x:c>
       <x:c r="F247" t="str">
-        <x:v>Windstep Instructor Jian Xing</x:v>
+        <x:v>加速训练师 · 简行</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -5307,16 +5325,16 @@
         <x:v>Buqi.Content.Trainer.trainer_ward.Name</x:v>
       </x:c>
       <x:c r="C248" t="str">
-        <x:v>垒山教习·岳定</x:v>
+        <x:v>护盾训练师 · 岳定</x:v>
       </x:c>
       <x:c r="D248" t="str">
-        <x:v>Mountain Ward Instructor Yue Ding</x:v>
+        <x:v>护盾训练师 · 岳定</x:v>
       </x:c>
       <x:c r="E248" t="str">
-        <x:v>垒山教习·岳定</x:v>
+        <x:v>护盾训练师 · 岳定</x:v>
       </x:c>
       <x:c r="F248" t="str">
-        <x:v>Mountain Ward Instructor Yue Ding</x:v>
+        <x:v>护盾训练师 · 岳定</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -5325,16 +5343,16 @@
         <x:v>Buqi.Content.Trainer.trainer_pulse.Name</x:v>
       </x:c>
       <x:c r="C249" t="str">
-        <x:v>归脉教习·苏衡</x:v>
+        <x:v>恢复训练师 · 苏衡</x:v>
       </x:c>
       <x:c r="D249" t="str">
-        <x:v>Pulse Instructor Su Heng</x:v>
+        <x:v>恢复训练师 · 苏衡</x:v>
       </x:c>
       <x:c r="E249" t="str">
-        <x:v>归脉教习·苏衡</x:v>
+        <x:v>恢复训练师 · 苏衡</x:v>
       </x:c>
       <x:c r="F249" t="str">
-        <x:v>Pulse Instructor Su Heng</x:v>
+        <x:v>恢复训练师 · 苏衡</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -5343,16 +5361,16 @@
         <x:v>Buqi.Content.Trainer.trainer_craft.Name</x:v>
       </x:c>
       <x:c r="C250" t="str">
-        <x:v>百工教习·鲁知微</x:v>
+        <x:v>强化训练师 · 鲁知微</x:v>
       </x:c>
       <x:c r="D250" t="str">
-        <x:v>Hundred Crafts Instructor Lu Zhiwei</x:v>
+        <x:v>强化训练师 · 鲁知微</x:v>
       </x:c>
       <x:c r="E250" t="str">
-        <x:v>百工教习·鲁知微</x:v>
+        <x:v>强化训练师 · 鲁知微</x:v>
       </x:c>
       <x:c r="F250" t="str">
-        <x:v>Hundred Crafts Instructor Lu Zhiwei</x:v>
+        <x:v>强化训练师 · 鲁知微</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -5361,16 +5379,16 @@
         <x:v>Buqi.Content.Training.training_wind_01.Name</x:v>
       </x:c>
       <x:c r="C251" t="str">
-        <x:v>疾行诀</x:v>
+        <x:v>冷却训练 · 疾行</x:v>
       </x:c>
       <x:c r="D251" t="str">
-        <x:v>Fleet Circuit</x:v>
+        <x:v>冷却训练 · 疾行</x:v>
       </x:c>
       <x:c r="E251" t="str">
-        <x:v>疾行诀</x:v>
+        <x:v>冷却训练 · 疾行</x:v>
       </x:c>
       <x:c r="F251" t="str">
-        <x:v>Fleet Circuit</x:v>
+        <x:v>冷却训练 · 疾行</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -5379,13 +5397,17 @@
         <x:v>Buqi.Content.Training.training_wind_01.Summary</x:v>
       </x:c>
       <x:c r="C252" t="str">
-        <x:v>All haste-tagged items have 10% lower base cooldown today.</x:v>
-      </x:c>
-      <x:c r="D252"/>
+        <x:v>本日所有加速标签装备基础冷却降低 10%。</x:v>
+      </x:c>
+      <x:c r="D252" t="str">
+        <x:v>本日所有加速标签装备基础冷却降低 10%。</x:v>
+      </x:c>
       <x:c r="E252" t="str">
-        <x:v>All haste-tagged items have 10% lower base cooldown today.</x:v>
-      </x:c>
-      <x:c r="F252"/>
+        <x:v>本日所有加速标签装备基础冷却降低 10%。</x:v>
+      </x:c>
+      <x:c r="F252" t="str">
+        <x:v>本日所有加速标签装备基础冷却降低 10%。</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253"/>
@@ -5393,16 +5415,16 @@
         <x:v>Buqi.Content.Training.training_wind_02.Name</x:v>
       </x:c>
       <x:c r="C253" t="str">
-        <x:v>开脉风</x:v>
+        <x:v>攻击加速 · 开脉</x:v>
       </x:c>
       <x:c r="D253" t="str">
-        <x:v>Opening Wind</x:v>
+        <x:v>攻击加速 · 开脉</x:v>
       </x:c>
       <x:c r="E253" t="str">
-        <x:v>开脉风</x:v>
+        <x:v>攻击加速 · 开脉</x:v>
       </x:c>
       <x:c r="F253" t="str">
-        <x:v>Opening Wind</x:v>
+        <x:v>攻击加速 · 开脉</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -5411,13 +5433,17 @@
         <x:v>Buqi.Content.Training.training_wind_02.Summary</x:v>
       </x:c>
       <x:c r="C254" t="str">
-        <x:v>Next battle starts with 1000 haste on attack items for 30 ticks.</x:v>
-      </x:c>
-      <x:c r="D254"/>
+        <x:v>下一战开场使攻击装备加速 1000，持续 30 时间单位。</x:v>
+      </x:c>
+      <x:c r="D254" t="str">
+        <x:v>下一战开场使攻击装备加速 1000，持续 30 时间单位。</x:v>
+      </x:c>
       <x:c r="E254" t="str">
-        <x:v>Next battle starts with 1000 haste on attack items for 30 ticks.</x:v>
-      </x:c>
-      <x:c r="F254"/>
+        <x:v>下一战开场使攻击装备加速 1000，持续 30 时间单位。</x:v>
+      </x:c>
+      <x:c r="F254" t="str">
+        <x:v>下一战开场使攻击装备加速 1000，持续 30 时间单位。</x:v>
+      </x:c>
     </x:row>
     <x:row r="255">
       <x:c r="A255"/>
@@ -5425,16 +5451,16 @@
         <x:v>Buqi.Content.Training.training_wind_03.Name</x:v>
       </x:c>
       <x:c r="C255" t="str">
-        <x:v>邻响步</x:v>
+        <x:v>相邻加速 · 邻响</x:v>
       </x:c>
       <x:c r="D255" t="str">
-        <x:v>Adjacent Step</x:v>
+        <x:v>相邻加速 · 邻响</x:v>
       </x:c>
       <x:c r="E255" t="str">
-        <x:v>邻响步</x:v>
+        <x:v>相邻加速 · 邻响</x:v>
       </x:c>
       <x:c r="F255" t="str">
-        <x:v>Adjacent Step</x:v>
+        <x:v>相邻加速 · 邻响</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -5443,13 +5469,17 @@
         <x:v>Buqi.Content.Training.training_wind_03.Summary</x:v>
       </x:c>
       <x:c r="C256" t="str">
-        <x:v>After the first adjacent trigger next battle, adjacent items gain 800 haste for 30 ticks.</x:v>
-      </x:c>
-      <x:c r="D256"/>
+        <x:v>下一战首次邻接触发后，使相邻装备加速 800，持续 30 时间单位。</x:v>
+      </x:c>
+      <x:c r="D256" t="str">
+        <x:v>下一战首次邻接触发后，使相邻装备加速 800，持续 30 时间单位。</x:v>
+      </x:c>
       <x:c r="E256" t="str">
-        <x:v>After the first adjacent trigger next battle, adjacent items gain 800 haste for 30 ticks.</x:v>
-      </x:c>
-      <x:c r="F256"/>
+        <x:v>下一战首次邻接触发后，使相邻装备加速 800，持续 30 时间单位。</x:v>
+      </x:c>
+      <x:c r="F256" t="str">
+        <x:v>下一战首次邻接触发后，使相邻装备加速 800，持续 30 时间单位。</x:v>
+      </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257"/>
@@ -5457,16 +5487,16 @@
         <x:v>Buqi.Content.Training.training_ward_01.Name</x:v>
       </x:c>
       <x:c r="C257" t="str">
-        <x:v>垒息</x:v>
+        <x:v>开场护盾 · 垒息</x:v>
       </x:c>
       <x:c r="D257" t="str">
-        <x:v>Raised Ward</x:v>
+        <x:v>开场护盾 · 垒息</x:v>
       </x:c>
       <x:c r="E257" t="str">
-        <x:v>垒息</x:v>
+        <x:v>开场护盾 · 垒息</x:v>
       </x:c>
       <x:c r="F257" t="str">
-        <x:v>Raised Ward</x:v>
+        <x:v>开场护盾 · 垒息</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -5475,13 +5505,17 @@
         <x:v>Buqi.Content.Training.training_ward_01.Summary</x:v>
       </x:c>
       <x:c r="C258" t="str">
-        <x:v>Gain 6 buffer at the start of the next battle.</x:v>
-      </x:c>
-      <x:c r="D258"/>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
+      </x:c>
+      <x:c r="D258" t="str">
+        <x:v>下一战开场获得 6 点护盾。</x:v>
+      </x:c>
       <x:c r="E258" t="str">
-        <x:v>Gain 6 buffer at the start of the next battle.</x:v>
-      </x:c>
-      <x:c r="F258"/>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
+      </x:c>
+      <x:c r="F258" t="str">
+        <x:v>下一战开场获得 6 点护盾。</x:v>
+      </x:c>
     </x:row>
     <x:row r="259">
       <x:c r="A259"/>
@@ -5489,16 +5523,16 @@
         <x:v>Buqi.Content.Training.training_ward_02.Name</x:v>
       </x:c>
       <x:c r="C259" t="str">
-        <x:v>守势</x:v>
+        <x:v>护盾强化 · 守势</x:v>
       </x:c>
       <x:c r="D259" t="str">
-        <x:v>Holding Form</x:v>
+        <x:v>护盾强化 · 守势</x:v>
       </x:c>
       <x:c r="E259" t="str">
-        <x:v>守势</x:v>
+        <x:v>护盾强化 · 守势</x:v>
       </x:c>
       <x:c r="F259" t="str">
-        <x:v>Holding Form</x:v>
+        <x:v>护盾强化 · 守势</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -5507,13 +5541,17 @@
         <x:v>Buqi.Content.Training.training_ward_02.Summary</x:v>
       </x:c>
       <x:c r="C260" t="str">
-        <x:v>Buffer gained is increased by 15% today.</x:v>
-      </x:c>
-      <x:c r="D260"/>
+        <x:v>本日护盾获得量提高 15%。</x:v>
+      </x:c>
+      <x:c r="D260" t="str">
+        <x:v>本日护盾获得量提高 15%。</x:v>
+      </x:c>
       <x:c r="E260" t="str">
-        <x:v>Buffer gained is increased by 15% today.</x:v>
-      </x:c>
-      <x:c r="F260"/>
+        <x:v>本日护盾获得量提高 15%。</x:v>
+      </x:c>
+      <x:c r="F260" t="str">
+        <x:v>本日护盾获得量提高 15%。</x:v>
+      </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261"/>
@@ -5521,16 +5559,16 @@
         <x:v>Buqi.Content.Training.training_ward_03.Name</x:v>
       </x:c>
       <x:c r="C261" t="str">
-        <x:v>定岳</x:v>
+        <x:v>受击护盾 · 定岳</x:v>
       </x:c>
       <x:c r="D261" t="str">
-        <x:v>Mountain Poise</x:v>
+        <x:v>受击护盾 · 定岳</x:v>
       </x:c>
       <x:c r="E261" t="str">
-        <x:v>定岳</x:v>
+        <x:v>受击护盾 · 定岳</x:v>
       </x:c>
       <x:c r="F261" t="str">
-        <x:v>Mountain Poise</x:v>
+        <x:v>受击护盾 · 定岳</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -5539,13 +5577,17 @@
         <x:v>Buqi.Content.Training.training_ward_03.Summary</x:v>
       </x:c>
       <x:c r="C262" t="str">
-        <x:v>Gain 8 buffer when first interfered with next battle.</x:v>
-      </x:c>
-      <x:c r="D262"/>
+        <x:v>下一战首次受到干扰时获得 8 点护盾。</x:v>
+      </x:c>
+      <x:c r="D262" t="str">
+        <x:v>下一战首次受到干扰时获得 8 点护盾。</x:v>
+      </x:c>
       <x:c r="E262" t="str">
-        <x:v>Gain 8 buffer when first interfered with next battle.</x:v>
-      </x:c>
-      <x:c r="F262"/>
+        <x:v>下一战首次受到干扰时获得 8 点护盾。</x:v>
+      </x:c>
+      <x:c r="F262" t="str">
+        <x:v>下一战首次受到干扰时获得 8 点护盾。</x:v>
+      </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263"/>
@@ -5553,16 +5595,16 @@
         <x:v>Buqi.Content.Training.training_pulse_01.Name</x:v>
       </x:c>
       <x:c r="C263" t="str">
-        <x:v>回气</x:v>
+        <x:v>开场恢复 · 回气</x:v>
       </x:c>
       <x:c r="D263" t="str">
-        <x:v>Returning Breath</x:v>
+        <x:v>开场恢复 · 回气</x:v>
       </x:c>
       <x:c r="E263" t="str">
-        <x:v>回气</x:v>
+        <x:v>开场恢复 · 回气</x:v>
       </x:c>
       <x:c r="F263" t="str">
-        <x:v>Returning Breath</x:v>
+        <x:v>开场恢复 · 回气</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -5571,13 +5613,17 @@
         <x:v>Buqi.Content.Training.training_pulse_01.Summary</x:v>
       </x:c>
       <x:c r="C264" t="str">
-        <x:v>Restore 6 life at the start of the next battle.</x:v>
-      </x:c>
-      <x:c r="D264"/>
+        <x:v>下一战开场恢复 6 点生命。</x:v>
+      </x:c>
+      <x:c r="D264" t="str">
+        <x:v>下一战开场恢复 6 点生命。</x:v>
+      </x:c>
       <x:c r="E264" t="str">
-        <x:v>Restore 6 life at the start of the next battle.</x:v>
-      </x:c>
-      <x:c r="F264"/>
+        <x:v>下一战开场恢复 6 点生命。</x:v>
+      </x:c>
+      <x:c r="F264" t="str">
+        <x:v>下一战开场恢复 6 点生命。</x:v>
+      </x:c>
     </x:row>
     <x:row r="265">
       <x:c r="A265"/>
@@ -5585,16 +5631,16 @@
         <x:v>Buqi.Content.Training.training_pulse_02.Name</x:v>
       </x:c>
       <x:c r="C265" t="str">
-        <x:v>续脉</x:v>
+        <x:v>治疗强化 · 续脉</x:v>
       </x:c>
       <x:c r="D265" t="str">
-        <x:v>Sustained Pulse</x:v>
+        <x:v>治疗强化 · 续脉</x:v>
       </x:c>
       <x:c r="E265" t="str">
-        <x:v>续脉</x:v>
+        <x:v>治疗强化 · 续脉</x:v>
       </x:c>
       <x:c r="F265" t="str">
-        <x:v>Sustained Pulse</x:v>
+        <x:v>治疗强化 · 续脉</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
@@ -5603,13 +5649,17 @@
         <x:v>Buqi.Content.Training.training_pulse_02.Summary</x:v>
       </x:c>
       <x:c r="C266" t="str">
-        <x:v>Effective healing is increased by 15% today.</x:v>
-      </x:c>
-      <x:c r="D266"/>
+        <x:v>本日有效治疗提高 15%。</x:v>
+      </x:c>
+      <x:c r="D266" t="str">
+        <x:v>本日有效治疗提高 15%。</x:v>
+      </x:c>
       <x:c r="E266" t="str">
-        <x:v>Effective healing is increased by 15% today.</x:v>
-      </x:c>
-      <x:c r="F266"/>
+        <x:v>本日有效治疗提高 15%。</x:v>
+      </x:c>
+      <x:c r="F266" t="str">
+        <x:v>本日有效治疗提高 15%。</x:v>
+      </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267"/>
@@ -5617,16 +5667,16 @@
         <x:v>Buqi.Content.Training.training_pulse_03.Name</x:v>
       </x:c>
       <x:c r="C267" t="str">
-        <x:v>长息</x:v>
+        <x:v>持续恢复 · 长息</x:v>
       </x:c>
       <x:c r="D267" t="str">
-        <x:v>Long Breath</x:v>
+        <x:v>持续恢复 · 长息</x:v>
       </x:c>
       <x:c r="E267" t="str">
-        <x:v>长息</x:v>
+        <x:v>持续恢复 · 长息</x:v>
       </x:c>
       <x:c r="F267" t="str">
-        <x:v>Long Breath</x:v>
+        <x:v>持续恢复 · 长息</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -5635,13 +5685,17 @@
         <x:v>Buqi.Content.Training.training_pulse_03.Summary</x:v>
       </x:c>
       <x:c r="C268" t="str">
-        <x:v>Regen effects last 20 ticks longer next battle.</x:v>
-      </x:c>
-      <x:c r="D268"/>
+        <x:v>下一战生命恢复效果持续时间增加 20 时间单位。</x:v>
+      </x:c>
+      <x:c r="D268" t="str">
+        <x:v>下一战生命恢复效果持续时间增加 20 时间单位。</x:v>
+      </x:c>
       <x:c r="E268" t="str">
-        <x:v>Regen effects last 20 ticks longer next battle.</x:v>
-      </x:c>
-      <x:c r="F268"/>
+        <x:v>下一战生命恢复效果持续时间增加 20 时间单位。</x:v>
+      </x:c>
+      <x:c r="F268" t="str">
+        <x:v>下一战生命恢复效果持续时间增加 20 时间单位。</x:v>
+      </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269"/>
@@ -5649,16 +5703,16 @@
         <x:v>Buqi.Content.Training.training_craft_01.Name</x:v>
       </x:c>
       <x:c r="C269" t="str">
-        <x:v>省材</x:v>
+        <x:v>升级折扣 · 省材</x:v>
       </x:c>
       <x:c r="D269" t="str">
-        <x:v>Frugal Upgrade</x:v>
+        <x:v>升级折扣 · 省材</x:v>
       </x:c>
       <x:c r="E269" t="str">
-        <x:v>省材</x:v>
+        <x:v>升级折扣 · 省材</x:v>
       </x:c>
       <x:c r="F269" t="str">
-        <x:v>Frugal Upgrade</x:v>
+        <x:v>升级折扣 · 省材</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -5667,13 +5721,17 @@
         <x:v>Buqi.Content.Training.training_craft_01.Summary</x:v>
       </x:c>
       <x:c r="C270" t="str">
-        <x:v>The first upgrade today costs 1 less coin, minimum 1.</x:v>
-      </x:c>
-      <x:c r="D270"/>
+        <x:v>本日首次升级少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
+      <x:c r="D270" t="str">
+        <x:v>本日首次升级少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
       <x:c r="E270" t="str">
-        <x:v>The first upgrade today costs 1 less coin, minimum 1.</x:v>
-      </x:c>
-      <x:c r="F270"/>
+        <x:v>本日首次升级少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
+      <x:c r="F270" t="str">
+        <x:v>本日首次升级少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271"/>
@@ -5681,16 +5739,16 @@
         <x:v>Buqi.Content.Training.training_craft_02.Name</x:v>
       </x:c>
       <x:c r="C271" t="str">
-        <x:v>净炉</x:v>
+        <x:v>改造折扣 · 净炉</x:v>
       </x:c>
       <x:c r="D271" t="str">
-        <x:v>Clear Furnace</x:v>
+        <x:v>改造折扣 · 净炉</x:v>
       </x:c>
       <x:c r="E271" t="str">
-        <x:v>净炉</x:v>
+        <x:v>改造折扣 · 净炉</x:v>
       </x:c>
       <x:c r="F271" t="str">
-        <x:v>Clear Furnace</x:v>
+        <x:v>改造折扣 · 净炉</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -5699,13 +5757,17 @@
         <x:v>Buqi.Content.Training.training_craft_02.Summary</x:v>
       </x:c>
       <x:c r="C272" t="str">
-        <x:v>The first refinement today costs 1 less coin, minimum 1.</x:v>
-      </x:c>
-      <x:c r="D272"/>
+        <x:v>本日首次改造少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
+      <x:c r="D272" t="str">
+        <x:v>本日首次改造少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
       <x:c r="E272" t="str">
-        <x:v>The first refinement today costs 1 less coin, minimum 1.</x:v>
-      </x:c>
-      <x:c r="F272"/>
+        <x:v>本日首次改造少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
+      <x:c r="F272" t="str">
+        <x:v>本日首次改造少花 1 金币，最低仍为 1。</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273"/>
@@ -5713,16 +5775,16 @@
         <x:v>Buqi.Content.Training.training_craft_03.Name</x:v>
       </x:c>
       <x:c r="C273" t="str">
-        <x:v>识货</x:v>
+        <x:v>免费刷新 · 识货</x:v>
       </x:c>
       <x:c r="D273" t="str">
-        <x:v>Keen Appraisal</x:v>
+        <x:v>免费刷新 · 识货</x:v>
       </x:c>
       <x:c r="E273" t="str">
-        <x:v>识货</x:v>
+        <x:v>免费刷新 · 识货</x:v>
       </x:c>
       <x:c r="F273" t="str">
-        <x:v>Keen Appraisal</x:v>
+        <x:v>免费刷新 · 识货</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -5731,13 +5793,17 @@
         <x:v>Buqi.Content.Training.training_craft_03.Summary</x:v>
       </x:c>
       <x:c r="C274" t="str">
-        <x:v>Gain one free shop refresh today.</x:v>
-      </x:c>
-      <x:c r="D274"/>
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="D274" t="str">
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
       <x:c r="E274" t="str">
-        <x:v>Gain one free shop refresh today.</x:v>
-      </x:c>
-      <x:c r="F274"/>
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
+      <x:c r="F274" t="str">
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275"/>
@@ -5745,16 +5811,16 @@
         <x:v>Buqi.Content.Event.event_trial_stele.Name</x:v>
       </x:c>
       <x:c r="C275" t="str">
-        <x:v>试锋碑</x:v>
+        <x:v>攻击测试碑 · 试锋</x:v>
       </x:c>
       <x:c r="D275" t="str">
-        <x:v>Edge-Trial Stele</x:v>
+        <x:v>攻击测试碑 · 试锋</x:v>
       </x:c>
       <x:c r="E275" t="str">
-        <x:v>试锋碑</x:v>
+        <x:v>攻击测试碑 · 试锋</x:v>
       </x:c>
       <x:c r="F275" t="str">
-        <x:v>Edge-Trial Stele</x:v>
+        <x:v>攻击测试碑 · 试锋</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -5763,16 +5829,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_read.Name</x:v>
       </x:c>
       <x:c r="C276" t="str">
-        <x:v>照刻试锋</x:v>
+        <x:v>购买攻击装备</x:v>
       </x:c>
       <x:c r="D276" t="str">
-        <x:v>Trace the Marks</x:v>
+        <x:v>购买攻击装备</x:v>
       </x:c>
       <x:c r="E276" t="str">
-        <x:v>照刻试锋</x:v>
+        <x:v>购买攻击装备</x:v>
       </x:c>
       <x:c r="F276" t="str">
-        <x:v>Trace the Marks</x:v>
+        <x:v>购买攻击装备</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -5781,16 +5847,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_read.Summary</x:v>
       </x:c>
       <x:c r="C277" t="str">
-        <x:v>支付 1 灵石，从攻击子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从攻击子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="D277" t="str">
-        <x:v>Pay 1 coin to gain a Normal small item from the attack pool.</x:v>
+        <x:v>支付 1 金币，从攻击子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="E277" t="str">
-        <x:v>支付 1 灵石，从攻击子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从攻击子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="F277" t="str">
-        <x:v>Pay 1 coin to gain a Normal small item from the attack pool.</x:v>
+        <x:v>支付 1 金币，从攻击子池获得一件普通小型装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -5799,16 +5865,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Name</x:v>
       </x:c>
       <x:c r="C278" t="str">
-        <x:v>以盾拓印</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="D278" t="str">
-        <x:v>Take a Ward Rubbing</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="E278" t="str">
-        <x:v>以盾拓印</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F278" t="str">
-        <x:v>Take a Ward Rubbing</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -5817,16 +5883,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Summary</x:v>
       </x:c>
       <x:c r="C279" t="str">
-        <x:v>下一战开场获得 6 点护体。</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
       <x:c r="D279" t="str">
-        <x:v>Gain 6 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
       <x:c r="E279" t="str">
-        <x:v>下一战开场获得 6 点护体。</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
       <x:c r="F279" t="str">
-        <x:v>Gain 6 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -5835,16 +5901,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Name</x:v>
       </x:c>
       <x:c r="C280" t="str">
-        <x:v>记下碑序</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="D280" t="str">
-        <x:v>Record the Sequence</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="E280" t="str">
-        <x:v>记下碑序</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="F280" t="str">
-        <x:v>Record the Sequence</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -5853,16 +5919,16 @@
         <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Summary</x:v>
       </x:c>
       <x:c r="C281" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="D281" t="str">
-        <x:v>Gain 1 coin.</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="E281" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="F281" t="str">
-        <x:v>Gain 1 coin.</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -5871,16 +5937,16 @@
         <x:v>Buqi.Content.Event.event_herb_stall.Name</x:v>
       </x:c>
       <x:c r="C282" t="str">
-        <x:v>旧城药摊</x:v>
+        <x:v>恢复药摊 · 旧城</x:v>
       </x:c>
       <x:c r="D282" t="str">
-        <x:v>Old City Herb Stall</x:v>
+        <x:v>恢复药摊 · 旧城</x:v>
       </x:c>
       <x:c r="E282" t="str">
-        <x:v>旧城药摊</x:v>
+        <x:v>恢复药摊 · 旧城</x:v>
       </x:c>
       <x:c r="F282" t="str">
-        <x:v>Old City Herb Stall</x:v>
+        <x:v>恢复药摊 · 旧城</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -5889,16 +5955,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_stall_dose.Name</x:v>
       </x:c>
       <x:c r="C283" t="str">
-        <x:v>买一剂</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="D283" t="str">
-        <x:v>Buy a Dose</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="E283" t="str">
-        <x:v>买一剂</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F283" t="str">
-        <x:v>Buy a Dose</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -5910,13 +5976,13 @@
         <x:v>下一战开场恢复 8 点生命。</x:v>
       </x:c>
       <x:c r="D284" t="str">
-        <x:v>Restore 8 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 8 点生命。</x:v>
       </x:c>
       <x:c r="E284" t="str">
         <x:v>下一战开场恢复 8 点生命。</x:v>
       </x:c>
       <x:c r="F284" t="str">
-        <x:v>Restore 8 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 8 点生命。</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -5925,16 +5991,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Name</x:v>
       </x:c>
       <x:c r="C285" t="str">
-        <x:v>换取药种</x:v>
+        <x:v>购买恢复装备</x:v>
       </x:c>
       <x:c r="D285" t="str">
-        <x:v>Trade for Seeds</x:v>
+        <x:v>购买恢复装备</x:v>
       </x:c>
       <x:c r="E285" t="str">
-        <x:v>换取药种</x:v>
+        <x:v>购买恢复装备</x:v>
       </x:c>
       <x:c r="F285" t="str">
-        <x:v>Trade for Seeds</x:v>
+        <x:v>购买恢复装备</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -5943,16 +6009,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Summary</x:v>
       </x:c>
       <x:c r="C286" t="str">
-        <x:v>支付 1 灵石，从恢复子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从恢复子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="D286" t="str">
-        <x:v>Pay 1 coin to gain a Normal small item from the sustain pool.</x:v>
+        <x:v>支付 1 金币，从恢复子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="E286" t="str">
-        <x:v>支付 1 灵石，从恢复子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从恢复子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="F286" t="str">
-        <x:v>Pay 1 coin to gain a Normal small item from the sustain pool.</x:v>
+        <x:v>支付 1 金币，从恢复子池获得一件普通小型装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -5961,16 +6027,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_stall_work.Name</x:v>
       </x:c>
       <x:c r="C287" t="str">
-        <x:v>帮忙理药</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="D287" t="str">
-        <x:v>Sort the Herbs</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="E287" t="str">
-        <x:v>帮忙理药</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F287" t="str">
-        <x:v>Sort the Herbs</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -5979,16 +6045,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_stall_work.Summary</x:v>
       </x:c>
       <x:c r="C288" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="D288" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="E288" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="F288" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -5997,16 +6063,16 @@
         <x:v>Buqi.Content.Event.event_broken_armor.Name</x:v>
       </x:c>
       <x:c r="C289" t="str">
-        <x:v>山门残甲</x:v>
+        <x:v>护盾装备 · 山门残甲</x:v>
       </x:c>
       <x:c r="D289" t="str">
-        <x:v>Gatehouse Relic Armor</x:v>
+        <x:v>护盾装备 · 山门残甲</x:v>
       </x:c>
       <x:c r="E289" t="str">
-        <x:v>山门残甲</x:v>
+        <x:v>护盾装备 · 山门残甲</x:v>
       </x:c>
       <x:c r="F289" t="str">
-        <x:v>Gatehouse Relic Armor</x:v>
+        <x:v>护盾装备 · 山门残甲</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -6015,16 +6081,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Name</x:v>
       </x:c>
       <x:c r="C290" t="str">
-        <x:v>补上甲片</x:v>
+        <x:v>强化护盾装备</x:v>
       </x:c>
       <x:c r="D290" t="str">
-        <x:v>Fit the Plate</x:v>
+        <x:v>强化护盾装备</x:v>
       </x:c>
       <x:c r="E290" t="str">
-        <x:v>补上甲片</x:v>
+        <x:v>强化护盾装备</x:v>
       </x:c>
       <x:c r="F290" t="str">
-        <x:v>Fit the Plate</x:v>
+        <x:v>强化护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -6033,16 +6099,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Summary</x:v>
       </x:c>
       <x:c r="C291" t="str">
-        <x:v>支付 1 灵石，将一件普通护体器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通护盾装备提升为强化。</x:v>
       </x:c>
       <x:c r="D291" t="str">
-        <x:v>Pay 1 coin to upgrade a Normal shield item to Improved.</x:v>
+        <x:v>支付 1 金币，将一件普通护盾装备提升为强化。</x:v>
       </x:c>
       <x:c r="E291" t="str">
-        <x:v>支付 1 灵石，将一件普通护体器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通护盾装备提升为强化。</x:v>
       </x:c>
       <x:c r="F291" t="str">
-        <x:v>Pay 1 coin to upgrade a Normal shield item to Improved.</x:v>
+        <x:v>支付 1 金币，将一件普通护盾装备提升为强化。</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -6051,16 +6117,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Name</x:v>
       </x:c>
       <x:c r="C292" t="str">
-        <x:v>拆取护片</x:v>
+        <x:v>过载换护盾装备</x:v>
       </x:c>
       <x:c r="D292" t="str">
-        <x:v>Salvage a Ward Plate</x:v>
+        <x:v>过载换护盾装备</x:v>
       </x:c>
       <x:c r="E292" t="str">
-        <x:v>拆取护片</x:v>
+        <x:v>过载换护盾装备</x:v>
       </x:c>
       <x:c r="F292" t="str">
-        <x:v>Salvage a Ward Plate</x:v>
+        <x:v>过载换护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -6069,16 +6135,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Summary</x:v>
       </x:c>
       <x:c r="C293" t="str">
-        <x:v>带 1 点失衡进入下一战，获得一件普通护体器物。</x:v>
+        <x:v>带 1 点过载进入下一战，获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="D293" t="str">
-        <x:v>Enter the next battle with 1 noise debt and gain a Normal shield item.</x:v>
+        <x:v>带 1 点过载进入下一战，获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="E293" t="str">
-        <x:v>带 1 点失衡进入下一战，获得一件普通护体器物。</x:v>
+        <x:v>带 1 点过载进入下一战，获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="F293" t="str">
-        <x:v>Enter the next battle with 1 noise debt and gain a Normal shield item.</x:v>
+        <x:v>带 1 点过载进入下一战，获得一件普通护盾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -6087,16 +6153,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Name</x:v>
       </x:c>
       <x:c r="C294" t="str">
-        <x:v>量下裂口</x:v>
+        <x:v>获得护盾购买折扣</x:v>
       </x:c>
       <x:c r="D294" t="str">
-        <x:v>Measure the Crack</x:v>
+        <x:v>获得护盾购买折扣</x:v>
       </x:c>
       <x:c r="E294" t="str">
-        <x:v>量下裂口</x:v>
+        <x:v>获得护盾购买折扣</x:v>
       </x:c>
       <x:c r="F294" t="str">
-        <x:v>Measure the Crack</x:v>
+        <x:v>获得护盾购买折扣</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -6105,16 +6171,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Summary</x:v>
       </x:c>
       <x:c r="C295" t="str">
-        <x:v>本日下一件护体器物少花 1 灵石。</x:v>
+        <x:v>本日下一件护盾装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="D295" t="str">
-        <x:v>The next shield item bought today costs 1 less coin.</x:v>
+        <x:v>本日下一件护盾装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="E295" t="str">
-        <x:v>本日下一件护体器物少花 1 灵石。</x:v>
+        <x:v>本日下一件护盾装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="F295" t="str">
-        <x:v>The next shield item bought today costs 1 less coin.</x:v>
+        <x:v>本日下一件护盾装备少花 1 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -6123,16 +6189,16 @@
         <x:v>Buqi.Content.Event.event_cloud_peddler.Name</x:v>
       </x:c>
       <x:c r="C296" t="str">
-        <x:v>云脚行商</x:v>
+        <x:v>旅行商人 · 云脚</x:v>
       </x:c>
       <x:c r="D296" t="str">
-        <x:v>Cloudstep Peddler</x:v>
+        <x:v>旅行商人 · 云脚</x:v>
       </x:c>
       <x:c r="E296" t="str">
-        <x:v>云脚行商</x:v>
+        <x:v>旅行商人 · 云脚</x:v>
       </x:c>
       <x:c r="F296" t="str">
-        <x:v>Cloudstep Peddler</x:v>
+        <x:v>旅行商人 · 云脚</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -6141,16 +6207,16 @@
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Name</x:v>
       </x:c>
       <x:c r="C297" t="str">
-        <x:v>买下杂包</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="D297" t="str">
-        <x:v>Buy the Mixed Bundle</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="E297" t="str">
-        <x:v>买下杂包</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="F297" t="str">
-        <x:v>Buy the Mixed Bundle</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -6159,16 +6225,16 @@
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Summary</x:v>
       </x:c>
       <x:c r="C298" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="D298" t="str">
-        <x:v>Gain a Normal bridge item.</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="E298" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="F298" t="str">
-        <x:v>Gain a Normal bridge item.</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -6177,16 +6243,16 @@
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_map.Name</x:v>
       </x:c>
       <x:c r="C299" t="str">
-        <x:v>买路线图</x:v>
+        <x:v>获得免费刷新</x:v>
       </x:c>
       <x:c r="D299" t="str">
-        <x:v>Buy the Route Map</x:v>
+        <x:v>获得免费刷新</x:v>
       </x:c>
       <x:c r="E299" t="str">
-        <x:v>买路线图</x:v>
+        <x:v>获得免费刷新</x:v>
       </x:c>
       <x:c r="F299" t="str">
-        <x:v>Buy the Route Map</x:v>
+        <x:v>获得免费刷新</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -6198,13 +6264,13 @@
         <x:v>本日获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="D300" t="str">
-        <x:v>Gain one free shop refresh today.</x:v>
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="E300" t="str">
         <x:v>本日获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="F300" t="str">
-        <x:v>Gain one free shop refresh today.</x:v>
+        <x:v>本日获得 1 次免费商店刷新。</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -6213,16 +6279,16 @@
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Name</x:v>
       </x:c>
       <x:c r="C301" t="str">
-        <x:v>替他叫卖</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="D301" t="str">
-        <x:v>Hawk His Wares</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="E301" t="str">
-        <x:v>替他叫卖</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F301" t="str">
-        <x:v>Hawk His Wares</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
@@ -6231,16 +6297,16 @@
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Summary</x:v>
       </x:c>
       <x:c r="C302" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="D302" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="E302" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="F302" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -6249,16 +6315,16 @@
         <x:v>Buqi.Content.Event.event_borrowed_flame.Name</x:v>
       </x:c>
       <x:c r="C303" t="str">
-        <x:v>借火炼器</x:v>
+        <x:v>强化炉 · 借火</x:v>
       </x:c>
       <x:c r="D303" t="str">
-        <x:v>Borrowed Flame</x:v>
+        <x:v>强化炉 · 借火</x:v>
       </x:c>
       <x:c r="E303" t="str">
-        <x:v>借火炼器</x:v>
+        <x:v>强化炉 · 借火</x:v>
       </x:c>
       <x:c r="F303" t="str">
-        <x:v>Borrowed Flame</x:v>
+        <x:v>强化炉 · 借火</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -6267,16 +6333,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Name</x:v>
       </x:c>
       <x:c r="C304" t="str">
-        <x:v>当场淬火</x:v>
+        <x:v>强化普通装备</x:v>
       </x:c>
       <x:c r="D304" t="str">
-        <x:v>Temper It Now</x:v>
+        <x:v>强化普通装备</x:v>
       </x:c>
       <x:c r="E304" t="str">
-        <x:v>当场淬火</x:v>
+        <x:v>强化普通装备</x:v>
       </x:c>
       <x:c r="F304" t="str">
-        <x:v>Temper It Now</x:v>
+        <x:v>强化普通装备</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -6285,16 +6351,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Summary</x:v>
       </x:c>
       <x:c r="C305" t="str">
-        <x:v>支付 2 灵石，将一件普通器物提升为改良。</x:v>
+        <x:v>支付 2 金币，将一件普通装备提升为强化。</x:v>
       </x:c>
       <x:c r="D305" t="str">
-        <x:v>Pay 2 coins to upgrade one Normal item to Improved.</x:v>
+        <x:v>支付 2 金币，将一件普通装备提升为强化。</x:v>
       </x:c>
       <x:c r="E305" t="str">
-        <x:v>支付 2 灵石，将一件普通器物提升为改良。</x:v>
+        <x:v>支付 2 金币，将一件普通装备提升为强化。</x:v>
       </x:c>
       <x:c r="F305" t="str">
-        <x:v>Pay 2 coins to upgrade one Normal item to Improved.</x:v>
+        <x:v>支付 2 金币，将一件普通装备提升为强化。</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -6303,16 +6369,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Name</x:v>
       </x:c>
       <x:c r="C306" t="str">
-        <x:v>借走火种</x:v>
+        <x:v>过载换升级折扣</x:v>
       </x:c>
       <x:c r="D306" t="str">
-        <x:v>Carry the Ember</x:v>
+        <x:v>过载换升级折扣</x:v>
       </x:c>
       <x:c r="E306" t="str">
-        <x:v>借走火种</x:v>
+        <x:v>过载换升级折扣</x:v>
       </x:c>
       <x:c r="F306" t="str">
-        <x:v>Carry the Ember</x:v>
+        <x:v>过载换升级折扣</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -6321,16 +6387,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Summary</x:v>
       </x:c>
       <x:c r="C307" t="str">
-        <x:v>未来两日首次升级少花 2 灵石；下一战增加 2 点失衡。</x:v>
+        <x:v>未来两日首次升级少花 2 金币；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="D307" t="str">
-        <x:v>The first upgrade within two days costs 2 less; next battle starts with 2 noise debt.</x:v>
+        <x:v>未来两日首次升级少花 2 金币；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="E307" t="str">
-        <x:v>未来两日首次升级少花 2 灵石；下一战增加 2 点失衡。</x:v>
+        <x:v>未来两日首次升级少花 2 金币；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="F307" t="str">
-        <x:v>The first upgrade within two days costs 2 less; next battle starts with 2 noise debt.</x:v>
+        <x:v>未来两日首次升级少花 2 金币；下一战增加 2 点过载。</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -6339,16 +6405,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Name</x:v>
       </x:c>
       <x:c r="C308" t="str">
-        <x:v>转卖余炭</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="D308" t="str">
-        <x:v>Sell the Coals</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="E308" t="str">
-        <x:v>转卖余炭</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F308" t="str">
-        <x:v>Sell the Coals</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -6357,16 +6423,16 @@
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Summary</x:v>
       </x:c>
       <x:c r="C309" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="D309" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="E309" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="F309" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -6375,16 +6441,16 @@
         <x:v>Buqi.Content.Event.event_broken_mechanism.Name</x:v>
       </x:c>
       <x:c r="C310" t="str">
-        <x:v>断弦机括</x:v>
+        <x:v>损坏机关 · 断弦</x:v>
       </x:c>
       <x:c r="D310" t="str">
-        <x:v>Severed Mechanism</x:v>
+        <x:v>损坏机关 · 断弦</x:v>
       </x:c>
       <x:c r="E310" t="str">
-        <x:v>断弦机括</x:v>
+        <x:v>损坏机关 · 断弦</x:v>
       </x:c>
       <x:c r="F310" t="str">
-        <x:v>Severed Mechanism</x:v>
+        <x:v>损坏机关 · 断弦</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -6393,16 +6459,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Name</x:v>
       </x:c>
       <x:c r="C311" t="str">
-        <x:v>接回弦线</x:v>
+        <x:v>强化桥接装备</x:v>
       </x:c>
       <x:c r="D311" t="str">
-        <x:v>Reconnect the Cord</x:v>
+        <x:v>强化桥接装备</x:v>
       </x:c>
       <x:c r="E311" t="str">
-        <x:v>接回弦线</x:v>
+        <x:v>强化桥接装备</x:v>
       </x:c>
       <x:c r="F311" t="str">
-        <x:v>Reconnect the Cord</x:v>
+        <x:v>强化桥接装备</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
@@ -6411,16 +6477,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Summary</x:v>
       </x:c>
       <x:c r="C312" t="str">
-        <x:v>支付 1 灵石，将一件普通桥接器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通桥接装备提升为强化。</x:v>
       </x:c>
       <x:c r="D312" t="str">
-        <x:v>Pay 1 coin to upgrade a Normal bridge item to Improved.</x:v>
+        <x:v>支付 1 金币，将一件普通桥接装备提升为强化。</x:v>
       </x:c>
       <x:c r="E312" t="str">
-        <x:v>支付 1 灵石，将一件普通桥接器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通桥接装备提升为强化。</x:v>
       </x:c>
       <x:c r="F312" t="str">
-        <x:v>Pay 1 coin to upgrade a Normal bridge item to Improved.</x:v>
+        <x:v>支付 1 金币，将一件普通桥接装备提升为强化。</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
@@ -6429,16 +6495,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Name</x:v>
       </x:c>
       <x:c r="C313" t="str">
-        <x:v>拆走转轴</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="D313" t="str">
-        <x:v>Take the Pivot</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="E313" t="str">
-        <x:v>拆走转轴</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="F313" t="str">
-        <x:v>Take the Pivot</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
@@ -6447,16 +6513,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Summary</x:v>
       </x:c>
       <x:c r="C314" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="D314" t="str">
-        <x:v>Gain a Normal bridge item.</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="E314" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="F314" t="str">
-        <x:v>Gain a Normal bridge item.</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -6465,16 +6531,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Name</x:v>
       </x:c>
       <x:c r="C315" t="str">
-        <x:v>空转试机</x:v>
+        <x:v>过载换相邻加速</x:v>
       </x:c>
       <x:c r="D315" t="str">
-        <x:v>Dry-Run the Device</x:v>
+        <x:v>过载换相邻加速</x:v>
       </x:c>
       <x:c r="E315" t="str">
-        <x:v>空转试机</x:v>
+        <x:v>过载换相邻加速</x:v>
       </x:c>
       <x:c r="F315" t="str">
-        <x:v>Dry-Run the Device</x:v>
+        <x:v>过载换相邻加速</x:v>
       </x:c>
     </x:row>
     <x:row r="316">
@@ -6483,16 +6549,16 @@
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Summary</x:v>
       </x:c>
       <x:c r="C316" t="str">
-        <x:v>下一战增加 1 点失衡；相邻器物开场加速 800，持续 30 tick。</x:v>
+        <x:v>下一战增加 1 点过载；相邻装备开场加速 800，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="D316" t="str">
-        <x:v>Next battle starts with 1 noise debt; adjacent items gain 800 haste for 30 ticks.</x:v>
+        <x:v>下一战增加 1 点过载；相邻装备开场加速 800，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="E316" t="str">
-        <x:v>下一战增加 1 点失衡；相邻器物开场加速 800，持续 30 tick。</x:v>
+        <x:v>下一战增加 1 点过载；相邻装备开场加速 800，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="F316" t="str">
-        <x:v>Next battle starts with 1 noise debt; adjacent items gain 800 haste for 30 ticks.</x:v>
+        <x:v>下一战增加 1 点过载；相邻装备开场加速 800，持续 30 时间单位。</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
@@ -6501,16 +6567,16 @@
         <x:v>Buqi.Content.Event.event_nameless_ledger.Name</x:v>
       </x:c>
       <x:c r="C317" t="str">
-        <x:v>无名账册</x:v>
+        <x:v>金币账册 · 无名</x:v>
       </x:c>
       <x:c r="D317" t="str">
-        <x:v>Nameless Ledger</x:v>
+        <x:v>金币账册 · 无名</x:v>
       </x:c>
       <x:c r="E317" t="str">
-        <x:v>无名账册</x:v>
+        <x:v>金币账册 · 无名</x:v>
       </x:c>
       <x:c r="F317" t="str">
-        <x:v>Nameless Ledger</x:v>
+        <x:v>金币账册 · 无名</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
@@ -6519,16 +6585,16 @@
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Name</x:v>
       </x:c>
       <x:c r="C318" t="str">
-        <x:v>记一笔赊账</x:v>
+        <x:v>延后结算换 4 金币</x:v>
       </x:c>
       <x:c r="D318" t="str">
-        <x:v>Open a Credit Line</x:v>
+        <x:v>延后结算换 4 金币</x:v>
       </x:c>
       <x:c r="E318" t="str">
-        <x:v>记一笔赊账</x:v>
+        <x:v>延后结算换 4 金币</x:v>
       </x:c>
       <x:c r="F318" t="str">
-        <x:v>Open a Credit Line</x:v>
+        <x:v>延后结算换 4 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -6537,16 +6603,16 @@
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Summary</x:v>
       </x:c>
       <x:c r="C319" t="str">
-        <x:v>获得 4 灵石；两日后账主回访。</x:v>
+        <x:v>获得 4 金币；两日后触发欠款结算事件。</x:v>
       </x:c>
       <x:c r="D319" t="str">
-        <x:v>Gain 4 coins; the ledger keeper returns in two days.</x:v>
+        <x:v>获得 4 金币；两日后触发欠款结算事件。</x:v>
       </x:c>
       <x:c r="E319" t="str">
-        <x:v>获得 4 灵石；两日后账主回访。</x:v>
+        <x:v>获得 4 金币；两日后触发欠款结算事件。</x:v>
       </x:c>
       <x:c r="F319" t="str">
-        <x:v>Gain 4 coins; the ledger keeper returns in two days.</x:v>
+        <x:v>获得 4 金币；两日后触发欠款结算事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -6555,16 +6621,16 @@
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_audit.Name</x:v>
       </x:c>
       <x:c r="C320" t="str">
-        <x:v>替它清账</x:v>
+        <x:v>获得两次免费刷新</x:v>
       </x:c>
       <x:c r="D320" t="str">
-        <x:v>Audit the Ledger</x:v>
+        <x:v>获得两次免费刷新</x:v>
       </x:c>
       <x:c r="E320" t="str">
-        <x:v>替它清账</x:v>
+        <x:v>获得两次免费刷新</x:v>
       </x:c>
       <x:c r="F320" t="str">
-        <x:v>Audit the Ledger</x:v>
+        <x:v>获得两次免费刷新</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -6576,13 +6642,13 @@
         <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="D321" t="str">
-        <x:v>Gain one free shop refresh on each of the next two days.</x:v>
+        <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="E321" t="str">
         <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
       </x:c>
       <x:c r="F321" t="str">
-        <x:v>Gain one free shop refresh on each of the next two days.</x:v>
+        <x:v>未来两日各获得 1 次免费商店刷新。</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
@@ -6591,16 +6657,16 @@
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Name</x:v>
       </x:c>
       <x:c r="C322" t="str">
-        <x:v>合上账册</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="D322" t="str">
-        <x:v>Close the Book</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="E322" t="str">
-        <x:v>合上账册</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="F322" t="str">
-        <x:v>Close the Book</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
@@ -6609,16 +6675,16 @@
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Summary</x:v>
       </x:c>
       <x:c r="C323" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="D323" t="str">
-        <x:v>Gain 1 coin.</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="E323" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="F323" t="str">
-        <x:v>Gain 1 coin.</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -6627,16 +6693,16 @@
         <x:v>Buqi.Content.Event.event_rain_umbrella.Name</x:v>
       </x:c>
       <x:c r="C324" t="str">
-        <x:v>雨夜借伞</x:v>
+        <x:v>护盾雨伞 · 雨夜</x:v>
       </x:c>
       <x:c r="D324" t="str">
-        <x:v>Umbrella in the Rain</x:v>
+        <x:v>护盾雨伞 · 雨夜</x:v>
       </x:c>
       <x:c r="E324" t="str">
-        <x:v>雨夜借伞</x:v>
+        <x:v>护盾雨伞 · 雨夜</x:v>
       </x:c>
       <x:c r="F324" t="str">
-        <x:v>Umbrella in the Rain</x:v>
+        <x:v>护盾雨伞 · 雨夜</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -6645,16 +6711,16 @@
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Name</x:v>
       </x:c>
       <x:c r="C325" t="str">
-        <x:v>借伞赶路</x:v>
+        <x:v>借用换开场护盾</x:v>
       </x:c>
       <x:c r="D325" t="str">
-        <x:v>Borrow the Umbrella</x:v>
+        <x:v>借用换开场护盾</x:v>
       </x:c>
       <x:c r="E325" t="str">
-        <x:v>借伞赶路</x:v>
+        <x:v>借用换开场护盾</x:v>
       </x:c>
       <x:c r="F325" t="str">
-        <x:v>Borrow the Umbrella</x:v>
+        <x:v>借用换开场护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -6663,16 +6729,16 @@
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Summary</x:v>
       </x:c>
       <x:c r="C326" t="str">
-        <x:v>下一战开场获得 8 点护体；两日后归伞人回访。</x:v>
+        <x:v>下一战开场获得 8 点护盾；两日后触发借用结算事件。</x:v>
       </x:c>
       <x:c r="D326" t="str">
-        <x:v>Gain 8 opening buffer next battle; the owner returns in two days.</x:v>
+        <x:v>下一战开场获得 8 点护盾；两日后触发借用结算事件。</x:v>
       </x:c>
       <x:c r="E326" t="str">
-        <x:v>下一战开场获得 8 点护体；两日后归伞人回访。</x:v>
+        <x:v>下一战开场获得 8 点护盾；两日后触发借用结算事件。</x:v>
       </x:c>
       <x:c r="F326" t="str">
-        <x:v>Gain 8 opening buffer next battle; the owner returns in two days.</x:v>
+        <x:v>下一战开场获得 8 点护盾；两日后触发借用结算事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -6681,16 +6747,16 @@
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Name</x:v>
       </x:c>
       <x:c r="C327" t="str">
-        <x:v>买下旧伞</x:v>
+        <x:v>获得护盾装备</x:v>
       </x:c>
       <x:c r="D327" t="str">
-        <x:v>Buy the Old Umbrella</x:v>
+        <x:v>获得护盾装备</x:v>
       </x:c>
       <x:c r="E327" t="str">
-        <x:v>买下旧伞</x:v>
+        <x:v>获得护盾装备</x:v>
       </x:c>
       <x:c r="F327" t="str">
-        <x:v>Buy the Old Umbrella</x:v>
+        <x:v>获得护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -6699,16 +6765,16 @@
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Summary</x:v>
       </x:c>
       <x:c r="C328" t="str">
-        <x:v>获得一件普通护体器物。</x:v>
+        <x:v>获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="D328" t="str">
-        <x:v>Gain a Normal shield item.</x:v>
+        <x:v>获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="E328" t="str">
-        <x:v>获得一件普通护体器物。</x:v>
+        <x:v>获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="F328" t="str">
-        <x:v>Gain a Normal shield item.</x:v>
+        <x:v>获得一件普通护盾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -6717,16 +6783,16 @@
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_wait.Name</x:v>
       </x:c>
       <x:c r="C329" t="str">
-        <x:v>檐下等雨</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="D329" t="str">
-        <x:v>Wait Under the Eaves</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="E329" t="str">
-        <x:v>檐下等雨</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F329" t="str">
-        <x:v>Wait Under the Eaves</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
@@ -6738,13 +6804,13 @@
         <x:v>下一战开场恢复 5 点生命。</x:v>
       </x:c>
       <x:c r="D330" t="str">
-        <x:v>Restore 5 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 5 点生命。</x:v>
       </x:c>
       <x:c r="E330" t="str">
         <x:v>下一战开场恢复 5 点生命。</x:v>
       </x:c>
       <x:c r="F330" t="str">
-        <x:v>Restore 5 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 5 点生命。</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -6753,16 +6819,16 @@
         <x:v>Buqi.Content.Event.event_sword_echo.Name</x:v>
       </x:c>
       <x:c r="C331" t="str">
-        <x:v>剑痕回声</x:v>
+        <x:v>攻击记录 · 剑痕</x:v>
       </x:c>
       <x:c r="D331" t="str">
-        <x:v>Echo of Sword Marks</x:v>
+        <x:v>攻击记录 · 剑痕</x:v>
       </x:c>
       <x:c r="E331" t="str">
-        <x:v>剑痕回声</x:v>
+        <x:v>攻击记录 · 剑痕</x:v>
       </x:c>
       <x:c r="F331" t="str">
-        <x:v>Echo of Sword Marks</x:v>
+        <x:v>攻击记录 · 剑痕</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
@@ -6771,16 +6837,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Name</x:v>
       </x:c>
       <x:c r="C332" t="str">
-        <x:v>循痕运刃</x:v>
+        <x:v>升级攻击装备</x:v>
       </x:c>
       <x:c r="D332" t="str">
-        <x:v>Follow the Cut</x:v>
+        <x:v>升级攻击装备</x:v>
       </x:c>
       <x:c r="E332" t="str">
-        <x:v>循痕运刃</x:v>
+        <x:v>升级攻击装备</x:v>
       </x:c>
       <x:c r="F332" t="str">
-        <x:v>Follow the Cut</x:v>
+        <x:v>升级攻击装备</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
@@ -6789,16 +6855,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Summary</x:v>
       </x:c>
       <x:c r="C333" t="str">
-        <x:v>支付 2 灵石，升级一件普通攻击器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通攻击装备。</x:v>
       </x:c>
       <x:c r="D333" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal attack item.</x:v>
+        <x:v>支付 2 金币，升级一件普通攻击装备。</x:v>
       </x:c>
       <x:c r="E333" t="str">
-        <x:v>支付 2 灵石，升级一件普通攻击器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通攻击装备。</x:v>
       </x:c>
       <x:c r="F333" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal attack item.</x:v>
+        <x:v>支付 2 金币，升级一件普通攻击装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="334">
@@ -6807,16 +6873,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Name</x:v>
       </x:c>
       <x:c r="C334" t="str">
-        <x:v>以甲受痕</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="D334" t="str">
-        <x:v>Receive It on Armor</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="E334" t="str">
-        <x:v>以甲受痕</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F334" t="str">
-        <x:v>Receive It on Armor</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -6825,16 +6891,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Summary</x:v>
       </x:c>
       <x:c r="C335" t="str">
-        <x:v>下一战开场获得 10 点护体。</x:v>
+        <x:v>下一战开场获得 10 点护盾。</x:v>
       </x:c>
       <x:c r="D335" t="str">
-        <x:v>Gain 10 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 10 点护盾。</x:v>
       </x:c>
       <x:c r="E335" t="str">
-        <x:v>下一战开场获得 10 点护体。</x:v>
+        <x:v>下一战开场获得 10 点护盾。</x:v>
       </x:c>
       <x:c r="F335" t="str">
-        <x:v>Gain 10 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 10 点护盾。</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -6843,16 +6909,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Name</x:v>
       </x:c>
       <x:c r="C336" t="str">
-        <x:v>拓下剑路</x:v>
+        <x:v>过载换加急改造</x:v>
       </x:c>
       <x:c r="D336" t="str">
-        <x:v>Copy the Sword Path</x:v>
+        <x:v>过载换加急改造</x:v>
       </x:c>
       <x:c r="E336" t="str">
-        <x:v>拓下剑路</x:v>
+        <x:v>过载换加急改造</x:v>
       </x:c>
       <x:c r="F336" t="str">
-        <x:v>Copy the Sword Path</x:v>
+        <x:v>过载换加急改造</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -6861,16 +6927,16 @@
         <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Summary</x:v>
       </x:c>
       <x:c r="C337" t="str">
-        <x:v>下一战增加 2 点失衡，获得加急精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得加急改造。</x:v>
       </x:c>
       <x:c r="D337" t="str">
-        <x:v>Start next battle with 2 noise debt and gain the Haste refinement.</x:v>
+        <x:v>下一战增加 2 点过载，获得加急改造。</x:v>
       </x:c>
       <x:c r="E337" t="str">
-        <x:v>下一战增加 2 点失衡，获得加急精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得加急改造。</x:v>
       </x:c>
       <x:c r="F337" t="str">
-        <x:v>Start next battle with 2 noise debt and gain the Haste refinement.</x:v>
+        <x:v>下一战增加 2 点过载，获得加急改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="338">
@@ -6879,16 +6945,16 @@
         <x:v>Buqi.Content.Event.event_wall_fissure.Name</x:v>
       </x:c>
       <x:c r="C338" t="str">
-        <x:v>城墙裂隙</x:v>
+        <x:v>护盾挑战 · 城墙裂隙</x:v>
       </x:c>
       <x:c r="D338" t="str">
-        <x:v>City Wall Fissure</x:v>
+        <x:v>护盾挑战 · 城墙裂隙</x:v>
       </x:c>
       <x:c r="E338" t="str">
-        <x:v>城墙裂隙</x:v>
+        <x:v>护盾挑战 · 城墙裂隙</x:v>
       </x:c>
       <x:c r="F338" t="str">
-        <x:v>City Wall Fissure</x:v>
+        <x:v>护盾挑战 · 城墙裂隙</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -6897,16 +6963,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Name</x:v>
       </x:c>
       <x:c r="C339" t="str">
-        <x:v>封住裂隙</x:v>
+        <x:v>升级护盾装备</x:v>
       </x:c>
       <x:c r="D339" t="str">
-        <x:v>Seal the Fissure</x:v>
+        <x:v>升级护盾装备</x:v>
       </x:c>
       <x:c r="E339" t="str">
-        <x:v>封住裂隙</x:v>
+        <x:v>升级护盾装备</x:v>
       </x:c>
       <x:c r="F339" t="str">
-        <x:v>Seal the Fissure</x:v>
+        <x:v>升级护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -6915,16 +6981,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Summary</x:v>
       </x:c>
       <x:c r="C340" t="str">
-        <x:v>支付 2 灵石，升级一件普通护体器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="D340" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal shield item.</x:v>
+        <x:v>支付 2 金币，升级一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="E340" t="str">
-        <x:v>支付 2 灵石，升级一件普通护体器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="F340" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal shield item.</x:v>
+        <x:v>支付 2 金币，升级一件普通护盾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -6933,16 +6999,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Name</x:v>
       </x:c>
       <x:c r="C341" t="str">
-        <x:v>立临时支架</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="D341" t="str">
-        <x:v>Raise a Brace</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="E341" t="str">
-        <x:v>立临时支架</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F341" t="str">
-        <x:v>Raise a Brace</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -6951,16 +7017,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Summary</x:v>
       </x:c>
       <x:c r="C342" t="str">
-        <x:v>下一战开场获得 12 点护体。</x:v>
+        <x:v>下一战开场获得 12 点护盾。</x:v>
       </x:c>
       <x:c r="D342" t="str">
-        <x:v>Gain 12 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 12 点护盾。</x:v>
       </x:c>
       <x:c r="E342" t="str">
-        <x:v>下一战开场获得 12 点护体。</x:v>
+        <x:v>下一战开场获得 12 点护盾。</x:v>
       </x:c>
       <x:c r="F342" t="str">
-        <x:v>Gain 12 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 12 点护盾。</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -6969,16 +7035,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Name</x:v>
       </x:c>
       <x:c r="C343" t="str">
-        <x:v>收走碎砖</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="D343" t="str">
-        <x:v>Take the Fallen Bricks</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="E343" t="str">
-        <x:v>收走碎砖</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F343" t="str">
-        <x:v>Take the Fallen Bricks</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -6987,16 +7053,16 @@
         <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Summary</x:v>
       </x:c>
       <x:c r="C344" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="D344" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="E344" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="F344" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -7005,16 +7071,16 @@
         <x:v>Buqi.Content.Event.event_herb_water.Name</x:v>
       </x:c>
       <x:c r="C345" t="str">
-        <x:v>药田争水</x:v>
+        <x:v>恢复训练 · 药田争水</x:v>
       </x:c>
       <x:c r="D345" t="str">
-        <x:v>Water for the Herb Fields</x:v>
+        <x:v>恢复训练 · 药田争水</x:v>
       </x:c>
       <x:c r="E345" t="str">
-        <x:v>药田争水</x:v>
+        <x:v>恢复训练 · 药田争水</x:v>
       </x:c>
       <x:c r="F345" t="str">
-        <x:v>Water for the Herb Fields</x:v>
+        <x:v>恢复训练 · 药田争水</x:v>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -7023,16 +7089,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_water_divert.Name</x:v>
       </x:c>
       <x:c r="C346" t="str">
-        <x:v>引水入田</x:v>
+        <x:v>升级恢复装备</x:v>
       </x:c>
       <x:c r="D346" t="str">
-        <x:v>Divert the Stream</x:v>
+        <x:v>升级恢复装备</x:v>
       </x:c>
       <x:c r="E346" t="str">
-        <x:v>引水入田</x:v>
+        <x:v>升级恢复装备</x:v>
       </x:c>
       <x:c r="F346" t="str">
-        <x:v>Divert the Stream</x:v>
+        <x:v>升级恢复装备</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -7041,16 +7107,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_water_divert.Summary</x:v>
       </x:c>
       <x:c r="C347" t="str">
-        <x:v>支付 2 灵石，升级一件普通恢复器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通恢复装备。</x:v>
       </x:c>
       <x:c r="D347" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal healing item.</x:v>
+        <x:v>支付 2 金币，升级一件普通恢复装备。</x:v>
       </x:c>
       <x:c r="E347" t="str">
-        <x:v>支付 2 灵石，升级一件普通恢复器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通恢复装备。</x:v>
       </x:c>
       <x:c r="F347" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal healing item.</x:v>
+        <x:v>支付 2 金币，升级一件普通恢复装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -7059,16 +7125,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_water_share.Name</x:v>
       </x:c>
       <x:c r="C348" t="str">
-        <x:v>平分水渠</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="D348" t="str">
-        <x:v>Share the Channel</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="E348" t="str">
-        <x:v>平分水渠</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F348" t="str">
-        <x:v>Share the Channel</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -7080,13 +7146,13 @@
         <x:v>下一战开场恢复 10 点生命。</x:v>
       </x:c>
       <x:c r="D349" t="str">
-        <x:v>Restore 10 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 10 点生命。</x:v>
       </x:c>
       <x:c r="E349" t="str">
         <x:v>下一战开场恢复 10 点生命。</x:v>
       </x:c>
       <x:c r="F349" t="str">
-        <x:v>Restore 10 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 10 点生命。</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -7095,16 +7161,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_water_sell.Name</x:v>
       </x:c>
       <x:c r="C350" t="str">
-        <x:v>卖出水权</x:v>
+        <x:v>生命换 5 金币</x:v>
       </x:c>
       <x:c r="D350" t="str">
-        <x:v>Sell the Water Right</x:v>
+        <x:v>生命换 5 金币</x:v>
       </x:c>
       <x:c r="E350" t="str">
-        <x:v>卖出水权</x:v>
+        <x:v>生命换 5 金币</x:v>
       </x:c>
       <x:c r="F350" t="str">
-        <x:v>Sell the Water Right</x:v>
+        <x:v>生命换 5 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -7113,16 +7179,16 @@
         <x:v>Buqi.Content.EventOption.event_herb_water_sell.Summary</x:v>
       </x:c>
       <x:c r="C351" t="str">
-        <x:v>失去 1 命，获得 5 灵石。</x:v>
+        <x:v>失去 1 命，获得 5 金币。</x:v>
       </x:c>
       <x:c r="D351" t="str">
-        <x:v>Lose 1 life and gain 5 coins.</x:v>
+        <x:v>失去 1 命，获得 5 金币。</x:v>
       </x:c>
       <x:c r="E351" t="str">
-        <x:v>失去 1 命，获得 5 灵石。</x:v>
+        <x:v>失去 1 命，获得 5 金币。</x:v>
       </x:c>
       <x:c r="F351" t="str">
-        <x:v>Lose 1 life and gain 5 coins.</x:v>
+        <x:v>失去 1 命，获得 5 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -7131,16 +7197,16 @@
         <x:v>Buqi.Content.Event.event_roving_furnace.Name</x:v>
       </x:c>
       <x:c r="C352" t="str">
-        <x:v>游炉换火</x:v>
+        <x:v>强化炉 · 换火</x:v>
       </x:c>
       <x:c r="D352" t="str">
-        <x:v>Roving Furnace Exchange</x:v>
+        <x:v>强化炉 · 换火</x:v>
       </x:c>
       <x:c r="E352" t="str">
-        <x:v>游炉换火</x:v>
+        <x:v>强化炉 · 换火</x:v>
       </x:c>
       <x:c r="F352" t="str">
-        <x:v>Roving Furnace Exchange</x:v>
+        <x:v>强化炉 · 换火</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -7149,16 +7215,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Name</x:v>
       </x:c>
       <x:c r="C353" t="str">
-        <x:v>归还火种</x:v>
+        <x:v>结清欠款并获得改造</x:v>
       </x:c>
       <x:c r="D353" t="str">
-        <x:v>Return the Ember</x:v>
+        <x:v>结清欠款并获得改造</x:v>
       </x:c>
       <x:c r="E353" t="str">
-        <x:v>归还火种</x:v>
+        <x:v>结清欠款并获得改造</x:v>
       </x:c>
       <x:c r="F353" t="str">
-        <x:v>Return the Ember</x:v>
+        <x:v>结清欠款并获得改造</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
@@ -7167,16 +7233,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Summary</x:v>
       </x:c>
       <x:c r="C354" t="str">
-        <x:v>支付 1 灵石归还火种，获得稳流精炼。</x:v>
+        <x:v>支付 1 金币并结清欠款，获得稳定改造。</x:v>
       </x:c>
       <x:c r="D354" t="str">
-        <x:v>Pay 1 coin to return the ember and gain the Steady Flow refinement.</x:v>
+        <x:v>支付 1 金币并结清欠款，获得稳定改造。</x:v>
       </x:c>
       <x:c r="E354" t="str">
-        <x:v>支付 1 灵石归还火种，获得稳流精炼。</x:v>
+        <x:v>支付 1 金币并结清欠款，获得稳定改造。</x:v>
       </x:c>
       <x:c r="F354" t="str">
-        <x:v>Pay 1 coin to return the ember and gain the Steady Flow refinement.</x:v>
+        <x:v>支付 1 金币并结清欠款，获得稳定改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -7185,16 +7251,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Name</x:v>
       </x:c>
       <x:c r="C355" t="str">
-        <x:v>留下火种</x:v>
+        <x:v>过载并升级灼烧装备</x:v>
       </x:c>
       <x:c r="D355" t="str">
-        <x:v>Keep the Ember</x:v>
+        <x:v>过载并升级灼烧装备</x:v>
       </x:c>
       <x:c r="E355" t="str">
-        <x:v>留下火种</x:v>
+        <x:v>过载并升级灼烧装备</x:v>
       </x:c>
       <x:c r="F355" t="str">
-        <x:v>Keep the Ember</x:v>
+        <x:v>过载并升级灼烧装备</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -7203,16 +7269,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Summary</x:v>
       </x:c>
       <x:c r="C356" t="str">
-        <x:v>下一战增加 3 点失衡，升级一件灼烧器物。</x:v>
+        <x:v>下一战增加 3 点过载，升级一件灼烧装备。</x:v>
       </x:c>
       <x:c r="D356" t="str">
-        <x:v>Start next battle with 3 noise debt and upgrade one burn item.</x:v>
+        <x:v>下一战增加 3 点过载，升级一件灼烧装备。</x:v>
       </x:c>
       <x:c r="E356" t="str">
-        <x:v>下一战增加 3 点失衡，升级一件灼烧器物。</x:v>
+        <x:v>下一战增加 3 点过载，升级一件灼烧装备。</x:v>
       </x:c>
       <x:c r="F356" t="str">
-        <x:v>Start next battle with 3 noise debt and upgrade one burn item.</x:v>
+        <x:v>下一战增加 3 点过载，升级一件灼烧装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -7221,16 +7287,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Name</x:v>
       </x:c>
       <x:c r="C357" t="str">
-        <x:v>换成灵石</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="D357" t="str">
-        <x:v>Trade It Away</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="E357" t="str">
-        <x:v>换成灵石</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="F357" t="str">
-        <x:v>Trade It Away</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -7239,16 +7305,16 @@
         <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Summary</x:v>
       </x:c>
       <x:c r="C358" t="str">
-        <x:v>获得 3 灵石并结清火种。</x:v>
+        <x:v>获得 3 金币并结清欠款。</x:v>
       </x:c>
       <x:c r="D358" t="str">
-        <x:v>Gain 3 coins and close the ember debt.</x:v>
+        <x:v>获得 3 金币并结清欠款。</x:v>
       </x:c>
       <x:c r="E358" t="str">
-        <x:v>获得 3 灵石并结清火种。</x:v>
+        <x:v>获得 3 金币并结清欠款。</x:v>
       </x:c>
       <x:c r="F358" t="str">
-        <x:v>Gain 3 coins and close the ember debt.</x:v>
+        <x:v>获得 3 金币并结清欠款。</x:v>
       </x:c>
     </x:row>
     <x:row r="359">
@@ -7257,16 +7323,16 @@
         <x:v>Buqi.Content.Event.event_ledger_collector.Name</x:v>
       </x:c>
       <x:c r="C359" t="str">
-        <x:v>欠账来客</x:v>
+        <x:v>欠款结算 · 来客</x:v>
       </x:c>
       <x:c r="D359" t="str">
-        <x:v>The Ledger Collector</x:v>
+        <x:v>欠款结算 · 来客</x:v>
       </x:c>
       <x:c r="E359" t="str">
-        <x:v>欠账来客</x:v>
+        <x:v>欠款结算 · 来客</x:v>
       </x:c>
       <x:c r="F359" t="str">
-        <x:v>The Ledger Collector</x:v>
+        <x:v>欠款结算 · 来客</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -7275,16 +7341,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Name</x:v>
       </x:c>
       <x:c r="C360" t="str">
-        <x:v>照数归还</x:v>
+        <x:v>支付欠款换免费刷新</x:v>
       </x:c>
       <x:c r="D360" t="str">
-        <x:v>Repay in Full</x:v>
+        <x:v>支付欠款换免费刷新</x:v>
       </x:c>
       <x:c r="E360" t="str">
-        <x:v>照数归还</x:v>
+        <x:v>支付欠款换免费刷新</x:v>
       </x:c>
       <x:c r="F360" t="str">
-        <x:v>Repay in Full</x:v>
+        <x:v>支付欠款换免费刷新</x:v>
       </x:c>
     </x:row>
     <x:row r="361">
@@ -7293,16 +7359,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Summary</x:v>
       </x:c>
       <x:c r="C361" t="str">
-        <x:v>支付 3 灵石，本日获得 1 次免费刷新。</x:v>
+        <x:v>支付 3 金币，本日获得 1 次免费刷新。</x:v>
       </x:c>
       <x:c r="D361" t="str">
-        <x:v>Pay 3 coins and gain one free refresh today.</x:v>
+        <x:v>支付 3 金币，本日获得 1 次免费刷新。</x:v>
       </x:c>
       <x:c r="E361" t="str">
-        <x:v>支付 3 灵石，本日获得 1 次免费刷新。</x:v>
+        <x:v>支付 3 金币，本日获得 1 次免费刷新。</x:v>
       </x:c>
       <x:c r="F361" t="str">
-        <x:v>Pay 3 coins and gain one free refresh today.</x:v>
+        <x:v>支付 3 金币，本日获得 1 次免费刷新。</x:v>
       </x:c>
     </x:row>
     <x:row r="362">
@@ -7311,16 +7377,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Name</x:v>
       </x:c>
       <x:c r="C362" t="str">
-        <x:v>替他收账</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="D362" t="str">
-        <x:v>Collect Another Debt</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="E362" t="str">
-        <x:v>替他收账</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="F362" t="str">
-        <x:v>Collect Another Debt</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -7329,16 +7395,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Summary</x:v>
       </x:c>
       <x:c r="C363" t="str">
-        <x:v>获得 1 灵石并结清账目。</x:v>
+        <x:v>获得 1 金币并结清账目。</x:v>
       </x:c>
       <x:c r="D363" t="str">
-        <x:v>Gain 1 coin and settle the account.</x:v>
+        <x:v>获得 1 金币并结清账目。</x:v>
       </x:c>
       <x:c r="E363" t="str">
-        <x:v>获得 1 灵石并结清账目。</x:v>
+        <x:v>获得 1 金币并结清账目。</x:v>
       </x:c>
       <x:c r="F363" t="str">
-        <x:v>Gain 1 coin and settle the account.</x:v>
+        <x:v>获得 1 金币并结清账目。</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -7347,16 +7413,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Name</x:v>
       </x:c>
       <x:c r="C364" t="str">
-        <x:v>拒绝认账</x:v>
+        <x:v>拒付并承受惩罚</x:v>
       </x:c>
       <x:c r="D364" t="str">
-        <x:v>Refuse the Debt</x:v>
+        <x:v>拒付并承受惩罚</x:v>
       </x:c>
       <x:c r="E364" t="str">
-        <x:v>拒绝认账</x:v>
+        <x:v>拒付并承受惩罚</x:v>
       </x:c>
       <x:c r="F364" t="str">
-        <x:v>Refuse the Debt</x:v>
+        <x:v>拒付并承受惩罚</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -7365,16 +7431,16 @@
         <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Summary</x:v>
       </x:c>
       <x:c r="C365" t="str">
-        <x:v>失去 1 命；下一战增加 2 点失衡。</x:v>
+        <x:v>失去 1 命；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="D365" t="str">
-        <x:v>Lose 1 life; next battle starts with 2 noise debt.</x:v>
+        <x:v>失去 1 命；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="E365" t="str">
-        <x:v>失去 1 命；下一战增加 2 点失衡。</x:v>
+        <x:v>失去 1 命；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="F365" t="str">
-        <x:v>Lose 1 life; next battle starts with 2 noise debt.</x:v>
+        <x:v>失去 1 命；下一战增加 2 点过载。</x:v>
       </x:c>
     </x:row>
     <x:row r="366">
@@ -7383,16 +7449,16 @@
         <x:v>Buqi.Content.Event.event_umbrella_return.Name</x:v>
       </x:c>
       <x:c r="C366" t="str">
-        <x:v>归伞人</x:v>
+        <x:v>护盾雨伞 · 归还</x:v>
       </x:c>
       <x:c r="D366" t="str">
-        <x:v>The Umbrella's Owner</x:v>
+        <x:v>护盾雨伞 · 归还</x:v>
       </x:c>
       <x:c r="E366" t="str">
-        <x:v>归伞人</x:v>
+        <x:v>护盾雨伞 · 归还</x:v>
       </x:c>
       <x:c r="F366" t="str">
-        <x:v>The Umbrella's Owner</x:v>
+        <x:v>护盾雨伞 · 归还</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -7401,16 +7467,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Name</x:v>
       </x:c>
       <x:c r="C367" t="str">
-        <x:v>原样归还</x:v>
+        <x:v>归还并获得金币</x:v>
       </x:c>
       <x:c r="D367" t="str">
-        <x:v>Return It Intact</x:v>
+        <x:v>归还并获得金币</x:v>
       </x:c>
       <x:c r="E367" t="str">
-        <x:v>原样归还</x:v>
+        <x:v>归还并获得金币</x:v>
       </x:c>
       <x:c r="F367" t="str">
-        <x:v>Return It Intact</x:v>
+        <x:v>归还并获得金币</x:v>
       </x:c>
     </x:row>
     <x:row r="368">
@@ -7419,16 +7485,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Summary</x:v>
       </x:c>
       <x:c r="C368" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="D368" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="E368" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="F368" t="str">
-        <x:v>Gain 2 coins.</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -7437,16 +7503,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Name</x:v>
       </x:c>
       <x:c r="C369" t="str">
-        <x:v>修好再还</x:v>
+        <x:v>支付金币换改造</x:v>
       </x:c>
       <x:c r="D369" t="str">
-        <x:v>Repair Before Returning</x:v>
+        <x:v>支付金币换改造</x:v>
       </x:c>
       <x:c r="E369" t="str">
-        <x:v>修好再还</x:v>
+        <x:v>支付金币换改造</x:v>
       </x:c>
       <x:c r="F369" t="str">
-        <x:v>Repair Before Returning</x:v>
+        <x:v>支付金币换改造</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -7455,16 +7521,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Summary</x:v>
       </x:c>
       <x:c r="C370" t="str">
-        <x:v>支付 1 灵石，获得可靠精炼。</x:v>
+        <x:v>支付 1 金币，获得可靠改造。</x:v>
       </x:c>
       <x:c r="D370" t="str">
-        <x:v>Pay 1 coin and gain the Reliable refinement.</x:v>
+        <x:v>支付 1 金币，获得可靠改造。</x:v>
       </x:c>
       <x:c r="E370" t="str">
-        <x:v>支付 1 灵石，获得可靠精炼。</x:v>
+        <x:v>支付 1 金币，获得可靠改造。</x:v>
       </x:c>
       <x:c r="F370" t="str">
-        <x:v>Pay 1 coin and gain the Reliable refinement.</x:v>
+        <x:v>支付 1 金币，获得可靠改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -7473,16 +7539,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Name</x:v>
       </x:c>
       <x:c r="C371" t="str">
-        <x:v>留下旧伞</x:v>
+        <x:v>生命换强化护盾装备</x:v>
       </x:c>
       <x:c r="D371" t="str">
-        <x:v>Keep the Umbrella</x:v>
+        <x:v>生命换强化护盾装备</x:v>
       </x:c>
       <x:c r="E371" t="str">
-        <x:v>留下旧伞</x:v>
+        <x:v>生命换强化护盾装备</x:v>
       </x:c>
       <x:c r="F371" t="str">
-        <x:v>Keep the Umbrella</x:v>
+        <x:v>生命换强化护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -7491,16 +7557,16 @@
         <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Summary</x:v>
       </x:c>
       <x:c r="C372" t="str">
-        <x:v>失去 1 命，获得一件改良护体器物。</x:v>
+        <x:v>失去 1 命，获得一件强化护盾装备。</x:v>
       </x:c>
       <x:c r="D372" t="str">
-        <x:v>Lose 1 life and gain an Improved shield item.</x:v>
+        <x:v>失去 1 命，获得一件强化护盾装备。</x:v>
       </x:c>
       <x:c r="E372" t="str">
-        <x:v>失去 1 命，获得一件改良护体器物。</x:v>
+        <x:v>失去 1 命，获得一件强化护盾装备。</x:v>
       </x:c>
       <x:c r="F372" t="str">
-        <x:v>Lose 1 life and gain an Improved shield item.</x:v>
+        <x:v>失去 1 命，获得一件强化护盾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="373">
@@ -7509,16 +7575,16 @@
         <x:v>Buqi.Content.Event.event_headwind_array.Name</x:v>
       </x:c>
       <x:c r="C373" t="str">
-        <x:v>逆风试阵</x:v>
+        <x:v>加速挑战 · 逆风</x:v>
       </x:c>
       <x:c r="D373" t="str">
-        <x:v>Headwind Trial Array</x:v>
+        <x:v>加速挑战 · 逆风</x:v>
       </x:c>
       <x:c r="E373" t="str">
-        <x:v>逆风试阵</x:v>
+        <x:v>加速挑战 · 逆风</x:v>
       </x:c>
       <x:c r="F373" t="str">
-        <x:v>Headwind Trial Array</x:v>
+        <x:v>加速挑战 · 逆风</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -7527,16 +7593,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Name</x:v>
       </x:c>
       <x:c r="C374" t="str">
-        <x:v>正面入阵</x:v>
+        <x:v>过载并升级反制装备</x:v>
       </x:c>
       <x:c r="D374" t="str">
-        <x:v>Enter Head-On</x:v>
+        <x:v>过载并升级反制装备</x:v>
       </x:c>
       <x:c r="E374" t="str">
-        <x:v>正面入阵</x:v>
+        <x:v>过载并升级反制装备</x:v>
       </x:c>
       <x:c r="F374" t="str">
-        <x:v>Enter Head-On</x:v>
+        <x:v>过载并升级反制装备</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -7545,16 +7611,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Summary</x:v>
       </x:c>
       <x:c r="C375" t="str">
-        <x:v>下一战增加 2 点失衡，升级一件反制器物。</x:v>
+        <x:v>下一战增加 2 点过载，升级一件反制装备。</x:v>
       </x:c>
       <x:c r="D375" t="str">
-        <x:v>Start next battle with 2 noise debt and upgrade one counter item.</x:v>
+        <x:v>下一战增加 2 点过载，升级一件反制装备。</x:v>
       </x:c>
       <x:c r="E375" t="str">
-        <x:v>下一战增加 2 点失衡，升级一件反制器物。</x:v>
+        <x:v>下一战增加 2 点过载，升级一件反制装备。</x:v>
       </x:c>
       <x:c r="F375" t="str">
-        <x:v>Start next battle with 2 noise debt and upgrade one counter item.</x:v>
+        <x:v>下一战增加 2 点过载，升级一件反制装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -7563,16 +7629,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Name</x:v>
       </x:c>
       <x:c r="C376" t="str">
-        <x:v>以镇心铃定阵</x:v>
+        <x:v>支付金币换相邻加速</x:v>
       </x:c>
       <x:c r="D376" t="str">
-        <x:v>Anchor with a Calming Bell</x:v>
+        <x:v>支付金币换相邻加速</x:v>
       </x:c>
       <x:c r="E376" t="str">
-        <x:v>以镇心铃定阵</x:v>
+        <x:v>支付金币换相邻加速</x:v>
       </x:c>
       <x:c r="F376" t="str">
-        <x:v>Anchor with a Calming Bell</x:v>
+        <x:v>支付金币换相邻加速</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -7581,16 +7647,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Summary</x:v>
       </x:c>
       <x:c r="C377" t="str">
-        <x:v>支付 1 灵石；下一战相邻器物开场加速 1000。</x:v>
+        <x:v>支付 1 金币；下一战相邻装备开场加速 1000。</x:v>
       </x:c>
       <x:c r="D377" t="str">
-        <x:v>Pay 1 coin; adjacent items gain 1000 opening haste next battle.</x:v>
+        <x:v>支付 1 金币；下一战相邻装备开场加速 1000。</x:v>
       </x:c>
       <x:c r="E377" t="str">
-        <x:v>支付 1 灵石；下一战相邻器物开场加速 1000。</x:v>
+        <x:v>支付 1 金币；下一战相邻装备开场加速 1000。</x:v>
       </x:c>
       <x:c r="F377" t="str">
-        <x:v>Pay 1 coin; adjacent items gain 1000 opening haste next battle.</x:v>
+        <x:v>支付 1 金币；下一战相邻装备开场加速 1000。</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -7599,16 +7665,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Name</x:v>
       </x:c>
       <x:c r="C378" t="str">
-        <x:v>阵外观风</x:v>
+        <x:v>获得反制购买折扣</x:v>
       </x:c>
       <x:c r="D378" t="str">
-        <x:v>Study the Wind</x:v>
+        <x:v>获得反制购买折扣</x:v>
       </x:c>
       <x:c r="E378" t="str">
-        <x:v>阵外观风</x:v>
+        <x:v>获得反制购买折扣</x:v>
       </x:c>
       <x:c r="F378" t="str">
-        <x:v>Study the Wind</x:v>
+        <x:v>获得反制购买折扣</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -7617,16 +7683,16 @@
         <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Summary</x:v>
       </x:c>
       <x:c r="C379" t="str">
-        <x:v>本日下一件反制器物少花 1 灵石。</x:v>
+        <x:v>本日下一件反制装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="D379" t="str">
-        <x:v>The next counter item bought today costs 1 less coin.</x:v>
+        <x:v>本日下一件反制装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="E379" t="str">
-        <x:v>本日下一件反制器物少花 1 灵石。</x:v>
+        <x:v>本日下一件反制装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="F379" t="str">
-        <x:v>The next counter item bought today costs 1 less coin.</x:v>
+        <x:v>本日下一件反制装备少花 1 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -7635,16 +7701,16 @@
         <x:v>Buqi.Content.Event.event_three_bidders.Name</x:v>
       </x:c>
       <x:c r="C380" t="str">
-        <x:v>三家竞价</x:v>
+        <x:v>装备竞价 · 三家</x:v>
       </x:c>
       <x:c r="D380" t="str">
-        <x:v>Three Bidders</x:v>
+        <x:v>装备竞价 · 三家</x:v>
       </x:c>
       <x:c r="E380" t="str">
-        <x:v>三家竞价</x:v>
+        <x:v>装备竞价 · 三家</x:v>
       </x:c>
       <x:c r="F380" t="str">
-        <x:v>Three Bidders</x:v>
+        <x:v>装备竞价 · 三家</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -7653,16 +7719,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Name</x:v>
       </x:c>
       <x:c r="C381" t="str">
-        <x:v>卖出闲器</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="D381" t="str">
-        <x:v>Sell a Spare Item</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="E381" t="str">
-        <x:v>卖出闲器</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="F381" t="str">
-        <x:v>Sell a Spare Item</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
     </x:row>
     <x:row r="382">
@@ -7671,16 +7737,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Summary</x:v>
       </x:c>
       <x:c r="C382" t="str">
-        <x:v>移除一件起手器物，获得 5 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 5 金币。</x:v>
       </x:c>
       <x:c r="D382" t="str">
-        <x:v>Remove one starter item and gain 5 coins.</x:v>
+        <x:v>移除一件起手装备，获得 5 金币。</x:v>
       </x:c>
       <x:c r="E382" t="str">
-        <x:v>移除一件起手器物，获得 5 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 5 金币。</x:v>
       </x:c>
       <x:c r="F382" t="str">
-        <x:v>Remove one starter item and gain 5 coins.</x:v>
+        <x:v>移除一件起手装备，获得 5 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -7689,16 +7755,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Name</x:v>
       </x:c>
       <x:c r="C383" t="str">
-        <x:v>压价竞买</x:v>
+        <x:v>获得强化核心装备</x:v>
       </x:c>
       <x:c r="D383" t="str">
-        <x:v>Bid for a Bargain</x:v>
+        <x:v>获得强化核心装备</x:v>
       </x:c>
       <x:c r="E383" t="str">
-        <x:v>压价竞买</x:v>
+        <x:v>获得强化核心装备</x:v>
       </x:c>
       <x:c r="F383" t="str">
-        <x:v>Bid for a Bargain</x:v>
+        <x:v>获得强化核心装备</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
@@ -7707,16 +7773,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Summary</x:v>
       </x:c>
       <x:c r="C384" t="str">
-        <x:v>获得一件改良核心器物。</x:v>
+        <x:v>获得一件强化核心装备。</x:v>
       </x:c>
       <x:c r="D384" t="str">
-        <x:v>Gain an Improved core item.</x:v>
+        <x:v>获得一件强化核心装备。</x:v>
       </x:c>
       <x:c r="E384" t="str">
-        <x:v>获得一件改良核心器物。</x:v>
+        <x:v>获得一件强化核心装备。</x:v>
       </x:c>
       <x:c r="F384" t="str">
-        <x:v>Gain an Improved core item.</x:v>
+        <x:v>获得一件强化核心装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -7725,16 +7791,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Name</x:v>
       </x:c>
       <x:c r="C385" t="str">
-        <x:v>押到第九日</x:v>
+        <x:v>投资至第九日</x:v>
       </x:c>
       <x:c r="D385" t="str">
-        <x:v>Stake It to Day Nine</x:v>
+        <x:v>投资至第九日</x:v>
       </x:c>
       <x:c r="E385" t="str">
-        <x:v>押到第九日</x:v>
+        <x:v>投资至第九日</x:v>
       </x:c>
       <x:c r="F385" t="str">
-        <x:v>Stake It to Day Nine</x:v>
+        <x:v>投资至第九日</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -7743,16 +7809,16 @@
         <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Summary</x:v>
       </x:c>
       <x:c r="C386" t="str">
-        <x:v>支付 2 灵石，第九日按当前构筑回收。</x:v>
+        <x:v>支付 2 金币，第九日按当前构筑回收。</x:v>
       </x:c>
       <x:c r="D386" t="str">
-        <x:v>Pay 2 coins for a Day Nine build-based settlement.</x:v>
+        <x:v>支付 2 金币，第九日按当前构筑回收。</x:v>
       </x:c>
       <x:c r="E386" t="str">
-        <x:v>支付 2 灵石，第九日按当前构筑回收。</x:v>
+        <x:v>支付 2 金币，第九日按当前构筑回收。</x:v>
       </x:c>
       <x:c r="F386" t="str">
-        <x:v>Pay 2 coins for a Day Nine build-based settlement.</x:v>
+        <x:v>支付 2 金币，第九日按当前构筑回收。</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -7761,16 +7827,16 @@
         <x:v>Buqi.Content.Event.event_heaven_gate.Name</x:v>
       </x:c>
       <x:c r="C387" t="str">
-        <x:v>天门校器</x:v>
+        <x:v>攻击校准 · 天门</x:v>
       </x:c>
       <x:c r="D387" t="str">
-        <x:v>Heaven Gate Calibration</x:v>
+        <x:v>攻击校准 · 天门</x:v>
       </x:c>
       <x:c r="E387" t="str">
-        <x:v>天门校器</x:v>
+        <x:v>攻击校准 · 天门</x:v>
       </x:c>
       <x:c r="F387" t="str">
-        <x:v>Heaven Gate Calibration</x:v>
+        <x:v>攻击校准 · 天门</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -7779,16 +7845,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Name</x:v>
       </x:c>
       <x:c r="C388" t="str">
-        <x:v>校正攻势</x:v>
+        <x:v>购买高级攻击装备</x:v>
       </x:c>
       <x:c r="D388" t="str">
-        <x:v>Calibrate Offense</x:v>
+        <x:v>购买高级攻击装备</x:v>
       </x:c>
       <x:c r="E388" t="str">
-        <x:v>校正攻势</x:v>
+        <x:v>购买高级攻击装备</x:v>
       </x:c>
       <x:c r="F388" t="str">
-        <x:v>Calibrate Offense</x:v>
+        <x:v>购买高级攻击装备</x:v>
       </x:c>
     </x:row>
     <x:row r="389">
@@ -7797,16 +7863,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Summary</x:v>
       </x:c>
       <x:c r="C389" t="str">
-        <x:v>支付 4 灵石，从攻击子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从攻击子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="D389" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the attack pool.</x:v>
+        <x:v>支付 4 金币，从攻击子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="E389" t="str">
-        <x:v>支付 4 灵石，从攻击子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从攻击子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="F389" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the attack pool.</x:v>
+        <x:v>支付 4 金币，从攻击子池获得一件高级收尾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
@@ -7815,16 +7881,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Name</x:v>
       </x:c>
       <x:c r="C390" t="str">
-        <x:v>校正节拍</x:v>
+        <x:v>购买加急改造</x:v>
       </x:c>
       <x:c r="D390" t="str">
-        <x:v>Calibrate Tempo</x:v>
+        <x:v>购买加急改造</x:v>
       </x:c>
       <x:c r="E390" t="str">
-        <x:v>校正节拍</x:v>
+        <x:v>购买加急改造</x:v>
       </x:c>
       <x:c r="F390" t="str">
-        <x:v>Calibrate Tempo</x:v>
+        <x:v>购买加急改造</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -7833,16 +7899,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Summary</x:v>
       </x:c>
       <x:c r="C391" t="str">
-        <x:v>支付 2 灵石，获得加急精炼。</x:v>
+        <x:v>支付 2 金币，获得加急改造。</x:v>
       </x:c>
       <x:c r="D391" t="str">
-        <x:v>Pay 2 coins and gain the Haste refinement.</x:v>
+        <x:v>支付 2 金币，获得加急改造。</x:v>
       </x:c>
       <x:c r="E391" t="str">
-        <x:v>支付 2 灵石，获得加急精炼。</x:v>
+        <x:v>支付 2 金币，获得加急改造。</x:v>
       </x:c>
       <x:c r="F391" t="str">
-        <x:v>Pay 2 coins and gain the Haste refinement.</x:v>
+        <x:v>支付 2 金币，获得加急改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -7851,16 +7917,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Name</x:v>
       </x:c>
       <x:c r="C392" t="str">
-        <x:v>留下余量</x:v>
+        <x:v>获得攻击装备加速</x:v>
       </x:c>
       <x:c r="D392" t="str">
-        <x:v>Keep the Margin</x:v>
+        <x:v>获得攻击装备加速</x:v>
       </x:c>
       <x:c r="E392" t="str">
-        <x:v>留下余量</x:v>
+        <x:v>获得攻击装备加速</x:v>
       </x:c>
       <x:c r="F392" t="str">
-        <x:v>Keep the Margin</x:v>
+        <x:v>获得攻击装备加速</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -7869,16 +7935,16 @@
         <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Summary</x:v>
       </x:c>
       <x:c r="C393" t="str">
-        <x:v>下一战攻击器物开场加速 1200。</x:v>
+        <x:v>下一战攻击装备开场加速 1200。</x:v>
       </x:c>
       <x:c r="D393" t="str">
-        <x:v>Attack items gain 1200 opening haste next battle.</x:v>
+        <x:v>下一战攻击装备开场加速 1200。</x:v>
       </x:c>
       <x:c r="E393" t="str">
-        <x:v>下一战攻击器物开场加速 1200。</x:v>
+        <x:v>下一战攻击装备开场加速 1200。</x:v>
       </x:c>
       <x:c r="F393" t="str">
-        <x:v>Attack items gain 1200 opening haste next battle.</x:v>
+        <x:v>下一战攻击装备开场加速 1200。</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -7887,16 +7953,16 @@
         <x:v>Buqi.Content.Event.event_mountain_eye.Name</x:v>
       </x:c>
       <x:c r="C394" t="str">
-        <x:v>护山阵眼</x:v>
+        <x:v>护盾核心 · 护山</x:v>
       </x:c>
       <x:c r="D394" t="str">
-        <x:v>Mountain Ward Eye</x:v>
+        <x:v>护盾核心 · 护山</x:v>
       </x:c>
       <x:c r="E394" t="str">
-        <x:v>护山阵眼</x:v>
+        <x:v>护盾核心 · 护山</x:v>
       </x:c>
       <x:c r="F394" t="str">
-        <x:v>Mountain Ward Eye</x:v>
+        <x:v>护盾核心 · 护山</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -7905,16 +7971,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Name</x:v>
       </x:c>
       <x:c r="C395" t="str">
-        <x:v>封入堡垒</x:v>
+        <x:v>购买高级护盾装备</x:v>
       </x:c>
       <x:c r="D395" t="str">
-        <x:v>Seal It into the Bastion</x:v>
+        <x:v>购买高级护盾装备</x:v>
       </x:c>
       <x:c r="E395" t="str">
-        <x:v>封入堡垒</x:v>
+        <x:v>购买高级护盾装备</x:v>
       </x:c>
       <x:c r="F395" t="str">
-        <x:v>Seal It into the Bastion</x:v>
+        <x:v>购买高级护盾装备</x:v>
       </x:c>
     </x:row>
     <x:row r="396">
@@ -7923,16 +7989,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Summary</x:v>
       </x:c>
       <x:c r="C396" t="str">
-        <x:v>支付 4 灵石，从护体子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从护盾子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="D396" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the shield pool.</x:v>
+        <x:v>支付 4 金币，从护盾子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="E396" t="str">
-        <x:v>支付 4 灵石，从护体子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从护盾子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="F396" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the shield pool.</x:v>
+        <x:v>支付 4 金币，从护盾子池获得一件高级收尾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="397">
@@ -7941,16 +8007,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Name</x:v>
       </x:c>
       <x:c r="C397" t="str">
-        <x:v>借阵护身</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="D397" t="str">
-        <x:v>Borrow the Ward</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="E397" t="str">
-        <x:v>借阵护身</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F397" t="str">
-        <x:v>Borrow the Ward</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -7959,16 +8025,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Summary</x:v>
       </x:c>
       <x:c r="C398" t="str">
-        <x:v>下一战开场获得 16 点护体。</x:v>
+        <x:v>下一战开场获得 16 点护盾。</x:v>
       </x:c>
       <x:c r="D398" t="str">
-        <x:v>Gain 16 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 16 点护盾。</x:v>
       </x:c>
       <x:c r="E398" t="str">
-        <x:v>下一战开场获得 16 点护体。</x:v>
+        <x:v>下一战开场获得 16 点护盾。</x:v>
       </x:c>
       <x:c r="F398" t="str">
-        <x:v>Gain 16 opening buffer next battle.</x:v>
+        <x:v>下一战开场获得 16 点护盾。</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -7977,16 +8043,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Name</x:v>
       </x:c>
       <x:c r="C399" t="str">
-        <x:v>取一枚阵石</x:v>
+        <x:v>过载换可靠改造</x:v>
       </x:c>
       <x:c r="D399" t="str">
-        <x:v>Take an Array Stone</x:v>
+        <x:v>过载换可靠改造</x:v>
       </x:c>
       <x:c r="E399" t="str">
-        <x:v>取一枚阵石</x:v>
+        <x:v>过载换可靠改造</x:v>
       </x:c>
       <x:c r="F399" t="str">
-        <x:v>Take an Array Stone</x:v>
+        <x:v>过载换可靠改造</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -7995,16 +8061,16 @@
         <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Summary</x:v>
       </x:c>
       <x:c r="C400" t="str">
-        <x:v>下一战增加 2 点失衡，获得可靠精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得可靠改造。</x:v>
       </x:c>
       <x:c r="D400" t="str">
-        <x:v>Start next battle with 2 noise debt and gain the Reliable refinement.</x:v>
+        <x:v>下一战增加 2 点过载，获得可靠改造。</x:v>
       </x:c>
       <x:c r="E400" t="str">
-        <x:v>下一战增加 2 点失衡，获得可靠精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得可靠改造。</x:v>
       </x:c>
       <x:c r="F400" t="str">
-        <x:v>Start next battle with 2 noise debt and gain the Reliable refinement.</x:v>
+        <x:v>下一战增加 2 点过载，获得可靠改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -8013,16 +8079,16 @@
         <x:v>Buqi.Content.Event.event_herbs_return.Name</x:v>
       </x:c>
       <x:c r="C401" t="str">
-        <x:v>百草归元</x:v>
+        <x:v>恢复强化 · 百草</x:v>
       </x:c>
       <x:c r="D401" t="str">
-        <x:v>Hundred Herbs Return</x:v>
+        <x:v>恢复强化 · 百草</x:v>
       </x:c>
       <x:c r="E401" t="str">
-        <x:v>百草归元</x:v>
+        <x:v>恢复强化 · 百草</x:v>
       </x:c>
       <x:c r="F401" t="str">
-        <x:v>Hundred Herbs Return</x:v>
+        <x:v>恢复强化 · 百草</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -8031,16 +8097,16 @@
         <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Name</x:v>
       </x:c>
       <x:c r="C402" t="str">
-        <x:v>合炼归元汤</x:v>
+        <x:v>购买高级恢复装备</x:v>
       </x:c>
       <x:c r="D402" t="str">
-        <x:v>Brew the Returning Draught</x:v>
+        <x:v>购买高级恢复装备</x:v>
       </x:c>
       <x:c r="E402" t="str">
-        <x:v>合炼归元汤</x:v>
+        <x:v>购买高级恢复装备</x:v>
       </x:c>
       <x:c r="F402" t="str">
-        <x:v>Brew the Returning Draught</x:v>
+        <x:v>购买高级恢复装备</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -8049,16 +8115,16 @@
         <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Summary</x:v>
       </x:c>
       <x:c r="C403" t="str">
-        <x:v>支付 4 灵石，从恢复子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从恢复子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="D403" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the healing pool.</x:v>
+        <x:v>支付 4 金币，从恢复子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="E403" t="str">
-        <x:v>支付 4 灵石，从恢复子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从恢复子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="F403" t="str">
-        <x:v>Pay 4 coins to gain a Fixed finisher from the healing pool.</x:v>
+        <x:v>支付 4 金币，从恢复子池获得一件高级收尾装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="404">
@@ -8067,16 +8133,16 @@
         <x:v>Buqi.Content.EventOption.event_herbs_return_share.Name</x:v>
       </x:c>
       <x:c r="C404" t="str">
-        <x:v>分饮药汤</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="D404" t="str">
-        <x:v>Share the Draught</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="E404" t="str">
-        <x:v>分饮药汤</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F404" t="str">
-        <x:v>Share the Draught</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="405">
@@ -8088,13 +8154,13 @@
         <x:v>下一战开场恢复 16 点生命。</x:v>
       </x:c>
       <x:c r="D405" t="str">
-        <x:v>Restore 16 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 16 点生命。</x:v>
       </x:c>
       <x:c r="E405" t="str">
         <x:v>下一战开场恢复 16 点生命。</x:v>
       </x:c>
       <x:c r="F405" t="str">
-        <x:v>Restore 16 life at the start of the next battle.</x:v>
+        <x:v>下一战开场恢复 16 点生命。</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -8103,16 +8169,16 @@
         <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Name</x:v>
       </x:c>
       <x:c r="C406" t="str">
-        <x:v>留下药引</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="D406" t="str">
-        <x:v>Keep the Catalyst</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="E406" t="str">
-        <x:v>留下药引</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F406" t="str">
-        <x:v>Keep the Catalyst</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -8121,16 +8187,16 @@
         <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Summary</x:v>
       </x:c>
       <x:c r="C407" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="D407" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="E407" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="F407" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -8139,16 +8205,16 @@
         <x:v>Buqi.Content.Event.event_old_pacts.Name</x:v>
       </x:c>
       <x:c r="C408" t="str">
-        <x:v>旧约清算</x:v>
+        <x:v>欠款清算 · 旧约</x:v>
       </x:c>
       <x:c r="D408" t="str">
-        <x:v>Old Pacts Settled</x:v>
+        <x:v>欠款清算 · 旧约</x:v>
       </x:c>
       <x:c r="E408" t="str">
-        <x:v>旧约清算</x:v>
+        <x:v>欠款清算 · 旧约</x:v>
       </x:c>
       <x:c r="F408" t="str">
-        <x:v>Old Pacts Settled</x:v>
+        <x:v>欠款清算 · 旧约</x:v>
       </x:c>
     </x:row>
     <x:row r="409">
@@ -8157,16 +8223,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Name</x:v>
       </x:c>
       <x:c r="C409" t="str">
-        <x:v>清偿旧约</x:v>
+        <x:v>清除全部欠款</x:v>
       </x:c>
       <x:c r="D409" t="str">
-        <x:v>Settle the Pact</x:v>
+        <x:v>清除全部欠款</x:v>
       </x:c>
       <x:c r="E409" t="str">
-        <x:v>清偿旧约</x:v>
+        <x:v>清除全部欠款</x:v>
       </x:c>
       <x:c r="F409" t="str">
-        <x:v>Settle the Pact</x:v>
+        <x:v>清除全部欠款</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -8175,16 +8241,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Summary</x:v>
       </x:c>
       <x:c r="C410" t="str">
-        <x:v>支付 3 灵石，清除账册与火种欠约。</x:v>
+        <x:v>支付 3 金币，清除全部欠款状态。</x:v>
       </x:c>
       <x:c r="D410" t="str">
-        <x:v>Pay 3 coins to clear ledger and ember obligations.</x:v>
+        <x:v>支付 3 金币，清除全部欠款状态。</x:v>
       </x:c>
       <x:c r="E410" t="str">
-        <x:v>支付 3 灵石，清除账册与火种欠约。</x:v>
+        <x:v>支付 3 金币，清除全部欠款状态。</x:v>
       </x:c>
       <x:c r="F410" t="str">
-        <x:v>Pay 3 coins to clear ledger and ember obligations.</x:v>
+        <x:v>支付 3 金币，清除全部欠款状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="411">
@@ -8193,16 +8259,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Name</x:v>
       </x:c>
       <x:c r="C411" t="str">
-        <x:v>带约入战</x:v>
+        <x:v>过载换超载改造</x:v>
       </x:c>
       <x:c r="D411" t="str">
-        <x:v>Carry the Pact</x:v>
+        <x:v>过载换超载改造</x:v>
       </x:c>
       <x:c r="E411" t="str">
-        <x:v>带约入战</x:v>
+        <x:v>过载换超载改造</x:v>
       </x:c>
       <x:c r="F411" t="str">
-        <x:v>Carry the Pact</x:v>
+        <x:v>过载换超载改造</x:v>
       </x:c>
     </x:row>
     <x:row r="412">
@@ -8211,16 +8277,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Summary</x:v>
       </x:c>
       <x:c r="C412" t="str">
-        <x:v>下一战增加 3 点失衡，获得超载精炼。</x:v>
+        <x:v>下一战增加 3 点过载，获得超载改造。</x:v>
       </x:c>
       <x:c r="D412" t="str">
-        <x:v>Start next battle with 3 noise debt and gain the Overload refinement.</x:v>
+        <x:v>下一战增加 3 点过载，获得超载改造。</x:v>
       </x:c>
       <x:c r="E412" t="str">
-        <x:v>下一战增加 3 点失衡，获得超载精炼。</x:v>
+        <x:v>下一战增加 3 点过载，获得超载改造。</x:v>
       </x:c>
       <x:c r="F412" t="str">
-        <x:v>Start next battle with 3 noise debt and gain the Overload refinement.</x:v>
+        <x:v>下一战增加 3 点过载，获得超载改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -8229,16 +8295,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Name</x:v>
       </x:c>
       <x:c r="C413" t="str">
-        <x:v>重订条款</x:v>
+        <x:v>获得购买折扣</x:v>
       </x:c>
       <x:c r="D413" t="str">
-        <x:v>Rewrite the Terms</x:v>
+        <x:v>获得购买折扣</x:v>
       </x:c>
       <x:c r="E413" t="str">
-        <x:v>重订条款</x:v>
+        <x:v>获得购买折扣</x:v>
       </x:c>
       <x:c r="F413" t="str">
-        <x:v>Rewrite the Terms</x:v>
+        <x:v>获得购买折扣</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -8247,16 +8313,16 @@
         <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Summary</x:v>
       </x:c>
       <x:c r="C414" t="str">
-        <x:v>支付 1 灵石，本日下一次购买少花 2 灵石。</x:v>
+        <x:v>支付 1 金币，本日下一次购买少花 2 金币。</x:v>
       </x:c>
       <x:c r="D414" t="str">
-        <x:v>Pay 1 coin; the next purchase today costs 2 less.</x:v>
+        <x:v>支付 1 金币，本日下一次购买少花 2 金币。</x:v>
       </x:c>
       <x:c r="E414" t="str">
-        <x:v>支付 1 灵石，本日下一次购买少花 2 灵石。</x:v>
+        <x:v>支付 1 金币，本日下一次购买少花 2 金币。</x:v>
       </x:c>
       <x:c r="F414" t="str">
-        <x:v>Pay 1 coin; the next purchase today costs 2 less.</x:v>
+        <x:v>支付 1 金币，本日下一次购买少花 2 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="415">
@@ -8265,16 +8331,16 @@
         <x:v>Buqi.Content.Event.event_scrap_recovery.Name</x:v>
       </x:c>
       <x:c r="C415" t="str">
-        <x:v>回收残器</x:v>
+        <x:v>装备回收 · 残件</x:v>
       </x:c>
       <x:c r="D415" t="str">
-        <x:v>Relic Recovery</x:v>
+        <x:v>装备回收 · 残件</x:v>
       </x:c>
       <x:c r="E415" t="str">
-        <x:v>回收残器</x:v>
+        <x:v>装备回收 · 残件</x:v>
       </x:c>
       <x:c r="F415" t="str">
-        <x:v>Relic Recovery</x:v>
+        <x:v>装备回收 · 残件</x:v>
       </x:c>
     </x:row>
     <x:row r="416">
@@ -8283,16 +8349,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Name</x:v>
       </x:c>
       <x:c r="C416" t="str">
-        <x:v>拆掉起手件</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="D416" t="str">
-        <x:v>Strip a Starter</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="E416" t="str">
-        <x:v>拆掉起手件</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="F416" t="str">
-        <x:v>Strip a Starter</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -8301,16 +8367,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Summary</x:v>
       </x:c>
       <x:c r="C417" t="str">
-        <x:v>移除一件起手器物，获得 4 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 4 金币。</x:v>
       </x:c>
       <x:c r="D417" t="str">
-        <x:v>Remove one starter item and gain 4 coins.</x:v>
+        <x:v>移除一件起手装备，获得 4 金币。</x:v>
       </x:c>
       <x:c r="E417" t="str">
-        <x:v>移除一件起手器物，获得 4 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 4 金币。</x:v>
       </x:c>
       <x:c r="F417" t="str">
-        <x:v>Remove one starter item and gain 4 coins.</x:v>
+        <x:v>移除一件起手装备，获得 4 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -8319,16 +8385,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Name</x:v>
       </x:c>
       <x:c r="C418" t="str">
-        <x:v>以旧换新</x:v>
+        <x:v>更换转向装备</x:v>
       </x:c>
       <x:c r="D418" t="str">
-        <x:v>Trade Old for New</x:v>
+        <x:v>更换转向装备</x:v>
       </x:c>
       <x:c r="E418" t="str">
-        <x:v>以旧换新</x:v>
+        <x:v>更换转向装备</x:v>
       </x:c>
       <x:c r="F418" t="str">
-        <x:v>Trade Old for New</x:v>
+        <x:v>更换转向装备</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -8337,16 +8403,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Summary</x:v>
       </x:c>
       <x:c r="C419" t="str">
-        <x:v>移除一件转向器物，获得一件改良反制器物。</x:v>
+        <x:v>移除一件转向装备，获得一件强化反制装备。</x:v>
       </x:c>
       <x:c r="D419" t="str">
-        <x:v>Remove one pivot item and gain an Improved counter item.</x:v>
+        <x:v>移除一件转向装备，获得一件强化反制装备。</x:v>
       </x:c>
       <x:c r="E419" t="str">
-        <x:v>移除一件转向器物，获得一件改良反制器物。</x:v>
+        <x:v>移除一件转向装备，获得一件强化反制装备。</x:v>
       </x:c>
       <x:c r="F419" t="str">
-        <x:v>Remove one pivot item and gain an Improved counter item.</x:v>
+        <x:v>移除一件转向装备，获得一件强化反制装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -8355,16 +8421,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Name</x:v>
       </x:c>
       <x:c r="C420" t="str">
-        <x:v>替人分拣</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="D420" t="str">
-        <x:v>Sort the Salvage</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="E420" t="str">
-        <x:v>替人分拣</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F420" t="str">
-        <x:v>Sort the Salvage</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -8373,16 +8439,16 @@
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Summary</x:v>
       </x:c>
       <x:c r="C421" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="D421" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="E421" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="F421" t="str">
-        <x:v>Gain 3 coins.</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -8391,16 +8457,16 @@
         <x:v>Buqi.Content.Event.event_calming_chime.Name</x:v>
       </x:c>
       <x:c r="C422" t="str">
-        <x:v>镇心钟鸣</x:v>
+        <x:v>状态调整 · 钟鸣</x:v>
       </x:c>
       <x:c r="D422" t="str">
-        <x:v>Calming Chime</x:v>
+        <x:v>状态调整 · 钟鸣</x:v>
       </x:c>
       <x:c r="E422" t="str">
-        <x:v>镇心钟鸣</x:v>
+        <x:v>状态调整 · 钟鸣</x:v>
       </x:c>
       <x:c r="F422" t="str">
-        <x:v>Calming Chime</x:v>
+        <x:v>状态调整 · 钟鸣</x:v>
       </x:c>
     </x:row>
     <x:row r="423">
@@ -8409,16 +8475,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Name</x:v>
       </x:c>
       <x:c r="C423" t="str">
-        <x:v>静听一刻</x:v>
+        <x:v>获得护盾与恢复</x:v>
       </x:c>
       <x:c r="D423" t="str">
-        <x:v>Listen in Stillness</x:v>
+        <x:v>获得护盾与恢复</x:v>
       </x:c>
       <x:c r="E423" t="str">
-        <x:v>静听一刻</x:v>
+        <x:v>获得护盾与恢复</x:v>
       </x:c>
       <x:c r="F423" t="str">
-        <x:v>Listen in Stillness</x:v>
+        <x:v>获得护盾与恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="424">
@@ -8427,16 +8493,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Summary</x:v>
       </x:c>
       <x:c r="C424" t="str">
-        <x:v>支付 1 灵石；下一战开场获得 10 护体并恢复 6 生命。</x:v>
+        <x:v>支付 1 金币；下一战开场获得 10 护盾并恢复 6 生命。</x:v>
       </x:c>
       <x:c r="D424" t="str">
-        <x:v>Pay 1 coin; next battle starts with 10 buffer and restores 6 life.</x:v>
+        <x:v>支付 1 金币；下一战开场获得 10 护盾并恢复 6 生命。</x:v>
       </x:c>
       <x:c r="E424" t="str">
-        <x:v>支付 1 灵石；下一战开场获得 10 护体并恢复 6 生命。</x:v>
+        <x:v>支付 1 金币；下一战开场获得 10 护盾并恢复 6 生命。</x:v>
       </x:c>
       <x:c r="F424" t="str">
-        <x:v>Pay 1 coin; next battle starts with 10 buffer and restores 6 life.</x:v>
+        <x:v>支付 1 金币；下一战开场获得 10 护盾并恢复 6 生命。</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -8445,16 +8511,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Name</x:v>
       </x:c>
       <x:c r="C425" t="str">
-        <x:v>调准钟舌</x:v>
+        <x:v>升级反制装备</x:v>
       </x:c>
       <x:c r="D425" t="str">
-        <x:v>Tune the Clapper</x:v>
+        <x:v>升级反制装备</x:v>
       </x:c>
       <x:c r="E425" t="str">
-        <x:v>调准钟舌</x:v>
+        <x:v>升级反制装备</x:v>
       </x:c>
       <x:c r="F425" t="str">
-        <x:v>Tune the Clapper</x:v>
+        <x:v>升级反制装备</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -8463,16 +8529,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Summary</x:v>
       </x:c>
       <x:c r="C426" t="str">
-        <x:v>支付 2 灵石，升级一件普通反制器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通反制装备。</x:v>
       </x:c>
       <x:c r="D426" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal counter item.</x:v>
+        <x:v>支付 2 金币，升级一件普通反制装备。</x:v>
       </x:c>
       <x:c r="E426" t="str">
-        <x:v>支付 2 灵石，升级一件普通反制器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通反制装备。</x:v>
       </x:c>
       <x:c r="F426" t="str">
-        <x:v>Pay 2 coins to upgrade a Normal counter item.</x:v>
+        <x:v>支付 2 金币，升级一件普通反制装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -8481,16 +8547,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Name</x:v>
       </x:c>
       <x:c r="C427" t="str">
-        <x:v>记下钟律</x:v>
+        <x:v>过载换共享装备</x:v>
       </x:c>
       <x:c r="D427" t="str">
-        <x:v>Record the Chime</x:v>
+        <x:v>过载换共享装备</x:v>
       </x:c>
       <x:c r="E427" t="str">
-        <x:v>记下钟律</x:v>
+        <x:v>过载换共享装备</x:v>
       </x:c>
       <x:c r="F427" t="str">
-        <x:v>Record the Chime</x:v>
+        <x:v>过载换共享装备</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -8499,16 +8565,16 @@
         <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Summary</x:v>
       </x:c>
       <x:c r="C428" t="str">
-        <x:v>下一战增加 2 点失衡，获得一件改良共享器物。</x:v>
+        <x:v>下一战增加 2 点过载，获得一件强化共享装备。</x:v>
       </x:c>
       <x:c r="D428" t="str">
-        <x:v>Start next battle with 2 noise debt and gain an Improved shared item.</x:v>
+        <x:v>下一战增加 2 点过载，获得一件强化共享装备。</x:v>
       </x:c>
       <x:c r="E428" t="str">
-        <x:v>下一战增加 2 点失衡，获得一件改良共享器物。</x:v>
+        <x:v>下一战增加 2 点过载，获得一件强化共享装备。</x:v>
       </x:c>
       <x:c r="F428" t="str">
-        <x:v>Start next battle with 2 noise debt and gain an Improved shared item.</x:v>
+        <x:v>下一战增加 2 点过载，获得一件强化共享装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="429">
@@ -8517,16 +8583,16 @@
         <x:v>Buqi.Content.Event.event_day_nine_ledger.Name</x:v>
       </x:c>
       <x:c r="C429" t="str">
-        <x:v>九日归账</x:v>
+        <x:v>第九日结算 · 账单</x:v>
       </x:c>
       <x:c r="D429" t="str">
-        <x:v>Day Nine Ledger</x:v>
+        <x:v>第九日结算 · 账单</x:v>
       </x:c>
       <x:c r="E429" t="str">
-        <x:v>九日归账</x:v>
+        <x:v>第九日结算 · 账单</x:v>
       </x:c>
       <x:c r="F429" t="str">
-        <x:v>Day Nine Ledger</x:v>
+        <x:v>第九日结算 · 账单</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -8535,16 +8601,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Name</x:v>
       </x:c>
       <x:c r="C430" t="str">
-        <x:v>按攻势结算</x:v>
+        <x:v>攻击构筑结算</x:v>
       </x:c>
       <x:c r="D430" t="str">
-        <x:v>Settle by Offense</x:v>
+        <x:v>攻击构筑结算</x:v>
       </x:c>
       <x:c r="E430" t="str">
-        <x:v>按攻势结算</x:v>
+        <x:v>攻击构筑结算</x:v>
       </x:c>
       <x:c r="F430" t="str">
-        <x:v>Settle by Offense</x:v>
+        <x:v>攻击构筑结算</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -8553,16 +8619,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Summary</x:v>
       </x:c>
       <x:c r="C431" t="str">
-        <x:v>攻击构筑获得 5 灵石。</x:v>
+        <x:v>攻击构筑获得 5 金币。</x:v>
       </x:c>
       <x:c r="D431" t="str">
-        <x:v>An attack build gains 5 coins.</x:v>
+        <x:v>攻击构筑获得 5 金币。</x:v>
       </x:c>
       <x:c r="E431" t="str">
-        <x:v>攻击构筑获得 5 灵石。</x:v>
+        <x:v>攻击构筑获得 5 金币。</x:v>
       </x:c>
       <x:c r="F431" t="str">
-        <x:v>An attack build gains 5 coins.</x:v>
+        <x:v>攻击构筑获得 5 金币。</x:v>
       </x:c>
     </x:row>
     <x:row r="432">
@@ -8571,16 +8637,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Name</x:v>
       </x:c>
       <x:c r="C432" t="str">
-        <x:v>按守势结算</x:v>
+        <x:v>护盾构筑结算</x:v>
       </x:c>
       <x:c r="D432" t="str">
-        <x:v>Settle by Defense</x:v>
+        <x:v>护盾构筑结算</x:v>
       </x:c>
       <x:c r="E432" t="str">
-        <x:v>按守势结算</x:v>
+        <x:v>护盾构筑结算</x:v>
       </x:c>
       <x:c r="F432" t="str">
-        <x:v>Settle by Defense</x:v>
+        <x:v>护盾构筑结算</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -8589,16 +8655,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Summary</x:v>
       </x:c>
       <x:c r="C433" t="str">
-        <x:v>护体构筑恢复 1 命。</x:v>
+        <x:v>护盾构筑恢复 1 命。</x:v>
       </x:c>
       <x:c r="D433" t="str">
-        <x:v>A shield build restores 1 life.</x:v>
+        <x:v>护盾构筑恢复 1 命。</x:v>
       </x:c>
       <x:c r="E433" t="str">
-        <x:v>护体构筑恢复 1 命。</x:v>
+        <x:v>护盾构筑恢复 1 命。</x:v>
       </x:c>
       <x:c r="F433" t="str">
-        <x:v>A shield build restores 1 life.</x:v>
+        <x:v>护盾构筑恢复 1 命。</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -8607,16 +8673,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Name</x:v>
       </x:c>
       <x:c r="C434" t="str">
-        <x:v>按续航结算</x:v>
+        <x:v>恢复构筑结算</x:v>
       </x:c>
       <x:c r="D434" t="str">
-        <x:v>Settle by Sustain</x:v>
+        <x:v>恢复构筑结算</x:v>
       </x:c>
       <x:c r="E434" t="str">
-        <x:v>按续航结算</x:v>
+        <x:v>恢复构筑结算</x:v>
       </x:c>
       <x:c r="F434" t="str">
-        <x:v>Settle by Sustain</x:v>
+        <x:v>恢复构筑结算</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -8625,16 +8691,16 @@
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Summary</x:v>
       </x:c>
       <x:c r="C435" t="str">
-        <x:v>恢复构筑获得复写精炼。</x:v>
+        <x:v>恢复构筑获得复写改造。</x:v>
       </x:c>
       <x:c r="D435" t="str">
-        <x:v>A healing build gains the Echo refinement.</x:v>
+        <x:v>恢复构筑获得复写改造。</x:v>
       </x:c>
       <x:c r="E435" t="str">
-        <x:v>恢复构筑获得复写精炼。</x:v>
+        <x:v>恢复构筑获得复写改造。</x:v>
       </x:c>
       <x:c r="F435" t="str">
-        <x:v>A healing build gains the Echo refinement.</x:v>
+        <x:v>恢复构筑获得复写改造。</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -8643,16 +8709,16 @@
         <x:v>Buqi.Content.Event.event_return_furnace.Name</x:v>
       </x:c>
       <x:c r="C436" t="str">
-        <x:v>不器归炉</x:v>
+        <x:v>最终强化 · 不器归炉</x:v>
       </x:c>
       <x:c r="D436" t="str">
-        <x:v>Return to the Formless Furnace</x:v>
+        <x:v>最终强化 · 不器归炉</x:v>
       </x:c>
       <x:c r="E436" t="str">
-        <x:v>不器归炉</x:v>
+        <x:v>最终强化 · 不器归炉</x:v>
       </x:c>
       <x:c r="F436" t="str">
-        <x:v>Return to the Formless Furnace</x:v>
+        <x:v>最终强化 · 不器归炉</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -8661,16 +8727,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Name</x:v>
       </x:c>
       <x:c r="C437" t="str">
-        <x:v>熔去旧起手</x:v>
+        <x:v>移除起手并升级装备</x:v>
       </x:c>
       <x:c r="D437" t="str">
-        <x:v>Melt the Old Starter</x:v>
+        <x:v>移除起手并升级装备</x:v>
       </x:c>
       <x:c r="E437" t="str">
-        <x:v>熔去旧起手</x:v>
+        <x:v>移除起手并升级装备</x:v>
       </x:c>
       <x:c r="F437" t="str">
-        <x:v>Melt the Old Starter</x:v>
+        <x:v>移除起手并升级装备</x:v>
       </x:c>
     </x:row>
     <x:row r="438">
@@ -8679,16 +8745,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Summary</x:v>
       </x:c>
       <x:c r="C438" t="str">
-        <x:v>移除一件起手器物，将一件收尾器物提升一级。</x:v>
+        <x:v>移除一件起手装备，将一件收尾装备提升一级。</x:v>
       </x:c>
       <x:c r="D438" t="str">
-        <x:v>Remove one starter item and upgrade one finisher item.</x:v>
+        <x:v>移除一件起手装备，将一件收尾装备提升一级。</x:v>
       </x:c>
       <x:c r="E438" t="str">
-        <x:v>移除一件起手器物，将一件收尾器物提升一级。</x:v>
+        <x:v>移除一件起手装备，将一件收尾装备提升一级。</x:v>
       </x:c>
       <x:c r="F438" t="str">
-        <x:v>Remove one starter item and upgrade one finisher item.</x:v>
+        <x:v>移除一件起手装备，将一件收尾装备提升一级。</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -8697,16 +8763,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Name</x:v>
       </x:c>
       <x:c r="C439" t="str">
-        <x:v>重排三路</x:v>
+        <x:v>购买高级转向装备</x:v>
       </x:c>
       <x:c r="D439" t="str">
-        <x:v>Rebalance the Three Paths</x:v>
+        <x:v>购买高级转向装备</x:v>
       </x:c>
       <x:c r="E439" t="str">
-        <x:v>重排三路</x:v>
+        <x:v>购买高级转向装备</x:v>
       </x:c>
       <x:c r="F439" t="str">
-        <x:v>Rebalance the Three Paths</x:v>
+        <x:v>购买高级转向装备</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -8715,16 +8781,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Summary</x:v>
       </x:c>
       <x:c r="C440" t="str">
-        <x:v>支付 2 灵石，获得一件定型转向器物。</x:v>
+        <x:v>支付 2 金币，获得一件高级转向装备。</x:v>
       </x:c>
       <x:c r="D440" t="str">
-        <x:v>Pay 2 coins to gain a Fixed pivot item.</x:v>
+        <x:v>支付 2 金币，获得一件高级转向装备。</x:v>
       </x:c>
       <x:c r="E440" t="str">
-        <x:v>支付 2 灵石，获得一件定型转向器物。</x:v>
+        <x:v>支付 2 金币，获得一件高级转向装备。</x:v>
       </x:c>
       <x:c r="F440" t="str">
-        <x:v>Pay 2 coins to gain a Fixed pivot item.</x:v>
+        <x:v>支付 2 金币，获得一件高级转向装备。</x:v>
       </x:c>
     </x:row>
     <x:row r="441">
@@ -8733,16 +8799,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_close.Name</x:v>
       </x:c>
       <x:c r="C441" t="str">
-        <x:v>封存余火</x:v>
+        <x:v>恢复生命并清除状态</x:v>
       </x:c>
       <x:c r="D441" t="str">
-        <x:v>Seal the Remaining Flame</x:v>
+        <x:v>恢复生命并清除状态</x:v>
       </x:c>
       <x:c r="E441" t="str">
-        <x:v>封存余火</x:v>
+        <x:v>恢复生命并清除状态</x:v>
       </x:c>
       <x:c r="F441" t="str">
-        <x:v>Seal the Remaining Flame</x:v>
+        <x:v>恢复生命并清除状态</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -8751,16 +8817,16 @@
         <x:v>Buqi.Content.EventOption.event_return_furnace_close.Summary</x:v>
       </x:c>
       <x:c r="C442" t="str">
-        <x:v>恢复 1 命并清除全部跨日约记。</x:v>
+        <x:v>恢复 1 命并清除全部跨日状态。</x:v>
       </x:c>
       <x:c r="D442" t="str">
-        <x:v>Restore 1 life and clear all cross-day obligations.</x:v>
+        <x:v>恢复 1 命并清除全部跨日状态。</x:v>
       </x:c>
       <x:c r="E442" t="str">
-        <x:v>恢复 1 命并清除全部跨日约记。</x:v>
+        <x:v>恢复 1 命并清除全部跨日状态。</x:v>
       </x:c>
       <x:c r="F442" t="str">
-        <x:v>Restore 1 life and clear all cross-day obligations.</x:v>
+        <x:v>恢复 1 命并清除全部跨日状态。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
